--- a/naver-place-crawler/results_nail/용산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/용산_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V71"/>
+  <dimension ref="A1:V116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7080,6 +7080,4196 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>살롱드다한</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ddalkong9830@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로 257 2층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>53</v>
+      </c>
+      <c r="R72" t="n">
+        <v>282</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1917414808</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1917414808</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>진유진네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>seoul2816@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1416-2081</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 284</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>52</v>
+      </c>
+      <c r="R73" t="n">
+        <v>93</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>31574498</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31574498</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>설화미</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>who1who2@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1381-4227</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sulwhami_beauty/</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>290</v>
+      </c>
+      <c r="R74" t="n">
+        <v>344</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>33647337</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33647337</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>제이제이 네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>yang4550@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1411-8138</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 회나무로 32-3 2층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jjjjnail</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2</v>
+      </c>
+      <c r="R75" t="n">
+        <v>3</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>79017915</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/79017915</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>유스뷰티</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>cej9261@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1422-3533</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로20길 21 1층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/youthnail/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>117</v>
+      </c>
+      <c r="R76" t="n">
+        <v>121</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>38467380</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38467380</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>네일래쉬</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>nailash@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1371-0008</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nailash</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>49</v>
+      </c>
+      <c r="R77" t="n">
+        <v>76</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1220901153</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1220901153</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>비바이유 한남</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>picobakery@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1371-9481</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/b.by_you</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2019591721</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2019591721</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>티아라네일어반스파</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>orora_1976@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>02-790-7882</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>33213520</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33213520</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>오늘도네일</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sws9383@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1345-4179</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>http://instagram.com/today_nail_ichon</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>292</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>7</v>
+      </c>
+      <c r="R80" t="n">
+        <v>299</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>21038031</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21038031</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>네일스눕</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>graceham_@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1428-1646</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로52길 38 202호</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_snoope</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>6</v>
+      </c>
+      <c r="R81" t="n">
+        <v>148</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1926501985</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1926501985</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>클리피</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>seoul2gun@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1855-4010</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_txcJCb</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>3</v>
+      </c>
+      <c r="R82" t="n">
+        <v>14</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1546271749</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1546271749</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>붙여핸썹</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>woowim@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1333965738</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1333965738</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>재니네일한남</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>evian___@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_eKxmLxl</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>44</v>
+      </c>
+      <c r="R84" t="n">
+        <v>77</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1593741438</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1593741438</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>춘희손톱</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>chii0216@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1306-7521</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>http://instagram.com/choonheenail</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>99</v>
+      </c>
+      <c r="R85" t="n">
+        <v>294</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>20559743</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20559743</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>아드</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>adfontes_math@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.th_kr</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>51</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1700535825</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1700535825</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>네일테라피은</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>mountain__sun@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1379-8496</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailtherapyeun</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>9</v>
+      </c>
+      <c r="R87" t="n">
+        <v>211</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1180134699</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1180134699</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>루아드네일</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sumr2002@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1452-9237</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xoEbJn/friend</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>8</v>
+      </c>
+      <c r="R88" t="n">
+        <v>80</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>2003721483</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2003721483</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>데코네일</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>bambi_showpu@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>82</v>
+      </c>
+      <c r="R89" t="n">
+        <v>122</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>36812317</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36812317</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>또또네일</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>clsald30@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1354-9049</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로 200 1층</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ttotto__nail</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>7</v>
+      </c>
+      <c r="R90" t="n">
+        <v>153</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2020672159</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2020672159</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>우아한 네일 살롱</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>findmyperfectdays@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wooanail_salon</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>63</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1370902820</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370902820</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>네일슈슈</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>brilliant14694@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1435-9113</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_chouchou_</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>458</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>28</v>
+      </c>
+      <c r="R92" t="n">
+        <v>486</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1185094311</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1185094311</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>후암네일</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>cleanleader1@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/huam_nail</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>2033884779</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2033884779</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>아로하네일</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>bbotive@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1391-4369</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로14길 10 2층</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/alohanail_chae</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>3</v>
+      </c>
+      <c r="R94" t="n">
+        <v>78</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1264306160</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1264306160</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>네일드모네</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2860126@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 67 206호</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/naildemonet</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>2</v>
+      </c>
+      <c r="R95" t="n">
+        <v>90</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>2062875678</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2062875678</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>네일디렉터</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>naildirector@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>02-797-8188</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/naildirector</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>11</v>
+      </c>
+      <c r="R96" t="n">
+        <v>153</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1487195546</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1487195546</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>헤더네일</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>mmmmbin@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1464-8960</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/heathernail_102/</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>2</v>
+      </c>
+      <c r="R97" t="n">
+        <v>27</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1399079243</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1399079243</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>제이매직네일스</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>tlstnals1010@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>070-8882-4343</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/j_magic_nail</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>25</v>
+      </c>
+      <c r="R98" t="n">
+        <v>90</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>1438268528</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1438268528</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>청담네일박스 용산점</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>smilehh406@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1325-5985</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 95 B동110호</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cheongdam_nailbox</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>2020464978</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2020464978</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>오렌지나무</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>vline310@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1323-2154</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한남대로20길 13 1층</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>2</v>
+      </c>
+      <c r="R100" t="n">
+        <v>15</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1568164546</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1568164546</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>네일샵베이비</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>zxlixz@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0507-1396-4649</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 우사단로2길 19 1층</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1</v>
+      </c>
+      <c r="R101" t="n">
+        <v>39</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>1847608869</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1847608869</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>네일의날씨</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>queen77577@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1430-0707</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 288-2 1층</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_nalssi</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>496</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>48</v>
+      </c>
+      <c r="R102" t="n">
+        <v>544</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>1050641028</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1050641028</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>프로네일</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>sonvely89@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1421-1525</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/itaewonpronail/</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>105</v>
+      </c>
+      <c r="R103" t="n">
+        <v>111</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>13028002</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13028002</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>뷰리뉼레</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>kimnr123@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0507-1389-5562</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 후암로 28 1층</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://toss.place/_lb/TYhSdSVIw</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>6</v>
+      </c>
+      <c r="R104" t="n">
+        <v>142</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>33277553</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33277553</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>쵸민네일</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>sunday020@naver.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0507-1403-3417</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
+      <c r="R105" t="n">
+        <v>2</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>1664663384</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1664663384</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>네일가꿈</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>dbcom36@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0507-1403-8723</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/e_nailshop_sj</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>75</v>
+      </c>
+      <c r="R106" t="n">
+        <v>547</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>1966796864</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1966796864</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>디에고푸스 희네일 이촌점</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jwkang3929@naver.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0507-1339-5732</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/heenail4345</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>80</v>
+      </c>
+      <c r="R107" t="n">
+        <v>155</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>1972424680</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1972424680</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>에일린</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>dsfafadf34@naver.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0507-1445-2816</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>388</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>78</v>
+      </c>
+      <c r="R108" t="n">
+        <v>466</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>1447531035</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1447531035</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>네일노마드 용산푸르지오써밋점</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>kjr1212a@naver.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0507-1310-3658</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailnomad_</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>470</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>8</v>
+      </c>
+      <c r="R109" t="n">
+        <v>478</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>1841821386</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1841821386</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>네일프롬다니</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>arielisflowery@naver.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0507-1349-9460</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>17</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>1774853191</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1774853191</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>글로시블라썸 아이파크몰</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>kmww234@naver.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로23길 55</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>54</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>1485867849</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1485867849</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>신용산네일라뜰리에왁싱</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>hee_1220@naver.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1380-7730</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>2</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>1054108199</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054108199</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>milkycoco95@naver.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>02-749-9134</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/vivinail</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>45</v>
+      </c>
+      <c r="R113" t="n">
+        <v>302</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>21834362</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21834362</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>블랑</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>hg6580@naver.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>02-790-8798</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nailist_blanc</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1</v>
+      </c>
+      <c r="R114" t="n">
+        <v>8</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>909330706</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/909330706</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>네일바라기</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>sydy8585@naver.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_baragi_</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>16</v>
+      </c>
+      <c r="R115" t="n">
+        <v>105</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>1091743517</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1091743517</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>메종드로르</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>stylechosun@naver.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0507-1386-1014</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>26</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>2029580174</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2029580174</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver-place-crawler/results_nail/용산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/용산_네일샵.xlsx
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뷰리뉼레</t>
+          <t>리라네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kimnr123@naver.com</t>
+          <t>kkmm_0707@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1389-5562</t>
+          <t>02-703-4125</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 후암로 28 1층</t>
+          <t>서울특별시 용산구 원효로41길 23</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYhSdSVIw</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>33277553</t>
+          <t>1131445662</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33277553</t>
+          <t>https://m.place.naver.com/place/1131445662</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아로하네일</t>
+          <t>티아라네일어반스파</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bbotive@naver.com</t>
+          <t>esthii@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1391-4369</t>
+          <t>02-790-7882</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로14길 10 2층</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/alohanail_chae</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1264306160</t>
+          <t>33213520</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264306160</t>
+          <t>https://m.place.naver.com/place/33213520</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,30 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>묘즈네일</t>
+          <t>오늘도네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>xoxobloggirl@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1345-4179</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
+          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WxedxgG</t>
+          <t>http://instagram.com/today_nail_ichon</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -796,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>46</v>
+        <v>293</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>56</v>
+        <v>300</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1136869573</t>
+          <t>21038031</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136869573</t>
+          <t>https://m.place.naver.com/place/21038031</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>카밍네일</t>
+          <t>루미가넷네일존 이마트 용산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>daisoblog@naver.com</t>
+          <t>hyer2986@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1357-1496</t>
+          <t>0507-1401-9470</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 42 1층</t>
+          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/calming_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -874,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -895,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1383549813</t>
+          <t>1619342094</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383549813</t>
+          <t>https://m.place.naver.com/place/1619342094</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -936,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>무구네일</t>
+          <t>제이비풋 굳은살&amp;발톱 케어</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mugunail2025@naver.com</t>
+          <t>sunny_0225@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1353-2420</t>
+          <t>02-794-8551</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 46 2층</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -968,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>190</v>
+        <v>351</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>179</v>
       </c>
       <c r="R6" t="n">
-        <v>232</v>
+        <v>530</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2093535455</t>
+          <t>12791408</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093535455</t>
+          <t>https://m.place.naver.com/place/12791408</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1030,34 +1034,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코코루네일</t>
+          <t>묘즈네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>xanxixxanx@naver.com</t>
+          <t>xoxobloggirl@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1390-4270</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
+          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_WxedxgG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1078,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R7" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1768871817</t>
+          <t>1136869573</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768871817</t>
+          <t>https://m.place.naver.com/place/1136869573</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>오렌지나무</t>
+          <t>네일뮤지엄</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dew517@naver.com</t>
+          <t>nail-museum@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1323-2154</t>
+          <t>070-7543-4009</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로20길 13 1층</t>
+          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
+          <t>https://blog.naver.com/nail-museum</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>13</v>
+        <v>345</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="R8" t="n">
-        <v>15</v>
+        <v>705</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1568164546</t>
+          <t>1881584782</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568164546</t>
+          <t>https://m.place.naver.com/place/1881584782</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>춘희손톱</t>
+          <t>제이제이 네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chii0216@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1306-7521</t>
+          <t>0507-1411-8138</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
+          <t>서울특별시 용산구 회나무로 32-3 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://instagram.com/choonheenail</t>
+          <t>https://www.instagram.com/jjjjnail</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>195</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>294</v>
+        <v>3</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>20559743</t>
+          <t>79017915</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20559743</t>
+          <t>https://m.place.naver.com/place/79017915</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일더누브</t>
+          <t>데코네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hasom0304@naver.com</t>
+          <t>bambi_showpu@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1325,17 +1325,17 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 210 1층</t>
+          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdFnxhn</t>
+          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="R10" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1146800442</t>
+          <t>36812317</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1146800442</t>
+          <t>https://m.place.naver.com/place/36812317</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>디에고푸스 희네일 이촌점</t>
+          <t>이촌동 네일타임 삼익상가</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jwkang3929@naver.com</t>
+          <t>yjk2650@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1339-5732</t>
+          <t>02-749-8604</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heenail4345</t>
+          <t>https://youtube.com/@ichon_nail_time</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="Q11" t="n">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="R11" t="n">
-        <v>157</v>
+        <v>250</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1972424680</t>
+          <t>1281193252</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972424680</t>
+          <t>https://m.place.naver.com/place/1281193252</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1496,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>바림</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>doyacart@naver.com</t>
-        </is>
-      </c>
+          <t>네일드모네</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>02-318-2055</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로 73</t>
+          <t>서울특별시 용산구 독서당로 67 206호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://instagram.com/Barim_nail</t>
+          <t>https://www.instagram.com/naildemonet</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1545,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1560,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1862156671</t>
+          <t>2062875678</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862156671</t>
+          <t>https://m.place.naver.com/place/2062875678</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1582,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>나비네일</t>
+          <t>오손내미오</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jytgh@naver.com</t>
+          <t>playnauts@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1416-0638</t>
+          <t>0507-1492-1340</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가-210</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oh_sonemio</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1622,7 +1614,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1643,17 +1635,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1654,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>36629016</t>
+          <t>1311070929</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36629016</t>
+          <t>https://m.place.naver.com/place/1311070929</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1684,25 +1676,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>어서오손네일</t>
+          <t>카밍네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>funhanbro@naver.com</t>
+          <t>daisoblog@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1357-1496</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
+          <t>서울특별시 용산구 소월로20길 42 1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/funhanbro</t>
+          <t>https://www.instagram.com/calming_nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1717,7 +1713,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1737,13 +1733,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="R14" t="n">
-        <v>23</v>
+        <v>192</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,56 +1748,52 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1030962704</t>
+          <t>1383549813</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030962704</t>
+          <t>https://m.place.naver.com/place/1383549813</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>네일아트재료</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일스눕</t>
+          <t>메이크케이</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>yseaeaho@naver.com</t>
+          <t>kbanknow@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1428-1646</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로52길 38 202호</t>
+          <t>서울특별시 용산구 청파로47길 56 1층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_snoope</t>
+          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1811,7 +1803,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1831,13 +1823,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1838,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1926501985</t>
+          <t>2081839313</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926501985</t>
+          <t>https://m.place.naver.com/place/2081839313</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1868,29 +1860,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일의날씨</t>
+          <t>투투네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mistymoon5@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1430-0707</t>
+          <t>0507-1336-4546</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 288-2 1층</t>
+          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_nalssi</t>
+          <t>https://www.instagram.com/twotwo_nail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1916,7 +1908,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1925,13 +1917,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>497</v>
+        <v>102</v>
       </c>
       <c r="Q16" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>545</v>
+        <v>107</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1932,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1050641028</t>
+          <t>1253759614</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050641028</t>
+          <t>https://m.place.naver.com/place/1253759614</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1962,29 +1954,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일삼각지</t>
+          <t>리네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nailsamgakji@naver.com</t>
+          <t>dlwjddo7053@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1316-2792</t>
+          <t>0507-1421-7880</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
+          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_samgakji</t>
+          <t>http://instagram.com/ri_nail7877</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2010,7 +2002,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2019,13 +2011,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2026,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1872968588</t>
+          <t>32244399</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1872968588</t>
+          <t>https://m.place.naver.com/place/32244399</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2048,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일드모네</t>
+          <t>더 트리니티 네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2860126@naver.com</t>
+          <t>dlfnfl0129@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2069,12 +2061,12 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 67 206호</t>
+          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildemonet</t>
+          <t>https://www.instagram.com/the_trinity_nail/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2109,13 +2101,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="R18" t="n">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2116,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2062875678</t>
+          <t>1060176123</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2062875678</t>
+          <t>https://m.place.naver.com/place/1060176123</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2146,29 +2138,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Breathnailz</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>mooisu@naver.com</t>
-        </is>
-      </c>
+          <t>청담네일박스 용산점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1358-6853</t>
+          <t>0507-1325-5985</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 36 1층</t>
+          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cheongdam_nailbox</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2178,7 +2166,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2194,22 +2182,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,17 +2206,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1488241394</t>
+          <t>2020464978</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488241394</t>
+          <t>https://m.place.naver.com/place/2020464978</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2240,29 +2228,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>신데렐라</t>
+          <t>손톱까끼</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dracura10@naver.com</t>
+          <t>sinachoco@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02-790-3304</t>
+          <t>0507-1310-9297</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 61</t>
+          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kkakki_nail/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2272,7 +2260,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2293,17 +2281,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2300,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>20662540</t>
+          <t>20939317</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20662540</t>
+          <t>https://m.place.naver.com/place/20939317</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2334,29 +2322,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>이촌 네일타임 LG프라자</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>blingsea@naver.com</t>
-        </is>
-      </c>
+          <t>마틸다네일M 한남점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1498-8612</t>
+          <t>0507-1412-3082</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
+          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://matildanailshop-mo3.imweb.me/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2366,12 +2350,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2387,17 +2371,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="R21" t="n">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2390,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>20064911</t>
+          <t>1798849933</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20064911</t>
+          <t>https://m.place.naver.com/place/1798849933</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2428,34 +2412,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>쵸코네일</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>boong27@naver.com</t>
-        </is>
-      </c>
+          <t>플리네일 용산해링턴점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>02-749-7795</t>
+          <t>0507-1406-7552</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
+          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2465,7 +2445,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2485,13 +2465,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>17</v>
+        <v>438</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,17 +2480,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>19490178</t>
+          <t>2075608465</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19490178</t>
+          <t>https://m.place.naver.com/place/2075608465</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2522,34 +2502,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>반디인하우스 용산아이파크몰점</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>bandinhouse_yongsan@naver.com</t>
-        </is>
-      </c>
+          <t>바림</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1472-1811</t>
+          <t>02-318-2055</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
+          <t>서울특별시 용산구 두텁바위로 73</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
+          <t>http://instagram.com/Barim_nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2559,7 +2535,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2579,13 +2555,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1241</v>
+        <v>11</v>
       </c>
       <c r="Q23" t="n">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1430</v>
+        <v>13</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,17 +2570,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1049297184</t>
+          <t>1862156671</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049297184</t>
+          <t>https://m.place.naver.com/place/1862156671</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2616,34 +2592,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>쿠로키네일</t>
+          <t>정원네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>pretty6144@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1481-2893</t>
+          <t>0507-1406-7118</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 19-2 1층</t>
+          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xaxcxeBG</t>
+          <t>http://instagram.com/jungwon_nail_</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2664,7 +2640,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2673,13 +2649,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,17 +2664,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1723956505</t>
+          <t>1935294802</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723956505</t>
+          <t>https://m.place.naver.com/place/1935294802</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2710,29 +2686,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>위위즈 용산점</t>
+          <t>제이미 네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yigu8@naver.com</t>
+          <t>see7833@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1366-3547</t>
+          <t>02-701-5602</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
+          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ouiouiznail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2742,7 +2718,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2763,17 +2739,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>509</v>
+        <v>29</v>
       </c>
       <c r="Q25" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>543</v>
+        <v>31</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2758,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1557214777</t>
+          <t>255540367</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557214777</t>
+          <t>https://m.place.naver.com/place/255540367</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2804,29 +2780,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일샵입니다</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>yooawo@naver.com</t>
-        </is>
-      </c>
+          <t>네일샵베이비</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1336-5457</t>
+          <t>0507-1396-4649</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
+          <t>서울특별시 용산구 우사단로2길 19 1층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shopnailshop/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2836,7 +2808,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2857,17 +2829,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>171</v>
+        <v>38</v>
       </c>
       <c r="Q26" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>206</v>
+        <v>39</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2848,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>954197461</t>
+          <t>1847608869</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/954197461</t>
+          <t>https://m.place.naver.com/place/1847608869</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2870,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>오드리네일</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ardusy@naver.com</t>
-        </is>
-      </c>
+          <t>신데렐라</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1446-0227</t>
+          <t>02-790-3304</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
+          <t>서울특별시 용산구 보광로 61</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oudreynail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2930,7 +2898,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2951,17 +2919,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2938,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1497063684</t>
+          <t>20662540</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1497063684</t>
+          <t>https://m.place.naver.com/place/20662540</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2992,29 +2960,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일슈슈</t>
+          <t>네일디렉터</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>brilliant14694@naver.com</t>
+          <t>naildirector@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1435-9113</t>
+          <t>02-797-8188</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
+          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_chouchou_</t>
+          <t>https://blog.naver.com/naildirector</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3029,7 +2997,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3049,13 +3017,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>461</v>
+        <v>157</v>
       </c>
       <c r="Q28" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="R28" t="n">
-        <v>489</v>
+        <v>168</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3032,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1185094311</t>
+          <t>1487195546</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185094311</t>
+          <t>https://m.place.naver.com/place/1487195546</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3086,29 +3054,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>후암네일</t>
+          <t>네일래쉬</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dndud7532@naver.com</t>
+          <t>nailash@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1301-4091</t>
+          <t>0507-1371-0008</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
+          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/huam_nail</t>
+          <t>https://blog.naver.com/nailash</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3123,7 +3091,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3143,13 +3111,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="R29" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,17 +3126,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2033884779</t>
+          <t>1220901153</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033884779</t>
+          <t>https://m.place.naver.com/place/1220901153</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3180,30 +3148,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>마고뷰티</t>
+          <t>네일삼각지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mago_smp@naver.com</t>
+          <t>nailsamgakji@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1316-2792</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
+          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xjBnAn</t>
+          <t>https://www.instagram.com/nail_samgakji</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3233,13 +3205,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="Q30" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,17 +3220,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1939429266</t>
+          <t>1872968588</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939429266</t>
+          <t>https://m.place.naver.com/place/1872968588</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3270,29 +3242,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>진주네 네일 효창공원점</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>cjaezero@naver.com</t>
-        </is>
-      </c>
+          <t>아드</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1403-6610</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
+          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jinjunenail</t>
+          <t>https://www.instagram.com/a.th_kr</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3327,13 +3291,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3342,17 +3306,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2056938739</t>
+          <t>1700535825</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056938739</t>
+          <t>https://m.place.naver.com/place/1700535825</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3364,25 +3328,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일클로버</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>bongbong323@naver.com</t>
-        </is>
-      </c>
+          <t>유스뷰티</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1422-3533</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
+          <t>서울특별시 용산구 이태원로20길 21 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailclover_yongsan</t>
+          <t>https://www.instagram.com/youthnail/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3417,13 +3381,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="R32" t="n">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3396,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>32496791</t>
+          <t>38467380</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32496791</t>
+          <t>https://m.place.naver.com/place/38467380</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3454,39 +3418,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일샵베이비</t>
+          <t>마고뷰티</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>zxlixz@naver.com</t>
+          <t>mago_smp@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1396-4649</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로2길 19 1층</t>
+          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xjBnAn</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3502,22 +3462,22 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="R33" t="n">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,17 +3486,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1847608869</t>
+          <t>1939429266</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847608869</t>
+          <t>https://m.place.naver.com/place/1939429266</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3548,25 +3508,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>아드</t>
+          <t>아로하네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>adfontes_math@naver.com</t>
+          <t>bbotive@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1391-4369</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
+          <t>서울특별시 용산구 이태원로14길 10 2층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.th_kr</t>
+          <t>http://www.instagram.com/alohanail_chae</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3601,13 +3565,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,17 +3580,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1700535825</t>
+          <t>1264306160</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700535825</t>
+          <t>https://m.place.naver.com/place/1264306160</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3638,29 +3602,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>투투네일</t>
+          <t>에일린</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>myungae7@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1336-4546</t>
+          <t>0507-1445-2816</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
+          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/twotwo_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3670,7 +3634,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3691,17 +3655,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>102</v>
+        <v>393</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="R35" t="n">
-        <v>107</v>
+        <v>471</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,17 +3674,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1253759614</t>
+          <t>1447531035</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253759614</t>
+          <t>https://m.place.naver.com/place/1447531035</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3732,29 +3696,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일월드</t>
+          <t>수아르네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>daisukitokyo@naver.com</t>
+          <t>xxong_11@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02-715-9585</t>
+          <t>0507-1354-9689</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6</t>
+          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/swa_rnail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3764,7 +3728,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3785,17 +3749,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,17 +3768,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1228817187</t>
+          <t>21568200</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228817187</t>
+          <t>https://m.place.naver.com/place/21568200</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3826,25 +3790,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>글로시블라썸 아이파크몰</t>
+          <t>메종드로르</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cueren@naver.com</t>
+          <t>stylechosun@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1386-1014</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55</t>
+          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3854,7 +3822,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3875,17 +3843,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3894,17 +3862,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1485867849</t>
+          <t>2029580174</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485867849</t>
+          <t>https://m.place.naver.com/place/2029580174</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3916,29 +3884,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>j2lang@naver.com</t>
-        </is>
-      </c>
+          <t>이촌 네일타임 LG프라자</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1345-4179</t>
+          <t>0507-1498-8612</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
+          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://instagram.com/today_nail_ichon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3948,7 +3912,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3969,17 +3933,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>293</v>
+        <v>12</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>300</v>
+        <v>17</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3988,17 +3952,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>21038031</t>
+          <t>20064911</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21038031</t>
+          <t>https://m.place.naver.com/place/20064911</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4010,29 +3974,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일휴</t>
+          <t>수 네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>white5198@naver.com</t>
+          <t>qkrqhrdfrn@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>02-711-3646</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
+          <t>서울특별시 용산구 만리재로 196 B1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/qkrqhrdfrn</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4042,12 +4002,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4058,22 +4018,22 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4082,17 +4042,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1611951357</t>
+          <t>1989007422</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611951357</t>
+          <t>https://m.place.naver.com/place/1989007422</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4104,39 +4064,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>에일린</t>
+          <t>쿠로키네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>myungae7@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1445-2816</t>
+          <t>0507-1481-2893</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
+          <t>서울특별시 용산구 신흥로 19-2 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xaxcxeBG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4152,22 +4112,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>393</v>
+        <v>157</v>
       </c>
       <c r="Q40" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="R40" t="n">
-        <v>471</v>
+        <v>165</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4176,17 +4136,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1447531035</t>
+          <t>1723956505</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447531035</t>
+          <t>https://m.place.naver.com/place/1723956505</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4198,29 +4158,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>네일바이르레</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>l5v2osh@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>02-749-9134</t>
+          <t>0507-1312-9470</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
+          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/vivinail</t>
+          <t>http://www.instagram.com/nail_by_lerre</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4255,13 +4215,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>257</v>
+        <v>88</v>
       </c>
       <c r="Q41" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="R41" t="n">
-        <v>302</v>
+        <v>94</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4270,17 +4230,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>21834362</t>
+          <t>37818863</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21834362</t>
+          <t>https://m.place.naver.com/place/37818863</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4292,29 +4252,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>플리네일 용산해링턴점</t>
+          <t>덴드네일한남</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>lamidays@naver.com</t>
+          <t>eunii222@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1406-7552</t>
+          <t>0507-1378-0596</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
+          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/eunii222</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4329,7 +4289,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4349,13 +4309,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>436</v>
+        <v>124</v>
       </c>
       <c r="Q42" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R42" t="n">
-        <v>451</v>
+        <v>146</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,52 +4324,56 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2075608465</t>
+          <t>1108900148</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075608465</t>
+          <t>https://m.place.naver.com/place/1108900148</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>네일아트재료</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>메이크케이</t>
+          <t>네일스눕</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kbanknow@naver.com</t>
+          <t>yseaeaho@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1428-1646</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 56 1층</t>
+          <t>서울특별시 용산구 한강대로52길 38 202호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
+          <t>https://www.instagram.com/nail_snoope</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4419,7 +4383,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4439,13 +4403,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4454,17 +4418,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2081839313</t>
+          <t>1926501985</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2081839313</t>
+          <t>https://m.place.naver.com/place/1926501985</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4476,34 +4440,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>마틸다네일M 한남점</t>
+          <t>플로르 네일 이태원점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>flornail@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1412-3082</t>
+          <t>02-790-4182</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
+          <t>서울특별시 용산구 우사단로 47 4층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://matildanailshop-mo3.imweb.me/</t>
+          <t>https://blog.naver.com/flornail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4533,13 +4497,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="Q44" t="n">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="R44" t="n">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4548,17 +4512,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1798849933</t>
+          <t>32435712</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798849933</t>
+          <t>https://m.place.naver.com/place/32435712</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4570,29 +4534,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일프롬다니</t>
+          <t>네일휴</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>arielisflowery@naver.com</t>
+          <t>white5198@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1349-9460</t>
+          <t>02-711-3646</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
+          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4602,7 +4566,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4623,17 +4587,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4642,17 +4606,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1774853191</t>
+          <t>1611951357</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774853191</t>
+          <t>https://m.place.naver.com/place/1611951357</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4664,29 +4628,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>제이제이 네일</t>
+          <t>네일바라기</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>sydy8585@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1411-8138</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 회나무로 32-3 2층</t>
+          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjjjnail</t>
+          <t>http://instagram.com/nail_baragi_</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4721,13 +4681,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="R46" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4736,17 +4696,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>79017915</t>
+          <t>1091743517</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/79017915</t>
+          <t>https://m.place.naver.com/place/1091743517</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4758,39 +4718,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일꾼</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>jinheeloo@naver.com</t>
-        </is>
-      </c>
+          <t>다교네일 한남</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1407-8585</t>
+          <t>0507-1339-1024</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_VZqxfG/chat</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4806,22 +4762,22 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>28</v>
+        <v>338</v>
       </c>
       <c r="Q47" t="n">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="R47" t="n">
-        <v>162</v>
+        <v>374</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4830,17 +4786,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1395413071</t>
+          <t>37620988</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395413071</t>
+          <t>https://m.place.naver.com/place/37620988</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4852,29 +4808,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일린</t>
+          <t>네일노마드 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>cookyismylife@naver.com</t>
+          <t>kjr1212a@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1344-8515</t>
+          <t>0507-1310-3658</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naileensalon</t>
+          <t>https://www.instagram.com/nailnomad_</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4909,13 +4865,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>479</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4924,17 +4880,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1996449351</t>
+          <t>1841821386</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996449351</t>
+          <t>https://m.place.naver.com/place/1841821386</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4946,39 +4902,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일셀레나</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>soeyn92@naver.com</t>
-        </is>
-      </c>
+          <t>글로시블라썸 아이파크몰</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>02-795-6529</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
+          <t>서울특별시 용산구 한강대로23길 55</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zJpfG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4994,22 +4942,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>384</v>
+        <v>54</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>389</v>
+        <v>54</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5018,17 +4966,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>35489351</t>
+          <t>1485867849</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35489351</t>
+          <t>https://m.place.naver.com/place/1485867849</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5040,29 +4988,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일뮤지엄</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>nail-museum@naver.com</t>
-        </is>
-      </c>
+          <t>블랑</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>070-7543-4009</t>
+          <t>02-790-8798</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail-museum</t>
+          <t>http://instagram.com/nailist_blanc</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5077,7 +5021,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5097,13 +5041,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>345</v>
+        <v>7</v>
       </c>
       <c r="Q50" t="n">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>705</v>
+        <v>8</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5112,17 +5056,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1881584782</t>
+          <t>909330706</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881584782</t>
+          <t>https://m.place.naver.com/place/909330706</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5134,29 +5078,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>우아엘뷰티</t>
+          <t>네일린</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>commathemoon_yongsan@naver.com</t>
+          <t>cookyismylife@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1379-1978</t>
+          <t>0507-1344-8515</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 147 2층</t>
+          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/commathemoon_yongsan</t>
+          <t>https://www.instagram.com/naileensalon</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5171,7 +5115,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5191,13 +5135,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5206,17 +5150,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1942029836</t>
+          <t>1996449351</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942029836</t>
+          <t>https://m.place.naver.com/place/1996449351</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5228,39 +5172,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>리네일</t>
+          <t>뷰리뉼레</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>dlwjddo7053@naver.com</t>
+          <t>kimnr123@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1421-7880</t>
+          <t>0507-1389-5562</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
+          <t>서울특별시 용산구 후암로 28 1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://instagram.com/ri_nail7877</t>
+          <t>https://toss.place/_lb/TYhSdSVIw</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5285,13 +5229,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>51</v>
+        <v>136</v>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R52" t="n">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5300,17 +5244,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>32244399</t>
+          <t>33277553</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32244399</t>
+          <t>https://m.place.naver.com/place/33277553</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5322,29 +5266,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>이촌동 네일타임 삼익상가</t>
+          <t>네일가꿈</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>yjk2650@naver.com</t>
+          <t>hyu3323@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>02-749-8604</t>
+          <t>0507-1403-8723</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://youtube.com/@ichon_nail_time</t>
+          <t>http://www.instagram.com/e_nailshop_sj</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5379,13 +5323,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>128</v>
+        <v>474</v>
       </c>
       <c r="Q53" t="n">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="R53" t="n">
-        <v>250</v>
+        <v>549</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5394,17 +5338,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1281193252</t>
+          <t>1966796864</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281193252</t>
+          <t>https://m.place.naver.com/place/1966796864</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5416,29 +5360,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>팝네일 신용산</t>
+          <t>쵸민네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mhhj951026@naver.com</t>
+          <t>sunday020@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1345-7477</t>
+          <t>0507-1403-3417</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
+          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/popnail_7477</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5448,7 +5392,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5464,22 +5408,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>363</v>
+        <v>2</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5488,17 +5432,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1306229960</t>
+          <t>1664663384</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306229960</t>
+          <t>https://m.place.naver.com/place/1664663384</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5510,25 +5454,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>우아한 네일 살롱</t>
+          <t>춘희손톱</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>findmyperfectdays@naver.com</t>
+          <t>chii0216@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1306-7521</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
+          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wooanail_salon</t>
+          <t>http://instagram.com/choonheenail</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5563,13 +5511,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>63</v>
+        <v>196</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="R55" t="n">
-        <v>64</v>
+        <v>295</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5578,17 +5526,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1370902820</t>
+          <t>20559743</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370902820</t>
+          <t>https://m.place.naver.com/place/20559743</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5600,25 +5548,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>살롱드다한</t>
+          <t>신용산네일라뜰리에왁싱</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ddalkong9830@naver.com</t>
+          <t>hee_1220@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1380-7730</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 257 2층</t>
+          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5653,13 +5605,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>282</v>
+        <v>2</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5668,17 +5620,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1917414808</t>
+          <t>1054108199</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917414808</t>
+          <t>https://m.place.naver.com/place/1054108199</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5690,24 +5642,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>리라네일</t>
+          <t>호박손톱</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kkmm_0707@naver.com</t>
+          <t>appealogad@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>02-703-4125</t>
+          <t>02-794-7958</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 23</t>
+          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5747,13 +5699,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5762,17 +5714,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1131445662</t>
+          <t>35927853</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131445662</t>
+          <t>https://m.place.naver.com/place/35927853</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5784,29 +5736,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>러블리핑크</t>
+          <t>봉선화물들이다</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kisever1@naver.com</t>
+          <t>s8h6y@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02-704-8470</t>
+          <t>02-6203-5478</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 27 2층</t>
+          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/s8h6y</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5816,12 +5768,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5837,17 +5789,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R58" t="n">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5856,17 +5808,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>36901322</t>
+          <t>33618035</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36901322</t>
+          <t>https://m.place.naver.com/place/33618035</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5878,29 +5830,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일노마드 용산푸르지오써밋점</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>kjr1212a@naver.com</t>
-        </is>
-      </c>
+          <t>위위즈 용산점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1310-3658</t>
+          <t>0507-1366-3547</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
+          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailnomad_</t>
+          <t>https://www.instagram.com/ouiouiznail</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5935,13 +5883,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="R59" t="n">
-        <v>479</v>
+        <v>542</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5950,17 +5898,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1841821386</t>
+          <t>1557214777</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1841821386</t>
+          <t>https://m.place.naver.com/place/1557214777</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5972,29 +5920,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>청담네일박스 용산점</t>
+          <t>켈리하우스 네일샵</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>smilehh406@naver.com</t>
+          <t>kellylove09@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1325-5985</t>
+          <t>0507-1393-9967</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
+          <t>서울특별시 용산구 보광로 49</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheongdam_nailbox</t>
+          <t>https://blog.naver.com/kellylove09</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6009,7 +5957,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6020,22 +5968,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6044,17 +5992,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2020464978</t>
+          <t>32875703</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020464978</t>
+          <t>https://m.place.naver.com/place/32875703</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6066,34 +6014,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>다교네일 한남</t>
+          <t>토마네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>oursophie@naver.com</t>
+          <t>yeoooey@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0507-1339-1024</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
+          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_VZqxfG/chat</t>
+          <t>https://www.instagram.com/to.ma.nail</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6114,7 +6058,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6123,13 +6067,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>338</v>
+        <v>123</v>
       </c>
       <c r="Q61" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="R61" t="n">
-        <v>374</v>
+        <v>130</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,17 +6082,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>37620988</t>
+          <t>1701565426</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37620988</t>
+          <t>https://m.place.naver.com/place/1701565426</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6160,29 +6104,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일래쉬</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>nailash@naver.com</t>
-        </is>
-      </c>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1371-0008</t>
+          <t>02-749-9134</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailash</t>
+          <t>http://www.instagram.com/vivinail</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6197,7 +6137,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6217,13 +6157,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>27</v>
+        <v>258</v>
       </c>
       <c r="Q62" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="R62" t="n">
-        <v>76</v>
+        <v>303</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,17 +6172,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1220901153</t>
+          <t>21834362</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220901153</t>
+          <t>https://m.place.naver.com/place/21834362</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6254,34 +6194,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>덴드네일한남</t>
+          <t>컬러테일러</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>eunii222@naver.com</t>
+          <t>ariarisom2@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0507-1378-0596</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
+          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eunii222</t>
+          <t>https://pf.kakao.com/_vpyXn</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6291,7 +6227,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6302,7 +6238,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6311,13 +6247,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>124</v>
+        <v>319</v>
       </c>
       <c r="Q63" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>146</v>
+        <v>321</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,17 +6262,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1108900148</t>
+          <t>1031854178</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108900148</t>
+          <t>https://m.place.naver.com/place/1031854178</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6348,29 +6284,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>또또네일</t>
+          <t>무구네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>clsald30@naver.com</t>
+          <t>mugunail2025@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1354-9049</t>
+          <t>0507-1353-2420</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 200 1층</t>
+          <t>서울특별시 용산구 새창로14길 46 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ttotto__nail</t>
+          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6405,13 +6341,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="Q64" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="R64" t="n">
-        <v>156</v>
+        <v>235</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,17 +6356,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2020672159</t>
+          <t>2093535455</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020672159</t>
+          <t>https://m.place.naver.com/place/2093535455</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6442,29 +6378,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>메종드로르</t>
+          <t>러블리핑크</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>stylechosun@naver.com</t>
+          <t>kisever1@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1386-1014</t>
+          <t>02-704-8470</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
+          <t>서울특별시 용산구 청파로45길 27 2층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6474,7 +6410,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6495,17 +6431,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6514,17 +6450,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2029580174</t>
+          <t>36901322</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029580174</t>
+          <t>https://m.place.naver.com/place/36901322</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6536,34 +6472,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>버들네일</t>
+          <t>네일셀레나</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>test_golry@naver.com</t>
+          <t>na_young03@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1400-7111</t>
+          <t>02-795-6529</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 147 1층</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b_d_nail</t>
+          <t>http://pf.kakao.com/_zJpfG</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6584,7 +6520,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6593,13 +6529,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>24</v>
+        <v>387</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R66" t="n">
-        <v>28</v>
+        <v>392</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,17 +6544,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1127614127</t>
+          <t>35489351</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127614127</t>
+          <t>https://m.place.naver.com/place/35489351</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6630,30 +6566,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>컬러테일러</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>ariarisom2@naver.com</t>
-        </is>
-      </c>
+          <t>또또네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1354-9049</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
+          <t>서울특별시 용산구 원효로 200 1층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_vpyXn</t>
+          <t>https://www.instagram.com/ttotto__nail</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6674,7 +6610,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6683,13 +6619,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>318</v>
+        <v>150</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R67" t="n">
-        <v>320</v>
+        <v>157</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6698,17 +6634,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1031854178</t>
+          <t>2020672159</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031854178</t>
+          <t>https://m.place.naver.com/place/2020672159</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6720,29 +6656,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일리모노 이태원점</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>nailremono@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1350-6775</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
+          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailremono</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6752,12 +6684,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6773,17 +6705,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>343</v>
+        <v>1</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6792,17 +6724,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1785734080</t>
+          <t>1222846707</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785734080</t>
+          <t>https://m.place.naver.com/place/1222846707</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6814,29 +6746,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일디렉터</t>
+          <t>네일퀸</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>naildirector@naver.com</t>
+          <t>kfreebaby@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>02-797-8188</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
+          <t>서울특별시 용산구 새창로14길 47</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naildirector</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6846,12 +6774,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6867,17 +6795,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>155</v>
+        <v>6</v>
       </c>
       <c r="Q69" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>166</v>
+        <v>7</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6886,17 +6814,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1487195546</t>
+          <t>1023738371</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487195546</t>
+          <t>https://m.place.naver.com/place/1023738371</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6908,29 +6836,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>수아르네일</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>xxong_11@naver.com</t>
-        </is>
-      </c>
+          <t>몽드메리</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1354-9689</t>
+          <t>0507-1382-2264</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
+          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/swa_rnail</t>
+          <t>https://www.instagram.com/monde.mery</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6965,13 +6889,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>11</v>
+        <v>761</v>
       </c>
       <c r="Q70" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="R70" t="n">
-        <v>14</v>
+        <v>775</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6980,17 +6904,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>21568200</t>
+          <t>1681006741</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21568200</t>
+          <t>https://m.place.naver.com/place/1681006741</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7002,29 +6926,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>팁셋 네일 한남점</t>
+          <t>레푸스 용산역점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>likelife_lovely@naver.com</t>
+          <t>refussyss@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1375-5705</t>
+          <t>0507-1417-1074</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
+          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tipset.seoul/</t>
+          <t>https://youtube.com/@레푸스용산역점</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7059,13 +6983,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>70</v>
+        <v>293</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>190</v>
       </c>
       <c r="R71" t="n">
-        <v>73</v>
+        <v>483</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7074,17 +6998,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1409853951</t>
+          <t>1153661148</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409853951</t>
+          <t>https://m.place.naver.com/place/1153661148</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7096,34 +7020,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>설화미</t>
+          <t>네일더누브</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>who1who2@naver.com</t>
+          <t>hasom0304@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1381-4227</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
+          <t>서울특별시 용산구 원효로 210 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sulwhami_beauty/</t>
+          <t>http://pf.kakao.com/_xdFnxhn</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7144,7 +7064,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7153,13 +7073,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="Q72" t="n">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="R72" t="n">
-        <v>342</v>
+        <v>131</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7168,17 +7088,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>33647337</t>
+          <t>1146800442</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33647337</t>
+          <t>https://m.place.naver.com/place/1146800442</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7190,25 +7110,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>데코네일</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>shwimlove@naver.com</t>
-        </is>
-      </c>
+          <t>더네일바 2호점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1411-8549</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
+          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
+          <t>http://www.instagram.com/thenailbar_hannam</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7243,13 +7163,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="Q73" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="R73" t="n">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7258,17 +7178,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>36812317</t>
+          <t>706072929</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36812317</t>
+          <t>https://m.place.naver.com/place/706072929</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7280,34 +7200,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>벨르네이쳐</t>
+          <t>비바이유 한남</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>dewsang@naver.com</t>
+          <t>enoctobre-@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1463-0395</t>
+          <t>0507-1371-9481</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
+          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pixftn/chat</t>
+          <t>https://www.instagram.com/b.by_you</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7328,7 +7248,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7337,13 +7257,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7352,17 +7272,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2043754067</t>
+          <t>2019591721</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043754067</t>
+          <t>https://m.place.naver.com/place/2019591721</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7374,29 +7294,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일헤라</t>
+          <t>네일테라피은</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jiyeon6305@naver.com</t>
+          <t>mountain__sun@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1334-2839</t>
+          <t>0507-1379-8496</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
+          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.hera</t>
+          <t>https://www.instagram.com/nailtherapyeun</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7431,13 +7351,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>203</v>
       </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R75" t="n">
-        <v>8</v>
+        <v>212</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7446,17 +7366,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1936017804</t>
+          <t>1180134699</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1936017804</t>
+          <t>https://m.place.naver.com/place/1180134699</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7468,34 +7388,30 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>신용산네일라뜰리에왁싱</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>hee_1220@naver.com</t>
-        </is>
-      </c>
+          <t>디에고푸스 희네일 이촌점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1380-7730</t>
+          <t>0507-1339-5732</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
+          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
+          <t>https://www.instagram.com/heenail4345</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7505,7 +7421,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7525,13 +7441,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="R76" t="n">
-        <v>2</v>
+        <v>157</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7540,17 +7456,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1054108199</t>
+          <t>1972424680</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054108199</t>
+          <t>https://m.place.naver.com/place/1972424680</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7562,34 +7478,34 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>네일가꿈</t>
+          <t>벨르네이쳐</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>hyu3323@naver.com</t>
+          <t>dewsang@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1403-8723</t>
+          <t>0507-1463-0395</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
+          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/e_nailshop_sj</t>
+          <t>http://pf.kakao.com/_pixftn/chat</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7610,7 +7526,7 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7619,13 +7535,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>474</v>
+        <v>57</v>
       </c>
       <c r="Q77" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="R77" t="n">
-        <v>549</v>
+        <v>65</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7634,17 +7550,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1966796864</t>
+          <t>2043754067</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966796864</t>
+          <t>https://m.place.naver.com/place/2043754067</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7656,35 +7572,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>재니네일한남</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>evian___@naver.com</t>
+          <t>jytgh@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1416-0638</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
+          <t>서울특별시 용산구 새창로 70 상가-210</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eKxmLxl</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7700,22 +7620,22 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="Q78" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="R78" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7724,17 +7644,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1593741438</t>
+          <t>36629016</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593741438</t>
+          <t>https://m.place.naver.com/place/36629016</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7746,29 +7666,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>유스뷰티</t>
+          <t>네일샵입니다</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jyrif91@naver.com</t>
+          <t>yooawo@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1422-3533</t>
+          <t>0507-1336-5457</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로20길 21 1층</t>
+          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youthnail/</t>
+          <t>https://www.instagram.com/shopnailshop/</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7803,13 +7723,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="Q79" t="n">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="R79" t="n">
-        <v>121</v>
+        <v>206</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7818,17 +7738,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>38467380</t>
+          <t>954197461</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38467380</t>
+          <t>https://m.place.naver.com/place/954197461</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7840,34 +7760,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>네일바이르레</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>l5v2osh@naver.com</t>
-        </is>
-      </c>
+          <t>쵸코네일</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1312-9470</t>
+          <t>02-749-7795</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
+          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_by_lerre</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7877,7 +7793,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7897,13 +7813,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="Q80" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R80" t="n">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7912,17 +7828,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>37818863</t>
+          <t>19490178</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37818863</t>
+          <t>https://m.place.naver.com/place/19490178</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7934,29 +7850,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>이앤앤</t>
+          <t>센스</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>eyennail@naver.com</t>
+          <t>showmblog@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>0507-1316-3771</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
+          <t>서울특별시 용산구 만리재로 140-1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_eyennail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7966,7 +7878,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7987,17 +7899,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>593</v>
+        <v>4</v>
       </c>
       <c r="Q81" t="n">
-        <v>1333</v>
+        <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>1926</v>
+        <v>6</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8006,17 +7918,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>375707328</t>
+          <t>1189922870</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/375707328</t>
+          <t>https://m.place.naver.com/place/1189922870</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8028,29 +7940,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>손톱의취향 용산푸르지오써밋점</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>tastein_nail_yongsan@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1483-0870</t>
+          <t>070-8882-4343</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
+          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taste_in_nail_</t>
+          <t>http://www.instagram.com/j_magic_nail</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8085,13 +7997,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="Q82" t="n">
-        <v>277</v>
+        <v>24</v>
       </c>
       <c r="R82" t="n">
-        <v>747</v>
+        <v>89</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8100,17 +8012,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2055593167</t>
+          <t>1438268528</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055593167</t>
+          <t>https://m.place.naver.com/place/1438268528</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8122,29 +8034,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>빛나러오소문제성발관리 용산점</t>
+          <t>네일리모노 이태원점</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>kknsky73@naver.com</t>
+          <t>nailremono@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1419-6888</t>
+          <t>0507-1350-6775</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
+          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://youtube.com/@user-gc4wk2yn2b</t>
+          <t>https://blog.naver.com/nailremono</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8159,7 +8071,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8170,7 +8082,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8179,13 +8091,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="Q83" t="n">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="R83" t="n">
-        <v>416</v>
+        <v>344</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8194,17 +8106,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1438224262</t>
+          <t>1785734080</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438224262</t>
+          <t>https://m.place.naver.com/place/1785734080</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8216,25 +8128,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>센스</t>
+          <t>네일의날씨</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>showmblog@naver.com</t>
+          <t>queen77577@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1430-0707</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 140-1</t>
+          <t>서울특별시 용산구 한강대로 288-2 1층</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_nalssi</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8244,7 +8160,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8260,22 +8176,22 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>4</v>
+        <v>497</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="R84" t="n">
-        <v>6</v>
+        <v>545</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8284,17 +8200,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1189922870</t>
+          <t>1050641028</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189922870</t>
+          <t>https://m.place.naver.com/place/1050641028</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8306,29 +8222,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>블랑</t>
+          <t>어서오손네일</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>hg6580@naver.com</t>
+          <t>funhanbro@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>02-790-8798</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
+          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailist_blanc</t>
+          <t>https://blog.naver.com/funhanbro</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8343,7 +8255,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8363,13 +8275,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R85" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8378,17 +8290,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>909330706</t>
+          <t>1030962704</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/909330706</t>
+          <t>https://m.place.naver.com/place/1030962704</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8400,29 +8312,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>정원네일</t>
+          <t>오나네일</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>wjsska1907@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0507-1406-7118</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
+          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>http://instagram.com/jungwon_nail_</t>
+          <t>https://www.instagram.com/o.nnail</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8457,13 +8365,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R86" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8472,17 +8380,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1935294802</t>
+          <t>1549497362</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935294802</t>
+          <t>https://m.place.naver.com/place/1549497362</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8494,29 +8402,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>레푸스 용산역점</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>refussyss@naver.com</t>
-        </is>
-      </c>
+          <t>오드리네일</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1417-1074</t>
+          <t>0507-1446-0227</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
+          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://youtube.com/@레푸스용산역점</t>
+          <t>https://www.instagram.com/oudreynail</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8551,13 +8455,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>291</v>
+        <v>29</v>
       </c>
       <c r="Q87" t="n">
-        <v>189</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>480</v>
+        <v>30</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8566,17 +8470,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1153661148</t>
+          <t>1497063684</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153661148</t>
+          <t>https://m.place.naver.com/place/1497063684</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8588,29 +8492,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>티아라네일어반스파</t>
+          <t>살롱드다한</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>esthii@naver.com</t>
+          <t>ddalkong9830@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>02-790-7882</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
+          <t>서울특별시 용산구 원효로 257 2층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8620,7 +8520,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8641,17 +8541,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>229</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R88" t="n">
-        <v>2</v>
+        <v>282</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8660,17 +8560,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>33213520</t>
+          <t>1917414808</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33213520</t>
+          <t>https://m.place.naver.com/place/1917414808</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8682,29 +8582,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>플로르 네일 이태원점</t>
+          <t>설화미</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>flornail@naver.com</t>
+          <t>who1who2@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>02-790-4182</t>
+          <t>0507-1381-4227</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로 47 4층</t>
+          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/flornail</t>
+          <t>https://www.instagram.com/sulwhami_beauty/</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8719,7 +8619,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8739,13 +8639,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="Q89" t="n">
-        <v>163</v>
+        <v>288</v>
       </c>
       <c r="R89" t="n">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8754,17 +8654,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>32435712</t>
+          <t>33647337</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32435712</t>
+          <t>https://m.place.naver.com/place/33647337</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8776,25 +8676,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>네일퀸</t>
+          <t>진주네 네일 효창공원점</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kfreebaby@naver.com</t>
+          <t>thwjd91070@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1403-6610</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 47</t>
+          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jinjunenail</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8804,7 +8708,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8825,17 +8729,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="R90" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8844,17 +8748,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1023738371</t>
+          <t>2056938739</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023738371</t>
+          <t>https://m.place.naver.com/place/2056938739</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8866,29 +8770,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>제이미 네일</t>
+          <t>네일헤라</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>see7833@naver.com</t>
+          <t>jiyeon6305@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>02-701-5602</t>
+          <t>0507-1334-2839</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
+          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail.hera</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8898,7 +8802,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8919,17 +8823,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R91" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8938,17 +8842,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>255540367</t>
+          <t>1936017804</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/255540367</t>
+          <t>https://m.place.naver.com/place/1936017804</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -8960,44 +8864,44 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>제이비풋 굳은살&amp;발톱 케어</t>
+          <t>반디인하우스 용산아이파크몰점</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>5cristal2@naver.com</t>
+          <t>bandinhouse_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>02-794-8551</t>
+          <t>0507-1472-1811</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
+          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9013,17 +8917,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>350</v>
+        <v>1249</v>
       </c>
       <c r="Q92" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="R92" t="n">
-        <v>529</v>
+        <v>1438</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9032,17 +8936,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>12791408</t>
+          <t>1049297184</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12791408</t>
+          <t>https://m.place.naver.com/place/1049297184</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9054,30 +8958,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>네일바래</t>
+          <t>루아드네일</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>naillab20@naver.com</t>
+          <t>sumr2002@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1452-9237</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 214-6 2층</t>
+          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailbarae_bboong</t>
+          <t>http://pf.kakao.com/_xoEbJn/friend</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9098,7 +9006,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9107,13 +9015,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="Q93" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R93" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9122,17 +9030,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>835341707</t>
+          <t>2003721483</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/835341707</t>
+          <t>https://m.place.naver.com/place/2003721483</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9144,29 +9052,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>손톱까끼</t>
+          <t>손톱의취향 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sinachoco@naver.com</t>
+          <t>tastein_nail_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1310-9297</t>
+          <t>0507-1483-0870</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kkakki_nail/</t>
+          <t>https://www.instagram.com/taste_in_nail_</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9201,13 +9109,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>49</v>
+        <v>475</v>
       </c>
       <c r="Q94" t="n">
-        <v>7</v>
+        <v>282</v>
       </c>
       <c r="R94" t="n">
-        <v>56</v>
+        <v>757</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9216,17 +9124,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>20939317</t>
+          <t>2055593167</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20939317</t>
+          <t>https://m.place.naver.com/place/2055593167</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9238,29 +9146,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>봉선화물들이다</t>
+          <t>네일바래</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>s8h6y@naver.com</t>
+          <t>naillab20@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>02-6203-5478</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
+          <t>서울특별시 용산구 원효로 214-6 2층</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s8h6y</t>
+          <t>http://www.instagram.com/nailbarae_bboong</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9275,7 +9179,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9295,13 +9199,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="Q95" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="R95" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9310,17 +9214,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>33618035</t>
+          <t>835341707</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33618035</t>
+          <t>https://m.place.naver.com/place/835341707</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9332,29 +9236,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>호박손톱</t>
+          <t>우아엘뷰티</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>bomi3692@naver.com</t>
+          <t>commathemoon_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>02-794-7958</t>
+          <t>0507-1379-1978</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
+          <t>서울특별시 용산구 효창원로 147 2층</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/commathemoon_yongsan</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9364,12 +9268,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9385,17 +9289,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="Q96" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="R96" t="n">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9404,17 +9308,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>35927853</t>
+          <t>1942029836</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35927853</t>
+          <t>https://m.place.naver.com/place/1942029836</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9426,29 +9330,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>루미가넷네일존 이마트 용산점</t>
+          <t>네일슈슈</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>hyer2986@naver.com</t>
+          <t>brilliant14694@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1401-9470</t>
+          <t>0507-1435-9113</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_chouchou_</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9458,7 +9362,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9479,17 +9383,17 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="Q97" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="R97" t="n">
-        <v>86</v>
+        <v>489</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9498,17 +9402,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1619342094</t>
+          <t>1185094311</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619342094</t>
+          <t>https://m.place.naver.com/place/1185094311</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9520,29 +9424,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>쵸민네일</t>
+          <t>헤더네일</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>sunday020@naver.com</t>
+          <t>mmmmbin@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1403-3417</t>
+          <t>0507-1464-8960</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/heathernail_102/</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9552,7 +9456,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9573,17 +9477,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Q98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9592,17 +9496,17 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1664663384</t>
+          <t>1399079243</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664663384</t>
+          <t>https://m.place.naver.com/place/1399079243</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9614,25 +9518,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>토마네일</t>
+          <t>코코루네일</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>yeoooey@naver.com</t>
+          <t>xanxixxanx@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1390-4270</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
+          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/to.ma.nail</t>
+          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9667,13 +9575,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="Q99" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R99" t="n">
-        <v>130</v>
+        <v>8</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9682,17 +9590,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1701565426</t>
+          <t>1768871817</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701565426</t>
+          <t>https://m.place.naver.com/place/1768871817</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9704,29 +9612,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>더네일바 2호점</t>
+          <t>버들네일</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>beczzam@naver.com</t>
+          <t>test_golry@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1411-8549</t>
+          <t>0507-1400-7111</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
+          <t>서울특별시 용산구 신흥로 147 1층</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/thenailbar_hannam</t>
+          <t>https://www.instagram.com/b_d_nail</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9761,13 +9669,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Q100" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9776,17 +9684,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>706072929</t>
+          <t>1127614127</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/706072929</t>
+          <t>https://m.place.naver.com/place/1127614127</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9798,29 +9706,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>켈리하우스 네일샵</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>kellylove09@naver.com</t>
-        </is>
-      </c>
+          <t>네일클로버</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>0507-1393-9967</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 49</t>
+          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kellylove09</t>
+          <t>http://instagram.com/nailclover_yongsan</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9835,7 +9735,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9851,17 +9751,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9870,17 +9770,17 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>32875703</t>
+          <t>32496791</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32875703</t>
+          <t>https://m.place.naver.com/place/32496791</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9892,25 +9792,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>오나네일</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>wjsska1907@naver.com</t>
-        </is>
-      </c>
+          <t>후암네일</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1301-4091</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
+          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/o.nnail</t>
+          <t>https://www.instagram.com/huam_nail</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9945,13 +9845,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="Q102" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9960,17 +9860,17 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1549497362</t>
+          <t>2033884779</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549497362</t>
+          <t>https://m.place.naver.com/place/2033884779</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -9982,29 +9882,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>비바이유 한남</t>
+          <t>프로네일</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>enoctobre-@naver.com</t>
+          <t>sonvely89@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0507-1371-9481</t>
+          <t>0507-1421-1525</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
+          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b.by_you</t>
+          <t>http://www.instagram.com/itaewonpronail/</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10039,13 +9939,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q103" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="R103" t="n">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10054,17 +9954,17 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>2019591721</t>
+          <t>13028002</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019591721</t>
+          <t>https://m.place.naver.com/place/13028002</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10076,29 +9976,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>루아드네일</t>
+          <t>클리피</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>sumr2002@naver.com</t>
+          <t>seoul2gun@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1452-9237</t>
+          <t>1855-4010</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
+          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xoEbJn/friend</t>
+          <t>http://pf.kakao.com/_txcJCb</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10133,13 +10033,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="Q104" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R104" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10148,17 +10048,17 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>2003721483</t>
+          <t>1546271749</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003721483</t>
+          <t>https://m.place.naver.com/place/1546271749</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10170,24 +10070,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>진유진네일</t>
+          <t>네일월드</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>seoul2816@naver.com</t>
+          <t>daisukitokyo@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1416-2081</t>
+          <t>02-715-9585</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 284</t>
+          <t>서울특별시 용산구 효창원로8길 6</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10227,13 +10127,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10242,17 +10142,17 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>31574498</t>
+          <t>1228817187</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31574498</t>
+          <t>https://m.place.naver.com/place/1228817187</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10264,12 +10164,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>붙여핸썹</t>
+          <t>재니네일한남</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>woowim@naver.com</t>
+          <t>evian___@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -10277,22 +10177,22 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
+          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_eKxmLxl</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -10308,22 +10208,22 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10332,17 +10232,17 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1333965738</t>
+          <t>1593741438</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333965738</t>
+          <t>https://m.place.naver.com/place/1593741438</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10354,29 +10254,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
+          <t>우아한 네일 살롱</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>tlstnals1010@naver.com</t>
+          <t>findmyperfectdays@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>070-8882-4343</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/j_magic_nail</t>
+          <t>https://www.instagram.com/wooanail_salon</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10411,13 +10307,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q107" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10426,17 +10322,17 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1438268528</t>
+          <t>1370902820</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438268528</t>
+          <t>https://m.place.naver.com/place/1370902820</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10448,29 +10344,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>프로네일</t>
+          <t>빛나러오소문제성발관리 용산점</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>sonvely89@naver.com</t>
+          <t>kknsky73@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0507-1421-1525</t>
+          <t>0507-1419-6888</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
+          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/itaewonpronail/</t>
+          <t>https://youtube.com/@user-gc4wk2yn2b</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10496,7 +10392,7 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -10505,13 +10401,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="Q108" t="n">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="R108" t="n">
-        <v>111</v>
+        <v>416</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10520,17 +10416,17 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>13028002</t>
+          <t>1438224262</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13028002</t>
+          <t>https://m.place.naver.com/place/1438224262</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10542,20 +10438,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
+          <t>네일꾼</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>tlstnals1010@naver.com</t>
+          <t>jinheeloo@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0507-1407-8585</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
+          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10595,13 +10495,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q109" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="R109" t="n">
-        <v>1</v>
+        <v>162</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10610,17 +10510,17 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1222846707</t>
+          <t>1395413071</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222846707</t>
+          <t>https://m.place.naver.com/place/1395413071</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10632,29 +10532,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>오손내미오</t>
+          <t>붙여핸썹</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>playnauts@naver.com</t>
+          <t>woowim@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0507-1492-1340</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
+          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oh_sonemio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -10664,7 +10560,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -10685,17 +10581,17 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10704,17 +10600,17 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1311070929</t>
+          <t>1333965738</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311070929</t>
+          <t>https://m.place.naver.com/place/1333965738</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10726,29 +10622,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>네일테라피은</t>
+          <t>이앤앤</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>mountain__sun@naver.com</t>
+          <t>eyennail@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1379-8496</t>
+          <t>0507-1316-3771</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
+          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailtherapyeun</t>
+          <t>http://www.instagram.com/_eyennail_</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10783,13 +10679,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>203</v>
+        <v>594</v>
       </c>
       <c r="Q111" t="n">
-        <v>9</v>
+        <v>1334</v>
       </c>
       <c r="R111" t="n">
-        <v>212</v>
+        <v>1928</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10798,17 +10694,17 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1180134699</t>
+          <t>375707328</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180134699</t>
+          <t>https://m.place.naver.com/place/375707328</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10820,25 +10716,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>네일바라기</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>sydy8585@naver.com</t>
-        </is>
-      </c>
+          <t>네일프롬다니</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1349-9460</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
+          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_baragi_</t>
+          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10873,13 +10769,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="Q112" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10888,17 +10784,17 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1091743517</t>
+          <t>1774853191</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091743517</t>
+          <t>https://m.place.naver.com/place/1774853191</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -10910,25 +10806,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>더 트리니티 네일</t>
+          <t>팁셋 네일 한남점</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>dlfnfl0129@naver.com</t>
+          <t>likelife_lovely@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0507-1375-5705</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
+          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the_trinity_nail/</t>
+          <t>https://www.instagram.com/tipset.seoul/</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10963,13 +10863,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q113" t="n">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="R113" t="n">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10978,17 +10878,17 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1060176123</t>
+          <t>1409853951</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060176123</t>
+          <t>https://m.place.naver.com/place/1409853951</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -11000,25 +10900,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>수 네일</t>
+          <t>Breathnailz</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>qkrqhrdfrn@naver.com</t>
+          <t>mooisu@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0507-1358-6853</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 196 B1층</t>
+          <t>서울특별시 용산구 소월로20길 36 1층</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qkrqhrdfrn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11028,12 +10932,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -11044,22 +10948,22 @@
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11068,17 +10972,17 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1989007422</t>
+          <t>1488241394</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989007422</t>
+          <t>https://m.place.naver.com/place/1488241394</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -11090,29 +10994,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>몽드메리</t>
+          <t>팝네일 신용산</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>happygirl223@naver.com</t>
+          <t>mhhj951026@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0507-1382-2264</t>
+          <t>0507-1345-7477</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
+          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/monde.mery</t>
+          <t>https://www.instagram.com/popnail_7477</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11138,7 +11042,7 @@
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -11147,13 +11051,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>759</v>
+        <v>316</v>
       </c>
       <c r="Q115" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="R115" t="n">
-        <v>773</v>
+        <v>363</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11162,17 +11066,17 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1681006741</t>
+          <t>1306229960</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681006741</t>
+          <t>https://m.place.naver.com/place/1306229960</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -11184,29 +11088,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>헤더네일</t>
+          <t>오렌지나무</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>mmmmbin@naver.com</t>
+          <t>dew517@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1464-8960</t>
+          <t>0507-1323-2154</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
+          <t>서울특별시 용산구 한남대로20길 13 1층</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heathernail_102/</t>
+          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11241,13 +11145,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="Q116" t="n">
         <v>2</v>
       </c>
       <c r="R116" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11256,17 +11160,17 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>1399079243</t>
+          <t>1568164546</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399079243</t>
+          <t>https://m.place.naver.com/place/1568164546</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -11278,39 +11182,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>클리피</t>
+          <t>진유진네일</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>seoul2gun@naver.com</t>
+          <t>seoul2816@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1855-4010</t>
+          <t>0507-1416-2081</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
+          <t>서울특별시 용산구 한강대로 284</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_txcJCb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -11326,22 +11230,22 @@
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="Q117" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="R117" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11350,17 +11254,17 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>1546271749</t>
+          <t>31574498</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546271749</t>
+          <t>https://m.place.naver.com/place/31574498</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/용산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/용산_네일샵.xlsx
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리라네일</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kkmm_0707@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>02-703-4125</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 23</t>
+          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nailclover_yongsan</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +592,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +613,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +632,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1131445662</t>
+          <t>32496791</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131445662</t>
+          <t>https://m.place.naver.com/place/32496791</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>티아라네일어반스파</t>
+          <t>신용산네일라뜰리에왁싱</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>esthii@naver.com</t>
+          <t>hee_1220@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02-790-7882</t>
+          <t>0507-1380-7730</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
+          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,14 +707,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>2</v>
@@ -730,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>33213520</t>
+          <t>1054108199</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33213520</t>
+          <t>https://m.place.naver.com/place/1054108199</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +748,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>j2lang@naver.com</t>
-        </is>
-      </c>
+          <t>네일테라피은</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1345-4179</t>
+          <t>0507-1379-8496</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
+          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/today_nail_ichon</t>
+          <t>https://www.instagram.com/nailtherapyeun</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>293</v>
+        <v>203</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>300</v>
+        <v>212</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +816,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>21038031</t>
+          <t>1180134699</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21038031</t>
+          <t>https://m.place.naver.com/place/1180134699</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +838,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>루미가넷네일존 이마트 용산점</t>
+          <t>수 네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hyer2986@naver.com</t>
+          <t>qkrqhrdfrn@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1401-9470</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
+          <t>서울특별시 용산구 만리재로 196 B1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/qkrqhrdfrn</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +866,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,22 +882,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +906,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1619342094</t>
+          <t>1989007422</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619342094</t>
+          <t>https://m.place.naver.com/place/1989007422</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +928,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>제이비풋 굳은살&amp;발톱 케어</t>
+          <t>더네일바 2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sunny_0225@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02-794-8551</t>
+          <t>0507-1411-8549</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
+          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/thenailbar_hannam</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +960,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,17 +981,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>351</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="R6" t="n">
-        <v>530</v>
+        <v>94</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1000,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>12791408</t>
+          <t>706072929</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12791408</t>
+          <t>https://m.place.naver.com/place/706072929</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,30 +1022,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>묘즈네일</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>xoxobloggirl@naver.com</t>
-        </is>
-      </c>
+          <t>바림</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>02-318-2055</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
+          <t>서울특별시 용산구 두텁바위로 73</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WxedxgG</t>
+          <t>http://instagram.com/Barim_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1078,7 +1066,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1075,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1090,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1136869573</t>
+          <t>1862156671</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136869573</t>
+          <t>https://m.place.naver.com/place/1862156671</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1119,39 +1107,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>네일아트재료</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일뮤지엄</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>nail-museum@naver.com</t>
-        </is>
-      </c>
+          <t>메이크케이</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>070-7543-4009</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
+          <t>서울특별시 용산구 청파로47길 56 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail-museum</t>
+          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1181,13 +1161,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1176,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1881584782</t>
+          <t>2081839313</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881584782</t>
+          <t>https://m.place.naver.com/place/2081839313</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1218,29 +1198,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제이제이 네일</t>
+          <t>글로시블라썸 아이파크몰</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>irumskin@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1411-8138</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 회나무로 32-3 2층</t>
+          <t>서울특별시 용산구 한강대로23길 55</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjjjnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,7 +1226,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1271,17 +1247,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1266,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>79017915</t>
+          <t>1485867849</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/79017915</t>
+          <t>https://m.place.naver.com/place/1485867849</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1312,30 +1288,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>데코네일</t>
+          <t>반디인하우스 용산아이파크몰점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bambi_showpu@naver.com</t>
+          <t>bandinhouse_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1472-1811</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
+          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
+          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1345,7 +1325,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1345,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>41</v>
+        <v>1249</v>
       </c>
       <c r="Q10" t="n">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="R10" t="n">
-        <v>123</v>
+        <v>1438</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1360,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36812317</t>
+          <t>1049297184</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36812317</t>
+          <t>https://m.place.naver.com/place/1049297184</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,29 +1382,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>이촌동 네일타임 삼익상가</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yjk2650@naver.com</t>
-        </is>
-      </c>
+          <t>러블리핑크</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-749-8604</t>
+          <t>02-704-8470</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
+          <t>서울특별시 용산구 청파로45길 27 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://youtube.com/@ichon_nail_time</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1434,7 +1410,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1455,17 +1431,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1450,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1281193252</t>
+          <t>36901322</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281193252</t>
+          <t>https://m.place.naver.com/place/36901322</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1496,26 +1472,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일드모네</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>쿠로키네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>vin2roo@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1481-2893</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 67 206호</t>
+          <t>서울특별시 용산구 신흥로 19-2 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildemonet</t>
+          <t>https://pf.kakao.com/_xaxcxeBG</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1536,7 +1520,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1545,13 +1529,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1560,12 +1544,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2062875678</t>
+          <t>1723956505</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2062875678</t>
+          <t>https://m.place.naver.com/place/1723956505</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1582,29 +1566,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>오손내미오</t>
+          <t>이촌 네일타임 LG프라자</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>playnauts@naver.com</t>
+          <t>blingsea@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1492-1340</t>
+          <t>0507-1498-8612</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
+          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oh_sonemio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1614,7 +1598,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1635,17 +1619,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1654,12 +1638,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1311070929</t>
+          <t>20064911</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311070929</t>
+          <t>https://m.place.naver.com/place/20064911</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1676,29 +1660,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>카밍네일</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>daisoblog@naver.com</t>
-        </is>
-      </c>
+          <t>아로하네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1357-1496</t>
+          <t>0507-1391-4369</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 42 1층</t>
+          <t>서울특별시 용산구 이태원로14길 10 2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/calming_nail</t>
+          <t>http://www.instagram.com/alohanail_chae</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1733,13 +1713,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1748,12 +1728,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1383549813</t>
+          <t>1264306160</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383549813</t>
+          <t>https://m.place.naver.com/place/1264306160</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1765,35 +1745,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>네일아트재료</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>메이크케이</t>
+          <t>빛나러오소문제성발관리 용산점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kbanknow@naver.com</t>
+          <t>kknsky73@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1419-6888</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 56 1층</t>
+          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
+          <t>https://youtube.com/@user-gc4wk2yn2b</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1803,7 +1787,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1814,7 +1798,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1823,13 +1807,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1838,12 +1822,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2081839313</t>
+          <t>1438224262</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2081839313</t>
+          <t>https://m.place.naver.com/place/1438224262</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1860,29 +1844,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>투투네일</t>
+          <t>유스뷰티</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>jyrif91@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1336-4546</t>
+          <t>0507-1422-3533</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
+          <t>서울특별시 용산구 이태원로20길 21 1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/twotwo_nail</t>
+          <t>https://www.instagram.com/youthnail/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1917,13 +1901,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="R16" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1932,12 +1916,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1253759614</t>
+          <t>38467380</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253759614</t>
+          <t>https://m.place.naver.com/place/38467380</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1954,29 +1938,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>리네일</t>
+          <t>네일헤라</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dlwjddo7053@naver.com</t>
+          <t>jiyeon6305@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1421-7880</t>
+          <t>0507-1334-2839</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
+          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://instagram.com/ri_nail7877</t>
+          <t>http://instagram.com/nail.hera</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2011,13 +1995,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2026,12 +2010,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>32244399</t>
+          <t>1936017804</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32244399</t>
+          <t>https://m.place.naver.com/place/1936017804</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2048,30 +2032,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>더 트리니티 네일</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>dlfnfl0129@naver.com</t>
-        </is>
-      </c>
+          <t>다교네일 한남</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1339-1024</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the_trinity_nail/</t>
+          <t>http://pf.kakao.com/_VZqxfG/chat</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2092,7 +2076,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2101,13 +2085,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>59</v>
+        <v>338</v>
       </c>
       <c r="Q18" t="n">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="R18" t="n">
-        <v>157</v>
+        <v>374</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2116,12 +2100,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1060176123</t>
+          <t>37620988</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060176123</t>
+          <t>https://m.place.naver.com/place/37620988</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2138,25 +2122,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>청담네일박스 용산점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>오늘도네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>j2lang@naver.com</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1325-5985</t>
+          <t>0507-1345-4179</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
+          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheongdam_nailbox</t>
+          <t>http://instagram.com/today_nail_ichon</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2182,7 +2170,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2191,13 +2179,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>293</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2206,12 +2194,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2020464978</t>
+          <t>21038031</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020464978</t>
+          <t>https://m.place.naver.com/place/21038031</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2228,34 +2216,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>손톱까끼</t>
+          <t>재니네일한남</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sinachoco@naver.com</t>
+          <t>evian___@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1310-9297</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
+          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kkakki_nail/</t>
+          <t>http://pf.kakao.com/_eKxmLxl</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2276,7 +2260,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2285,13 +2269,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="R20" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2300,12 +2284,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>20939317</t>
+          <t>1593741438</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20939317</t>
+          <t>https://m.place.naver.com/place/1593741438</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2322,25 +2306,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>마틸다네일M 한남점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>이앤앤</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>eyennail@naver.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1412-3082</t>
+          <t>0507-1316-3771</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
+          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://matildanailshop-mo3.imweb.me/</t>
+          <t>http://www.instagram.com/_eyennail_</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2355,7 +2343,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2375,13 +2363,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>92</v>
+        <v>594</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>1334</v>
       </c>
       <c r="R21" t="n">
-        <v>111</v>
+        <v>1928</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2390,12 +2378,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1798849933</t>
+          <t>375707328</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798849933</t>
+          <t>https://m.place.naver.com/place/375707328</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2412,25 +2400,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>플리네일 용산해링턴점</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>네일삼각지</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>nailsamgakji@naver.com</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1406-7552</t>
+          <t>0507-1316-2792</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
+          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_samgakji</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2456,7 +2448,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2465,13 +2457,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>438</v>
+        <v>17</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>453</v>
+        <v>22</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2480,12 +2472,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2075608465</t>
+          <t>1872968588</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075608465</t>
+          <t>https://m.place.naver.com/place/1872968588</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2502,30 +2494,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>바림</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>카밍네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>daisoblog@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>02-318-2055</t>
+          <t>0507-1357-1496</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로 73</t>
+          <t>서울특별시 용산구 소월로20길 42 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://instagram.com/Barim_nail</t>
+          <t>https://www.instagram.com/calming_nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2535,7 +2531,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2555,13 +2551,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="R23" t="n">
-        <v>13</v>
+        <v>192</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2570,12 +2566,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1862156671</t>
+          <t>1383549813</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862156671</t>
+          <t>https://m.place.naver.com/place/1383549813</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2592,29 +2588,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>정원네일</t>
+          <t>헤더네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>pretty6144@naver.com</t>
+          <t>mmmmbin@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1406-7118</t>
+          <t>0507-1464-8960</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://instagram.com/jungwon_nail_</t>
+          <t>https://www.instagram.com/heathernail_102/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2649,13 +2645,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2664,12 +2660,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1935294802</t>
+          <t>1399079243</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935294802</t>
+          <t>https://m.place.naver.com/place/1399079243</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2686,29 +2682,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>제이미 네일</t>
+          <t>플로르 네일 이태원점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>see7833@naver.com</t>
+          <t>flornail@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-701-5602</t>
+          <t>02-790-4182</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
+          <t>서울특별시 용산구 우사단로 47 4층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/flornail</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2718,12 +2714,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2739,17 +2735,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="R25" t="n">
-        <v>31</v>
+        <v>280</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2758,12 +2754,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>255540367</t>
+          <t>32435712</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/255540367</t>
+          <t>https://m.place.naver.com/place/32435712</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2780,20 +2776,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일샵베이비</t>
+          <t>네일월드</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1396-4649</t>
+          <t>02-715-9585</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로2길 19 1층</t>
+          <t>서울특별시 용산구 효창원로8길 6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2833,13 +2829,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2848,12 +2844,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1847608869</t>
+          <t>1228817187</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847608869</t>
+          <t>https://m.place.naver.com/place/1228817187</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2870,20 +2866,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>신데렐라</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>네일퀸</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>kfreebaby@naver.com</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>02-790-3304</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 61</t>
+          <t>서울특별시 용산구 새창로14길 47</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2923,13 +2919,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2938,12 +2934,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>20662540</t>
+          <t>1023738371</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20662540</t>
+          <t>https://m.place.naver.com/place/1023738371</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2960,29 +2956,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일디렉터</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>naildirector@naver.com</t>
-        </is>
-      </c>
+          <t>후암네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02-797-8188</t>
+          <t>0507-1301-4091</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
+          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naildirector</t>
+          <t>https://www.instagram.com/huam_nail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2997,7 +2989,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3017,13 +3009,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3032,12 +3024,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1487195546</t>
+          <t>2033884779</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487195546</t>
+          <t>https://m.place.naver.com/place/2033884779</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3054,29 +3046,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일래쉬</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>nailash@naver.com</t>
-        </is>
-      </c>
+          <t>쵸민네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1371-0008</t>
+          <t>0507-1403-3417</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
+          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailash</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3086,12 +3074,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3107,17 +3095,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3126,12 +3114,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1220901153</t>
+          <t>1664663384</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220901153</t>
+          <t>https://m.place.naver.com/place/1664663384</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3148,29 +3136,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일삼각지</t>
+          <t>네일바이르레</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nailsamgakji@naver.com</t>
+          <t>l5v2osh@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1316-2792</t>
+          <t>0507-1312-9470</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
+          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_samgakji</t>
+          <t>http://www.instagram.com/nail_by_lerre</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3196,7 +3184,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3205,13 +3193,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3220,12 +3208,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1872968588</t>
+          <t>37818863</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1872968588</t>
+          <t>https://m.place.naver.com/place/37818863</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3242,21 +3230,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아드</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>블랑</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>hg6580@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>02-790-8798</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.th_kr</t>
+          <t>http://instagram.com/nailist_blanc</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3291,13 +3287,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3306,12 +3302,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1700535825</t>
+          <t>909330706</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700535825</t>
+          <t>https://m.place.naver.com/place/909330706</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3328,25 +3324,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>유스뷰티</t>
+          <t>티아라네일어반스파</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1422-3533</t>
+          <t>02-790-7882</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로20길 21 1층</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youthnail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3356,7 +3352,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3377,17 +3373,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3396,12 +3392,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>38467380</t>
+          <t>33213520</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38467380</t>
+          <t>https://m.place.naver.com/place/33213520</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3418,35 +3414,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>마고뷰티</t>
+          <t>호박손톱</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mago_smp@naver.com</t>
+          <t>appealogad@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>02-794-7958</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
+          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xjBnAn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3462,22 +3462,22 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="Q33" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="R33" t="n">
-        <v>155</v>
+        <v>30</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3486,12 +3486,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1939429266</t>
+          <t>35927853</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939429266</t>
+          <t>https://m.place.naver.com/place/35927853</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3508,34 +3508,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>아로하네일</t>
+          <t>마고뷰티</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>bbotive@naver.com</t>
+          <t>mago_smp@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1391-4369</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로14길 10 2층</t>
+          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/alohanail_chae</t>
+          <t>https://pf.kakao.com/_xjBnAn</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3556,7 +3552,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3565,13 +3561,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="R34" t="n">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3580,12 +3576,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1264306160</t>
+          <t>1939429266</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264306160</t>
+          <t>https://m.place.naver.com/place/1939429266</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3602,24 +3598,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>에일린</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>myungae7@naver.com</t>
-        </is>
-      </c>
+          <t>제이비풋 굳은살&amp;발톱 케어</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1445-2816</t>
+          <t>02-794-8551</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3659,13 +3651,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>393</v>
+        <v>351</v>
       </c>
       <c r="Q35" t="n">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="R35" t="n">
-        <v>471</v>
+        <v>530</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3674,12 +3666,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1447531035</t>
+          <t>12791408</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447531035</t>
+          <t>https://m.place.naver.com/place/12791408</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3696,29 +3688,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>수아르네일</t>
+          <t>오나네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>xxong_11@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0507-1354-9689</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
+          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/swa_rnail</t>
+          <t>https://www.instagram.com/o.nnail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3753,13 +3741,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="R36" t="n">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3768,12 +3756,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>21568200</t>
+          <t>1549497362</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21568200</t>
+          <t>https://m.place.naver.com/place/1549497362</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3790,29 +3778,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>메종드로르</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>stylechosun@naver.com</t>
-        </is>
-      </c>
+          <t>네일꾼</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1386-1014</t>
+          <t>0507-1407-8585</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
+          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3822,7 +3806,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3843,17 +3827,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="R37" t="n">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3862,12 +3846,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2029580174</t>
+          <t>1395413071</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029580174</t>
+          <t>https://m.place.naver.com/place/1395413071</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3884,25 +3868,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>이촌 네일타임 LG프라자</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>더 트리니티 네일</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dlfnfl0129@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0507-1498-8612</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
+          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/the_trinity_nail/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3912,7 +3896,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3933,17 +3917,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="R38" t="n">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3952,12 +3936,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>20064911</t>
+          <t>1060176123</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20064911</t>
+          <t>https://m.place.naver.com/place/1060176123</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3974,25 +3958,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>수 네일</t>
+          <t>또또네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>qkrqhrdfrn@naver.com</t>
+          <t>clsald30@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1354-9049</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 196 B1층</t>
+          <t>서울특별시 용산구 원효로 200 1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qkrqhrdfrn</t>
+          <t>https://www.instagram.com/ttotto__nail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4007,7 +3995,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4018,7 +4006,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4027,13 +4015,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4042,12 +4030,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1989007422</t>
+          <t>2020672159</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989007422</t>
+          <t>https://m.place.naver.com/place/2020672159</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4064,34 +4052,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>쿠로키네일</t>
+          <t>네일스눕</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>yseaeaho@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1481-2893</t>
+          <t>0507-1428-1646</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 19-2 1층</t>
+          <t>서울특별시 용산구 한강대로52길 38 202호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xaxcxeBG</t>
+          <t>https://www.instagram.com/nail_snoope</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4112,7 +4100,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4121,13 +4109,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R40" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4136,12 +4124,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1723956505</t>
+          <t>1926501985</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723956505</t>
+          <t>https://m.place.naver.com/place/1926501985</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4158,29 +4146,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일바이르레</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>l5v2osh@naver.com</t>
-        </is>
-      </c>
+          <t>네일샵입니다</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1312-9470</t>
+          <t>0507-1336-5457</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
+          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_by_lerre</t>
+          <t>https://www.instagram.com/shopnailshop/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4215,13 +4199,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="R41" t="n">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4230,12 +4214,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>37818863</t>
+          <t>954197461</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37818863</t>
+          <t>https://m.place.naver.com/place/954197461</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4252,29 +4236,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>덴드네일한남</t>
+          <t>정원네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>eunii222@naver.com</t>
+          <t>pretty6144@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1378-0596</t>
+          <t>0507-1406-7118</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
+          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eunii222</t>
+          <t>http://instagram.com/jungwon_nail_</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4289,7 +4273,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4309,13 +4293,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4324,12 +4308,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1108900148</t>
+          <t>1935294802</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108900148</t>
+          <t>https://m.place.naver.com/place/1935294802</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4346,29 +4330,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일스눕</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>yseaeaho@naver.com</t>
-        </is>
-      </c>
+          <t>프로네일</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1428-1646</t>
+          <t>0507-1421-1525</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로52길 38 202호</t>
+          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_snoope</t>
+          <t>http://www.instagram.com/itaewonpronail/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4403,13 +4383,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="R43" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4418,12 +4398,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1926501985</t>
+          <t>13028002</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926501985</t>
+          <t>https://m.place.naver.com/place/13028002</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4440,29 +4420,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>플로르 네일 이태원점</t>
+          <t>켈리하우스 네일샵</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>flornail@naver.com</t>
+          <t>kellylove09@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>02-790-4182</t>
+          <t>0507-1393-9967</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로 47 4층</t>
+          <t>서울특별시 용산구 보광로 49</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/flornail</t>
+          <t>https://blog.naver.com/kellylove09</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4493,17 +4473,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="Q44" t="n">
-        <v>163</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>280</v>
+        <v>12</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4512,12 +4492,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>32435712</t>
+          <t>32875703</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32435712</t>
+          <t>https://m.place.naver.com/place/32875703</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4534,24 +4514,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일휴</t>
+          <t>신데렐라</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>white5198@naver.com</t>
+          <t>dracura10@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>02-711-3646</t>
+          <t>02-790-3304</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
+          <t>서울특별시 용산구 보광로 61</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4591,13 +4571,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
         <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4606,12 +4586,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1611951357</t>
+          <t>20662540</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611951357</t>
+          <t>https://m.place.naver.com/place/20662540</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4628,25 +4608,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일바라기</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>sydy8585@naver.com</t>
-        </is>
-      </c>
+          <t>네일샵베이비</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1396-4649</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
+          <t>서울특별시 용산구 우사단로2길 19 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_baragi_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4656,7 +4636,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4677,17 +4657,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4696,12 +4676,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1091743517</t>
+          <t>1847608869</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091743517</t>
+          <t>https://m.place.naver.com/place/1847608869</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4718,35 +4698,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>다교네일 한남</t>
+          <t>에일린</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1339-1024</t>
+          <t>0507-1445-2816</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
+          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_VZqxfG/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4762,22 +4742,22 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="R47" t="n">
-        <v>374</v>
+        <v>471</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4786,12 +4766,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>37620988</t>
+          <t>1447531035</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37620988</t>
+          <t>https://m.place.naver.com/place/1447531035</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4808,29 +4788,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일노마드 용산푸르지오써밋점</t>
+          <t>어서오손네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kjr1212a@naver.com</t>
+          <t>funhanbro@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1310-3658</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
+          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailnomad_</t>
+          <t>https://blog.naver.com/funhanbro</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4845,7 +4821,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4865,13 +4841,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>471</v>
+        <v>11</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R48" t="n">
-        <v>479</v>
+        <v>23</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4880,12 +4856,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1841821386</t>
+          <t>1030962704</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1841821386</t>
+          <t>https://m.place.naver.com/place/1030962704</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4902,21 +4878,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>글로시블라썸 아이파크몰</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>춘희손톱</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>chii0216@naver.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1306-7521</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55</t>
+          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/choonheenail</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4926,7 +4910,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4947,17 +4931,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>54</v>
+        <v>196</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="R49" t="n">
-        <v>54</v>
+        <v>295</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4966,12 +4950,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1485867849</t>
+          <t>20559743</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485867849</t>
+          <t>https://m.place.naver.com/place/20559743</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4988,25 +4972,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>블랑</t>
+          <t>네일바라기</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>02-790-8798</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
+          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailist_blanc</t>
+          <t>http://instagram.com/nail_baragi_</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5041,13 +5021,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R50" t="n">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5056,12 +5036,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>909330706</t>
+          <t>1091743517</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/909330706</t>
+          <t>https://m.place.naver.com/place/1091743517</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5078,29 +5058,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일린</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>cookyismylife@naver.com</t>
-        </is>
-      </c>
+          <t>코코루네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1344-8515</t>
+          <t>0507-1390-4270</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
+          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naileensalon</t>
+          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5135,13 +5111,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5150,12 +5126,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1996449351</t>
+          <t>1768871817</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996449351</t>
+          <t>https://m.place.naver.com/place/1768871817</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5172,29 +5148,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>뷰리뉼레</t>
+          <t>네일더누브</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kimnr123@naver.com</t>
+          <t>hasom0304@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0507-1389-5562</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 후암로 28 1층</t>
+          <t>서울특별시 용산구 원효로 210 1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYhSdSVIw</t>
+          <t>http://pf.kakao.com/_xdFnxhn</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5204,7 +5176,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5220,7 +5192,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5229,13 +5201,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="Q52" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="R52" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5244,12 +5216,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>33277553</t>
+          <t>1146800442</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33277553</t>
+          <t>https://m.place.naver.com/place/1146800442</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5266,29 +5238,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일가꿈</t>
+          <t>오드리네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>hyu3323@naver.com</t>
+          <t>ardusy@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1403-8723</t>
+          <t>0507-1446-0227</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
+          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/e_nailshop_sj</t>
+          <t>https://www.instagram.com/oudreynail</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5323,13 +5295,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>474</v>
+        <v>29</v>
       </c>
       <c r="Q53" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>549</v>
+        <v>30</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5338,12 +5310,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1966796864</t>
+          <t>1497063684</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966796864</t>
+          <t>https://m.place.naver.com/place/1497063684</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5360,29 +5332,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>쵸민네일</t>
+          <t>오렌지나무</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sunday020@naver.com</t>
+          <t>dew517@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1403-3417</t>
+          <t>0507-1323-2154</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
+          <t>서울특별시 용산구 한남대로20길 13 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5392,7 +5364,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5413,17 +5385,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5432,12 +5404,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1664663384</t>
+          <t>1568164546</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664663384</t>
+          <t>https://m.place.naver.com/place/1568164546</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5454,29 +5426,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>춘희손톱</t>
+          <t>네일리모노 이태원점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>chii0216@naver.com</t>
+          <t>nailremono@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1306-7521</t>
+          <t>0507-1350-6775</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
+          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://instagram.com/choonheenail</t>
+          <t>https://blog.naver.com/nailremono</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5491,7 +5463,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5511,13 +5483,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>196</v>
+        <v>325</v>
       </c>
       <c r="Q55" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="R55" t="n">
-        <v>295</v>
+        <v>344</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5526,12 +5498,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>20559743</t>
+          <t>1785734080</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20559743</t>
+          <t>https://m.place.naver.com/place/1785734080</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5548,29 +5520,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>신용산네일라뜰리에왁싱</t>
+          <t>메종드로르</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>hee_1220@naver.com</t>
+          <t>stylechosun@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1380-7730</t>
+          <t>0507-1386-1014</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
+          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
+          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5605,13 +5577,13 @@
         </is>
       </c>
       <c r="P56" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>2</v>
-      </c>
       <c r="R56" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5620,12 +5592,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1054108199</t>
+          <t>2029580174</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054108199</t>
+          <t>https://m.place.naver.com/place/2029580174</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5642,29 +5614,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>호박손톱</t>
+          <t>버들네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>appealogad@naver.com</t>
+          <t>test_golry@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>02-794-7958</t>
+          <t>0507-1400-7111</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
+          <t>서울특별시 용산구 신흥로 147 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/b_d_nail</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5674,7 +5646,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5695,17 +5667,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5714,12 +5686,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>35927853</t>
+          <t>1127614127</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35927853</t>
+          <t>https://m.place.naver.com/place/1127614127</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5736,29 +5708,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>봉선화물들이다</t>
+          <t>오손내미오</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>s8h6y@naver.com</t>
+          <t>playnauts@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02-6203-5478</t>
+          <t>0507-1492-1340</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s8h6y</t>
+          <t>https://www.instagram.com/oh_sonemio</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5773,7 +5745,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5793,13 +5765,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="Q58" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5808,12 +5780,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>33618035</t>
+          <t>1311070929</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33618035</t>
+          <t>https://m.place.naver.com/place/1311070929</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5830,25 +5802,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>위위즈 용산점</t>
+          <t>진주네 네일 효창공원점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1366-3547</t>
+          <t>0507-1403-6610</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
+          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ouiouiznail</t>
+          <t>https://www.instagram.com/jinjunenail</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5883,13 +5855,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>509</v>
+        <v>79</v>
       </c>
       <c r="Q59" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="R59" t="n">
-        <v>542</v>
+        <v>98</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5898,12 +5870,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1557214777</t>
+          <t>2056938739</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557214777</t>
+          <t>https://m.place.naver.com/place/2056938739</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5920,29 +5892,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>켈리하우스 네일샵</t>
+          <t>청담네일박스 용산점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kellylove09@naver.com</t>
+          <t>smilehh406@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1393-9967</t>
+          <t>0507-1325-5985</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 49</t>
+          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kellylove09</t>
+          <t>https://www.instagram.com/cheongdam_nailbox</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5957,7 +5929,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5968,23 +5940,23 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
         <v>5</v>
       </c>
-      <c r="R60" t="n">
-        <v>12</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>X</t>
@@ -5992,12 +5964,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>32875703</t>
+          <t>2020464978</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32875703</t>
+          <t>https://m.place.naver.com/place/2020464978</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6014,25 +5986,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>토마네일</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>yeoooey@naver.com</t>
-        </is>
-      </c>
+          <t>투투네일</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1336-4546</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
+          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/to.ma.nail</t>
+          <t>https://www.instagram.com/twotwo_nail</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6067,13 +6039,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="Q61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6082,12 +6054,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1701565426</t>
+          <t>1253759614</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701565426</t>
+          <t>https://m.place.naver.com/place/1253759614</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6104,25 +6076,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>비비네일</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Breathnailz</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>mooisu@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>02-749-9134</t>
+          <t>0507-1358-6853</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
+          <t>서울특별시 용산구 소월로20길 36 1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/vivinail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6132,7 +6108,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6153,17 +6129,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>303</v>
+        <v>2</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6172,12 +6148,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>21834362</t>
+          <t>1488241394</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21834362</t>
+          <t>https://m.place.naver.com/place/1488241394</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6194,12 +6170,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>컬러테일러</t>
+          <t>살롱드다한</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ariarisom2@naver.com</t>
+          <t>ddalkong9830@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -6207,17 +6183,17 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
+          <t>서울특별시 용산구 원효로 257 2층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_vpyXn</t>
+          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6238,7 +6214,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6247,13 +6223,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>319</v>
+        <v>229</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="R63" t="n">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6262,12 +6238,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1031854178</t>
+          <t>1917414808</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031854178</t>
+          <t>https://m.place.naver.com/place/1917414808</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6284,29 +6260,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>무구네일</t>
+          <t>센스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>mugunail2025@naver.com</t>
+          <t>showmblog@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0507-1353-2420</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 46 2층</t>
+          <t>서울특별시 용산구 만리재로 140-1</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6316,7 +6288,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6337,17 +6309,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>192</v>
+        <v>4</v>
       </c>
       <c r="Q64" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>235</v>
+        <v>6</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6356,12 +6328,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2093535455</t>
+          <t>1189922870</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093535455</t>
+          <t>https://m.place.naver.com/place/1189922870</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6378,29 +6350,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>러블리핑크</t>
+          <t>우아엘뷰티</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kisever1@naver.com</t>
+          <t>commathemoon_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>02-704-8470</t>
+          <t>0507-1379-1978</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 27 2층</t>
+          <t>서울특별시 용산구 효창원로 147 2층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/commathemoon_yongsan</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6410,12 +6382,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6431,17 +6403,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="R65" t="n">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6450,12 +6422,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>36901322</t>
+          <t>1942029836</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36901322</t>
+          <t>https://m.place.naver.com/place/1942029836</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6472,34 +6444,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일셀레나</t>
+          <t>수아르네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>na_young03@naver.com</t>
+          <t>xxong_11@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>02-795-6529</t>
+          <t>0507-1354-9689</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
+          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zJpfG</t>
+          <t>http://www.instagram.com/swa_rnail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6520,7 +6492,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6529,13 +6501,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>387</v>
+        <v>11</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R66" t="n">
-        <v>392</v>
+        <v>14</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6544,12 +6516,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>35489351</t>
+          <t>21568200</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35489351</t>
+          <t>https://m.place.naver.com/place/21568200</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6566,25 +6538,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>또또네일</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>팁셋 네일 한남점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>likelife_lovely@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1354-9049</t>
+          <t>0507-1375-5705</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 200 1층</t>
+          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ttotto__nail</t>
+          <t>https://www.instagram.com/tipset.seoul/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6619,13 +6595,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6634,12 +6610,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2020672159</t>
+          <t>1409853951</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020672159</t>
+          <t>https://m.place.naver.com/place/1409853951</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6656,12 +6632,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
+          <t>네일바래</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>tlstnals1010@naver.com</t>
+          <t>naillab20@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -6669,12 +6645,12 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
+          <t>서울특별시 용산구 원효로 214-6 2층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nailbarae_bboong</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6684,7 +6660,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6705,17 +6681,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6724,12 +6700,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1222846707</t>
+          <t>835341707</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222846707</t>
+          <t>https://m.place.naver.com/place/835341707</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6746,25 +6722,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일퀸</t>
+          <t>네일노마드 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kfreebaby@naver.com</t>
+          <t>kjr1212a@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1310-3658</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 47</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailnomad_</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6774,7 +6754,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6795,17 +6775,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>6</v>
+        <v>471</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R69" t="n">
-        <v>7</v>
+        <v>479</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6814,12 +6794,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1023738371</t>
+          <t>1841821386</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023738371</t>
+          <t>https://m.place.naver.com/place/1841821386</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6836,25 +6816,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>몽드메리</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>이촌동 네일타임 삼익상가</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>yjk2650@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1382-2264</t>
+          <t>02-749-8604</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/monde.mery</t>
+          <t>https://youtube.com/@ichon_nail_time</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6889,13 +6873,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>761</v>
+        <v>128</v>
       </c>
       <c r="Q70" t="n">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="R70" t="n">
-        <v>775</v>
+        <v>250</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6904,12 +6888,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1681006741</t>
+          <t>1281193252</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681006741</t>
+          <t>https://m.place.naver.com/place/1281193252</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6926,34 +6910,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>레푸스 용산역점</t>
+          <t>벨르네이쳐</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>refussyss@naver.com</t>
+          <t>dewsang@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1417-1074</t>
+          <t>0507-1463-0395</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
+          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://youtube.com/@레푸스용산역점</t>
+          <t>http://pf.kakao.com/_pixftn/chat</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6974,7 +6958,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6983,13 +6967,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>293</v>
+        <v>57</v>
       </c>
       <c r="Q71" t="n">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="R71" t="n">
-        <v>483</v>
+        <v>65</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6998,12 +6982,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1153661148</t>
+          <t>2043754067</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153661148</t>
+          <t>https://m.place.naver.com/place/2043754067</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7020,30 +7004,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일더누브</t>
+          <t>손톱까끼</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>hasom0304@naver.com</t>
+          <t>sinachoco@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1310-9297</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 210 1층</t>
+          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdFnxhn</t>
+          <t>https://www.instagram.com/kkakki_nail/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7064,7 +7052,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7073,13 +7061,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="Q72" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="R72" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7088,12 +7076,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1146800442</t>
+          <t>20939317</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1146800442</t>
+          <t>https://m.place.naver.com/place/20939317</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7110,25 +7098,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>더네일바 2호점</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>네일의날씨</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>queen77577@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1411-8549</t>
+          <t>0507-1430-0707</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
+          <t>서울특별시 용산구 한강대로 288-2 1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/thenailbar_hannam</t>
+          <t>http://instagram.com/nail_nalssi</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7154,7 +7146,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7163,13 +7155,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>6</v>
+        <v>497</v>
       </c>
       <c r="Q73" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="R73" t="n">
-        <v>94</v>
+        <v>545</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7178,12 +7170,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>706072929</t>
+          <t>1050641028</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/706072929</t>
+          <t>https://m.place.naver.com/place/1050641028</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7200,29 +7192,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>비바이유 한남</t>
+          <t>붙여핸썹</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>enoctobre-@naver.com</t>
+          <t>woowim@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1371-9481</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
+          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b.by_you</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7232,7 +7220,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7253,17 +7241,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7272,12 +7260,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2019591721</t>
+          <t>1333965738</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019591721</t>
+          <t>https://m.place.naver.com/place/1333965738</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7294,34 +7282,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일테라피은</t>
+          <t>컬러테일러</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>mountain__sun@naver.com</t>
+          <t>ariarisom2@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1379-8496</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
+          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailtherapyeun</t>
+          <t>https://pf.kakao.com/_vpyXn</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7342,7 +7326,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7351,13 +7335,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>203</v>
+        <v>319</v>
       </c>
       <c r="Q75" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R75" t="n">
-        <v>212</v>
+        <v>321</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7366,12 +7350,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1180134699</t>
+          <t>1031854178</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180134699</t>
+          <t>https://m.place.naver.com/place/1031854178</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7388,25 +7372,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>디에고푸스 희네일 이촌점</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>제이미 네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>see7833@naver.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1339-5732</t>
+          <t>02-701-5602</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
+          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heenail4345</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7416,7 +7404,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7437,17 +7425,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="Q76" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>157</v>
+        <v>31</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7456,12 +7444,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1972424680</t>
+          <t>255540367</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972424680</t>
+          <t>https://m.place.naver.com/place/255540367</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7478,34 +7466,34 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>벨르네이쳐</t>
+          <t>덴드네일한남</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>dewsang@naver.com</t>
+          <t>eunii222@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1463-0395</t>
+          <t>0507-1378-0596</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
+          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pixftn/chat</t>
+          <t>https://blog.naver.com/eunii222</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7515,7 +7503,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7526,7 +7514,7 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7535,13 +7523,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="Q77" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="R77" t="n">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7550,12 +7538,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>2043754067</t>
+          <t>1108900148</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043754067</t>
+          <t>https://m.place.naver.com/place/1108900148</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7572,29 +7560,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>나비네일</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>jytgh@naver.com</t>
-        </is>
-      </c>
+          <t>팝네일 신용산</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1416-0638</t>
+          <t>0507-1345-7477</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가-210</t>
+          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/popnail_7477</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7604,7 +7588,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7620,22 +7604,22 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>5</v>
+        <v>316</v>
       </c>
       <c r="Q78" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="R78" t="n">
-        <v>10</v>
+        <v>363</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7644,12 +7628,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>36629016</t>
+          <t>1306229960</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36629016</t>
+          <t>https://m.place.naver.com/place/1306229960</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7666,29 +7650,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>네일샵입니다</t>
+          <t>리라네일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>yooawo@naver.com</t>
+          <t>kkmm_0707@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1336-5457</t>
+          <t>02-703-4125</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
+          <t>서울특별시 용산구 원효로41길 23</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shopnailshop/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7698,7 +7682,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7719,17 +7703,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>206</v>
+        <v>1</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7738,12 +7722,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>954197461</t>
+          <t>1131445662</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/954197461</t>
+          <t>https://m.place.naver.com/place/1131445662</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7760,30 +7744,26 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>쵸코네일</t>
+          <t>네일드모네</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>02-749-7795</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
+          <t>서울특별시 용산구 독서당로 67 206호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>https://www.instagram.com/naildemonet</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7793,7 +7773,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7813,13 +7793,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="Q80" t="n">
         <v>3</v>
       </c>
       <c r="R80" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7828,12 +7808,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>19490178</t>
+          <t>2062875678</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19490178</t>
+          <t>https://m.place.naver.com/place/2062875678</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7850,25 +7830,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>센스</t>
+          <t>네일뮤지엄</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>showmblog@naver.com</t>
+          <t>nail-museum@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>070-7543-4009</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 140-1</t>
+          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nail-museum</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7878,12 +7862,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7899,17 +7883,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4</v>
+        <v>345</v>
       </c>
       <c r="Q81" t="n">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="R81" t="n">
-        <v>6</v>
+        <v>705</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7918,12 +7902,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1189922870</t>
+          <t>1881584782</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189922870</t>
+          <t>https://m.place.naver.com/place/1881584782</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -7940,29 +7924,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
+          <t>네일린</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>tlstnals1010@naver.com</t>
+          <t>cookyismylife@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>070-8882-4343</t>
+          <t>0507-1344-8515</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
+          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/j_magic_nail</t>
+          <t>https://www.instagram.com/naileensalon</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7997,13 +7981,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8012,12 +7996,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1438268528</t>
+          <t>1996449351</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438268528</t>
+          <t>https://m.place.naver.com/place/1996449351</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8034,29 +8018,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>네일리모노 이태원점</t>
+          <t>네일가꿈</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>nailremono@naver.com</t>
+          <t>hyu3323@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1350-6775</t>
+          <t>0507-1403-8723</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailremono</t>
+          <t>http://www.instagram.com/e_nailshop_sj</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8071,7 +8055,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8091,13 +8075,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="Q83" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="R83" t="n">
-        <v>344</v>
+        <v>549</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8106,12 +8090,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1785734080</t>
+          <t>1966796864</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785734080</t>
+          <t>https://m.place.naver.com/place/1966796864</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8128,29 +8112,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>네일의날씨</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>queen77577@naver.com</t>
-        </is>
-      </c>
+          <t>제이매직네일스</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1430-0707</t>
+          <t>070-8882-4343</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 288-2 1층</t>
+          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_nalssi</t>
+          <t>http://www.instagram.com/j_magic_nail</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8176,7 +8156,7 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8185,13 +8165,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>497</v>
+        <v>65</v>
       </c>
       <c r="Q84" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R84" t="n">
-        <v>545</v>
+        <v>89</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8200,12 +8180,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1050641028</t>
+          <t>1438268528</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050641028</t>
+          <t>https://m.place.naver.com/place/1438268528</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8222,30 +8202,34 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>어서오손네일</t>
+          <t>클리피</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>funhanbro@naver.com</t>
+          <t>seoul2gun@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1855-4010</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
+          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/funhanbro</t>
+          <t>http://pf.kakao.com/_txcJCb</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8255,7 +8239,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8266,7 +8250,7 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8278,10 +8262,10 @@
         <v>11</v>
       </c>
       <c r="Q85" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R85" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8290,12 +8274,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1030962704</t>
+          <t>1546271749</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030962704</t>
+          <t>https://m.place.naver.com/place/1546271749</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8312,25 +8296,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>오나네일</t>
+          <t>플리네일 용산해링턴점</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>wjsska1907@naver.com</t>
+          <t>lamidays@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1406-7552</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
+          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/o.nnail</t>
+          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8365,13 +8353,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>133</v>
+        <v>438</v>
       </c>
       <c r="Q86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R86" t="n">
-        <v>147</v>
+        <v>453</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8380,12 +8368,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1549497362</t>
+          <t>2075608465</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549497362</t>
+          <t>https://m.place.naver.com/place/2075608465</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8402,35 +8390,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>오드리네일</t>
+          <t>뷰리뉼레</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1446-0227</t>
+          <t>0507-1389-5562</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
+          <t>서울특별시 용산구 후암로 28 1층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oudreynail</t>
+          <t>https://toss.place/_lb/TYhSdSVIw</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8455,13 +8443,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R87" t="n">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8470,12 +8458,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1497063684</t>
+          <t>33277553</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1497063684</t>
+          <t>https://m.place.naver.com/place/33277553</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8492,25 +8480,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>살롱드다한</t>
+          <t>네일래쉬</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ddalkong9830@naver.com</t>
+          <t>nailash@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1371-0008</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 257 2층</t>
+          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/nailash</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8525,7 +8517,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8545,13 +8537,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>229</v>
+        <v>27</v>
       </c>
       <c r="Q88" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="R88" t="n">
-        <v>282</v>
+        <v>76</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8560,12 +8552,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1917414808</t>
+          <t>1220901153</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917414808</t>
+          <t>https://m.place.naver.com/place/1220901153</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8582,29 +8574,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>설화미</t>
+          <t>디에고푸스 희네일 이촌점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>who1who2@naver.com</t>
+          <t>jwkang3929@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1381-4227</t>
+          <t>0507-1339-5732</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
+          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sulwhami_beauty/</t>
+          <t>https://www.instagram.com/heenail4345</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8639,13 +8631,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="Q89" t="n">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="R89" t="n">
-        <v>342</v>
+        <v>157</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8654,12 +8646,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>33647337</t>
+          <t>1972424680</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33647337</t>
+          <t>https://m.place.naver.com/place/1972424680</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8676,29 +8668,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>진주네 네일 효창공원점</t>
+          <t>설화미</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>thwjd91070@naver.com</t>
+          <t>who1who2@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1403-6610</t>
+          <t>0507-1381-4227</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
+          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jinjunenail</t>
+          <t>https://www.instagram.com/sulwhami_beauty/</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8733,13 +8725,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="Q90" t="n">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="R90" t="n">
-        <v>98</v>
+        <v>342</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8748,12 +8740,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2056938739</t>
+          <t>33647337</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056938739</t>
+          <t>https://m.place.naver.com/place/33647337</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8770,34 +8762,34 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>네일헤라</t>
+          <t>쵸코네일</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jiyeon6305@naver.com</t>
+          <t>boong27@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1334-2839</t>
+          <t>02-749-7795</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
+          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.hera</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8807,7 +8799,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8827,13 +8819,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Q91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8842,12 +8834,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1936017804</t>
+          <t>19490178</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1936017804</t>
+          <t>https://m.place.naver.com/place/19490178</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8864,29 +8856,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>반디인하우스 용산아이파크몰점</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>bandinhouse_yongsan@naver.com</t>
-        </is>
-      </c>
+          <t>루아드네일</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1472-1811</t>
+          <t>0507-1452-9237</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
+          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
+          <t>http://pf.kakao.com/_xoEbJn/friend</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8901,7 +8889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8912,7 +8900,7 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8921,13 +8909,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1249</v>
+        <v>73</v>
       </c>
       <c r="Q92" t="n">
-        <v>189</v>
+        <v>8</v>
       </c>
       <c r="R92" t="n">
-        <v>1438</v>
+        <v>81</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -8936,12 +8924,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1049297184</t>
+          <t>2003721483</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049297184</t>
+          <t>https://m.place.naver.com/place/2003721483</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -8958,29 +8946,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>루아드네일</t>
+          <t>네일셀레나</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>sumr2002@naver.com</t>
+          <t>na_young03@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0507-1452-9237</t>
+          <t>02-795-6529</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xoEbJn/friend</t>
+          <t>http://pf.kakao.com/_zJpfG</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9015,13 +9003,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>73</v>
+        <v>387</v>
       </c>
       <c r="Q93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R93" t="n">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9030,12 +9018,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>2003721483</t>
+          <t>35489351</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003721483</t>
+          <t>https://m.place.naver.com/place/35489351</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9052,29 +9040,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>손톱의취향 용산푸르지오써밋점</t>
+          <t>몽드메리</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>tastein_nail_yongsan@naver.com</t>
+          <t>happygirl223@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1483-0870</t>
+          <t>0507-1382-2264</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
+          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taste_in_nail_</t>
+          <t>https://www.instagram.com/monde.mery</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9109,13 +9097,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>475</v>
+        <v>761</v>
       </c>
       <c r="Q94" t="n">
-        <v>282</v>
+        <v>14</v>
       </c>
       <c r="R94" t="n">
-        <v>757</v>
+        <v>775</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9124,12 +9112,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>2055593167</t>
+          <t>1681006741</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055593167</t>
+          <t>https://m.place.naver.com/place/1681006741</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9146,12 +9134,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>네일바래</t>
+          <t>우아한 네일 살롱</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>naillab20@naver.com</t>
+          <t>findmyperfectdays@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -9159,12 +9147,12 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 214-6 2층</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailbarae_bboong</t>
+          <t>https://www.instagram.com/wooanail_salon</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9199,13 +9187,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="Q95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9214,12 +9202,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>835341707</t>
+          <t>1370902820</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/835341707</t>
+          <t>https://m.place.naver.com/place/1370902820</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9236,29 +9224,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>우아엘뷰티</t>
+          <t>제이제이 네일</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>commathemoon_yongsan@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1379-1978</t>
+          <t>0507-1411-8138</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 147 2층</t>
+          <t>서울특별시 용산구 회나무로 32-3 2층</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/commathemoon_yongsan</t>
+          <t>https://www.instagram.com/jjjjnail</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9273,7 +9261,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9293,13 +9281,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="Q96" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9308,12 +9296,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1942029836</t>
+          <t>79017915</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942029836</t>
+          <t>https://m.place.naver.com/place/79017915</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9330,29 +9318,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>네일슈슈</t>
+          <t>네일휴</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>brilliant14694@naver.com</t>
+          <t>white5198@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1435-9113</t>
+          <t>02-711-3646</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
+          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_chouchou_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9362,7 +9350,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9383,17 +9371,17 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>461</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>489</v>
+        <v>2</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9402,12 +9390,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1185094311</t>
+          <t>1611951357</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185094311</t>
+          <t>https://m.place.naver.com/place/1611951357</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9424,29 +9412,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>헤더네일</t>
+          <t>네일슈슈</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>mmmmbin@naver.com</t>
+          <t>brilliant14694@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1464-8960</t>
+          <t>0507-1435-9113</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heathernail_102/</t>
+          <t>https://www.instagram.com/nail_chouchou_</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9481,13 +9469,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>25</v>
+        <v>461</v>
       </c>
       <c r="Q98" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="R98" t="n">
-        <v>27</v>
+        <v>489</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9496,12 +9484,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1399079243</t>
+          <t>1185094311</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399079243</t>
+          <t>https://m.place.naver.com/place/1185094311</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9518,29 +9506,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>코코루네일</t>
+          <t>위위즈 용산점</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>xanxixxanx@naver.com</t>
+          <t>yigu8@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1390-4270</t>
+          <t>0507-1366-3547</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
+          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/ouiouiznail</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9575,13 +9563,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3</v>
+        <v>509</v>
       </c>
       <c r="Q99" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="R99" t="n">
-        <v>8</v>
+        <v>542</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9590,12 +9578,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1768871817</t>
+          <t>1557214777</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768871817</t>
+          <t>https://m.place.naver.com/place/1557214777</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9612,29 +9600,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>버들네일</t>
+          <t>무구네일</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>test_golry@naver.com</t>
+          <t>mugunail2025@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1400-7111</t>
+          <t>0507-1353-2420</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 147 1층</t>
+          <t>서울특별시 용산구 새창로14길 46 2층</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b_d_nail</t>
+          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9669,13 +9657,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="Q100" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="R100" t="n">
-        <v>28</v>
+        <v>235</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9684,12 +9672,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1127614127</t>
+          <t>2093535455</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127614127</t>
+          <t>https://m.place.naver.com/place/2093535455</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9706,21 +9694,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>네일클로버</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0507-1416-0638</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
+          <t>서울특별시 용산구 새창로 70 상가-210</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailclover_yongsan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9730,7 +9722,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9751,17 +9743,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9770,12 +9762,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>32496791</t>
+          <t>36629016</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32496791</t>
+          <t>https://m.place.naver.com/place/36629016</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -9792,25 +9784,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>후암네일</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>봉선화물들이다</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>s8h6y@naver.com</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0507-1301-4091</t>
+          <t>02-6203-5478</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
+          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/huam_nail</t>
+          <t>https://blog.naver.com/s8h6y</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9825,7 +9821,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9845,13 +9841,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="Q102" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R102" t="n">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9860,12 +9856,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>2033884779</t>
+          <t>33618035</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033884779</t>
+          <t>https://m.place.naver.com/place/33618035</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -9882,34 +9878,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>프로네일</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>sonvely89@naver.com</t>
-        </is>
-      </c>
+          <t>묘즈네일</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0507-1421-1525</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
+          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/itaewonpronail/</t>
+          <t>http://pf.kakao.com/_WxedxgG</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -9930,7 +9918,7 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -9939,13 +9927,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="Q103" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="R103" t="n">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -9954,12 +9942,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>13028002</t>
+          <t>1136869573</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13028002</t>
+          <t>https://m.place.naver.com/place/1136869573</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -9976,34 +9964,30 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>클리피</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>seoul2gun@naver.com</t>
-        </is>
-      </c>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1855-4010</t>
+          <t>02-749-9134</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_txcJCb</t>
+          <t>http://www.instagram.com/vivinail</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10024,7 +10008,7 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -10033,13 +10017,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>11</v>
+        <v>258</v>
       </c>
       <c r="Q104" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="R104" t="n">
-        <v>14</v>
+        <v>303</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10048,12 +10032,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1546271749</t>
+          <t>21834362</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546271749</t>
+          <t>https://m.place.naver.com/place/21834362</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10070,29 +10054,25 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>네일월드</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>daisukitokyo@naver.com</t>
-        </is>
-      </c>
+          <t>리네일</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>02-715-9585</t>
+          <t>0507-1421-7880</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6</t>
+          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/ri_nail7877</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10102,7 +10082,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10123,17 +10103,17 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10142,12 +10122,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1228817187</t>
+          <t>32244399</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228817187</t>
+          <t>https://m.place.naver.com/place/32244399</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10164,35 +10144,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>재니네일한남</t>
+          <t>루미가넷네일존 이마트 용산점</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>evian___@naver.com</t>
+          <t>hyer2986@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0507-1401-9470</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
+          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eKxmLxl</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -10208,22 +10192,22 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="Q106" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="R106" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10232,12 +10216,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1593741438</t>
+          <t>1619342094</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593741438</t>
+          <t>https://m.place.naver.com/place/1619342094</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10254,30 +10238,34 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>우아한 네일 살롱</t>
+          <t>마틸다네일M 한남점</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>findmyperfectdays@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0507-1412-3082</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
+          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wooanail_salon</t>
+          <t>https://matildanailshop-mo3.imweb.me/</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10287,7 +10275,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -10307,13 +10295,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="Q107" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="R107" t="n">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10322,12 +10310,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1370902820</t>
+          <t>1798849933</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370902820</t>
+          <t>https://m.place.naver.com/place/1798849933</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10344,29 +10332,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>빛나러오소문제성발관리 용산점</t>
+          <t>데코네일</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>kknsky73@naver.com</t>
+          <t>bambi_showpu@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>0507-1419-6888</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
+          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://youtube.com/@user-gc4wk2yn2b</t>
+          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10392,7 +10376,7 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -10401,13 +10385,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>250</v>
+        <v>41</v>
       </c>
       <c r="Q108" t="n">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="R108" t="n">
-        <v>416</v>
+        <v>123</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10416,12 +10400,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>1438224262</t>
+          <t>36812317</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438224262</t>
+          <t>https://m.place.naver.com/place/36812317</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10438,29 +10422,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>네일꾼</t>
+          <t>아드</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jinheeloo@naver.com</t>
+          <t>adfontes_math@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>0507-1407-8585</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
+          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/a.th_kr</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10470,7 +10450,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -10491,17 +10471,17 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="Q109" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10510,12 +10490,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1395413071</t>
+          <t>1700535825</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395413071</t>
+          <t>https://m.place.naver.com/place/1700535825</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10532,20 +10512,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>붙여핸썹</t>
+          <t>진유진네일</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>woowim@naver.com</t>
+          <t>seoul2816@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0507-1416-2081</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
+          <t>서울특별시 용산구 한강대로 284</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10585,13 +10569,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10600,12 +10584,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1333965738</t>
+          <t>31574498</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333965738</t>
+          <t>https://m.place.naver.com/place/31574498</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10622,29 +10606,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>이앤앤</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>eyennail@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0507-1316-3771</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
+          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_eyennail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10654,7 +10634,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -10675,17 +10655,17 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>594</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>1334</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>1928</v>
+        <v>1</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10694,12 +10674,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>375707328</t>
+          <t>1222846707</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/375707328</t>
+          <t>https://m.place.naver.com/place/1222846707</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10716,25 +10696,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>네일프롬다니</t>
+          <t>토마네일</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>0507-1349-9460</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
+          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
+          <t>https://www.instagram.com/to.ma.nail</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10769,13 +10745,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R112" t="n">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10784,12 +10760,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1774853191</t>
+          <t>1701565426</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774853191</t>
+          <t>https://m.place.naver.com/place/1701565426</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -10806,29 +10782,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>팁셋 네일 한남점</t>
+          <t>레푸스 용산역점</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>likelife_lovely@naver.com</t>
+          <t>refussyss@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0507-1375-5705</t>
+          <t>0507-1417-1074</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
+          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tipset.seoul/</t>
+          <t>https://youtube.com/@레푸스용산역점</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10863,13 +10839,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>70</v>
+        <v>293</v>
       </c>
       <c r="Q113" t="n">
-        <v>3</v>
+        <v>190</v>
       </c>
       <c r="R113" t="n">
-        <v>73</v>
+        <v>483</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10878,12 +10854,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1409853951</t>
+          <t>1153661148</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409853951</t>
+          <t>https://m.place.naver.com/place/1153661148</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -10900,29 +10876,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Breathnailz</t>
+          <t>네일프롬다니</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>mooisu@naver.com</t>
+          <t>arielisflowery@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1358-6853</t>
+          <t>0507-1349-9460</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 36 1층</t>
+          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10932,7 +10908,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -10953,17 +10929,17 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P114" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>2</v>
-      </c>
       <c r="R114" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -10972,12 +10948,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1488241394</t>
+          <t>1774853191</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488241394</t>
+          <t>https://m.place.naver.com/place/1774853191</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -10994,29 +10970,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>팝네일 신용산</t>
+          <t>네일디렉터</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>mhhj951026@naver.com</t>
+          <t>naildirector@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0507-1345-7477</t>
+          <t>02-797-8188</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
+          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/popnail_7477</t>
+          <t>https://blog.naver.com/naildirector</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11031,7 +11007,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11042,7 +11018,7 @@
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -11051,13 +11027,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>316</v>
+        <v>157</v>
       </c>
       <c r="Q115" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="R115" t="n">
-        <v>363</v>
+        <v>168</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11066,12 +11042,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1306229960</t>
+          <t>1487195546</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306229960</t>
+          <t>https://m.place.naver.com/place/1487195546</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -11088,29 +11064,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>오렌지나무</t>
+          <t>손톱의취향 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>dew517@naver.com</t>
+          <t>tastein_nail_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1323-2154</t>
+          <t>0507-1483-0870</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로20길 13 1층</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
+          <t>https://www.instagram.com/taste_in_nail_</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11145,13 +11121,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>13</v>
+        <v>475</v>
       </c>
       <c r="Q116" t="n">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="R116" t="n">
-        <v>15</v>
+        <v>762</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11160,12 +11136,12 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>1568164546</t>
+          <t>2055593167</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568164546</t>
+          <t>https://m.place.naver.com/place/2055593167</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -11182,29 +11158,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>진유진네일</t>
+          <t>비바이유 한남</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>seoul2816@naver.com</t>
+          <t>enoctobre-@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0507-1416-2081</t>
+          <t>0507-1371-9481</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 284</t>
+          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/b.by_you</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11214,7 +11190,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -11235,17 +11211,17 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="R117" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11254,12 +11230,12 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>31574498</t>
+          <t>2019591721</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31574498</t>
+          <t>https://m.place.naver.com/place/2019591721</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">

--- a/naver-place-crawler/results_nail/용산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/용산_네일샵.xlsx
@@ -564,12 +564,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일클로버</t>
+          <t>살롱드다한</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>ddalkong9830@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -577,12 +577,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
+          <t>서울특별시 용산구 원효로 257 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailclover_yongsan</t>
+          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>229</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>282</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>32496791</t>
+          <t>1917414808</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32496791</t>
+          <t>https://m.place.naver.com/place/1917414808</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -654,29 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>신용산네일라뜰리에왁싱</t>
+          <t>네일휴</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hee_1220@naver.com</t>
+          <t>white5198@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1380-7730</t>
+          <t>02-711-3646</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
+          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -726,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1054108199</t>
+          <t>1611951357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054108199</t>
+          <t>https://m.place.naver.com/place/1611951357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -748,25 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일테라피은</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>진유진네일</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>seoul2816@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1379-8496</t>
+          <t>0507-1416-2081</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
+          <t>서울특별시 용산구 한강대로 284</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailtherapyeun</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -776,7 +780,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -797,17 +801,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>203</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="R4" t="n">
-        <v>212</v>
+        <v>93</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1180134699</t>
+          <t>31574498</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180134699</t>
+          <t>https://m.place.naver.com/place/31574498</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -838,25 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>수 네일</t>
+          <t>네일프롬다니</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>qkrqhrdfrn@naver.com</t>
+          <t>arielisflowery@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1349-9460</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 196 B1층</t>
+          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qkrqhrdfrn</t>
+          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -871,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -882,7 +890,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -891,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -906,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1989007422</t>
+          <t>1774853191</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989007422</t>
+          <t>https://m.place.naver.com/place/1774853191</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -928,34 +936,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더네일바 2호점</t>
+          <t>반디인하우스 용산아이파크몰점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>beczzam@naver.com</t>
+          <t>bandinhouse_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1411-8549</t>
+          <t>0507-1472-1811</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
+          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/thenailbar_hannam</t>
+          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -965,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -985,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>1249</v>
       </c>
       <c r="Q6" t="n">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="R6" t="n">
-        <v>94</v>
+        <v>1438</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1000,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>706072929</t>
+          <t>1049297184</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/706072929</t>
+          <t>https://m.place.naver.com/place/1049297184</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1022,25 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바림</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>투투네일</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>vin2roo@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-318-2055</t>
+          <t>0507-1336-4546</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로 73</t>
+          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://instagram.com/Barim_nail</t>
+          <t>https://www.instagram.com/twotwo_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1090,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1862156671</t>
+          <t>1253759614</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862156671</t>
+          <t>https://m.place.naver.com/place/1253759614</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1107,31 +1119,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>네일아트재료</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>메이크케이</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>어서오손네일</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>funhanbro@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 56 1층</t>
+          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
+          <t>https://blog.naver.com/funhanbro</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1161,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1176,12 +1192,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2081839313</t>
+          <t>1030962704</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2081839313</t>
+          <t>https://m.place.naver.com/place/1030962704</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1198,25 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>글로시블라썸 아이파크몰</t>
+          <t>비바이유 한남</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>irumskin@naver.com</t>
+          <t>enoctobre-@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1371-9481</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55</t>
+          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/b.by_you</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1226,7 +1246,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1247,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1266,12 +1286,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1485867849</t>
+          <t>2019591721</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485867849</t>
+          <t>https://m.place.naver.com/place/2019591721</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1288,29 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>반디인하우스 용산아이파크몰점</t>
+          <t>벨르네이쳐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bandinhouse_yongsan@naver.com</t>
+          <t>dewsang@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1472-1811</t>
+          <t>0507-1463-0395</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
+          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
+          <t>http://pf.kakao.com/_pixftn/chat</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1325,7 +1345,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1336,7 +1356,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1345,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1249</v>
+        <v>57</v>
       </c>
       <c r="Q10" t="n">
-        <v>189</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>1438</v>
+        <v>65</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1360,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1049297184</t>
+          <t>2043754067</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049297184</t>
+          <t>https://m.place.naver.com/place/2043754067</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1382,35 +1402,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>러블리핑크</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>레푸스 용산역점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>refussyss@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-704-8470</t>
+          <t>0507-1417-1074</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 27 2층</t>
+          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@레푸스용산역점</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1431,17 +1455,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>293</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="R11" t="n">
-        <v>13</v>
+        <v>483</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1450,12 +1474,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36901322</t>
+          <t>1153661148</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36901322</t>
+          <t>https://m.place.naver.com/place/1153661148</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1472,34 +1496,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>쿠로키네일</t>
+          <t>팁셋 네일 한남점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>likelife_lovely@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1481-2893</t>
+          <t>0507-1375-5705</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 19-2 1층</t>
+          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xaxcxeBG</t>
+          <t>https://www.instagram.com/tipset.seoul/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1520,7 +1544,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1529,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>157</v>
+        <v>71</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1544,12 +1568,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1723956505</t>
+          <t>1409853951</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723956505</t>
+          <t>https://m.place.naver.com/place/1409853951</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1566,29 +1590,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>이촌 네일타임 LG프라자</t>
+          <t>또또네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>blingsea@naver.com</t>
+          <t>clsald30@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1498-8612</t>
+          <t>0507-1354-9049</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
+          <t>서울특별시 용산구 원효로 200 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ttotto__nail</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1598,7 +1622,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1619,17 +1643,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1638,12 +1662,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>20064911</t>
+          <t>2020672159</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20064911</t>
+          <t>https://m.place.naver.com/place/2020672159</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1660,30 +1684,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>아로하네일</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>손톱까끼</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sinachoco@naver.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1391-4369</t>
+          <t>0507-1310-9297</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로14길 10 2층</t>
+          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/alohanail_chae</t>
+          <t>https://www.instagram.com/kkakki_nail/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1693,7 +1721,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1713,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1728,12 +1756,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1264306160</t>
+          <t>20939317</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264306160</t>
+          <t>https://m.place.naver.com/place/20939317</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1750,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>빛나러오소문제성발관리 용산점</t>
+          <t>리네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kknsky73@naver.com</t>
+          <t>dlwjddo7053@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1419-6888</t>
+          <t>0507-1421-7880</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
+          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://youtube.com/@user-gc4wk2yn2b</t>
+          <t>http://instagram.com/ri_nail7877</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1798,7 +1826,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1807,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>250</v>
+        <v>51</v>
       </c>
       <c r="Q15" t="n">
-        <v>166</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>416</v>
+        <v>53</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1822,12 +1850,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1438224262</t>
+          <t>32244399</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438224262</t>
+          <t>https://m.place.naver.com/place/32244399</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1844,29 +1872,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>유스뷰티</t>
+          <t>센스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jyrif91@naver.com</t>
+          <t>showmblog@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1422-3533</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로20길 21 1층</t>
+          <t>서울특별시 용산구 만리재로 140-1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youthnail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1876,7 +1900,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1897,17 +1921,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1916,12 +1940,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>38467380</t>
+          <t>1189922870</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38467380</t>
+          <t>https://m.place.naver.com/place/1189922870</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1938,29 +1962,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일헤라</t>
+          <t>에일린</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jiyeon6305@naver.com</t>
+          <t>myungae7@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1334-2839</t>
+          <t>0507-1445-2816</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
+          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.hera</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1970,7 +1994,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1991,17 +2015,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>393</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="R17" t="n">
-        <v>8</v>
+        <v>471</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2010,12 +2034,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1936017804</t>
+          <t>1447531035</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1936017804</t>
+          <t>https://m.place.naver.com/place/1447531035</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2032,25 +2056,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>다교네일 한남</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>쿠로키네일</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>vin2roo@naver.com</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1339-1024</t>
+          <t>0507-1481-2893</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
+          <t>서울특별시 용산구 신흥로 19-2 1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_VZqxfG/chat</t>
+          <t>https://pf.kakao.com/_xaxcxeBG</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2085,13 +2113,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>338</v>
+        <v>157</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="R18" t="n">
-        <v>374</v>
+        <v>165</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2100,12 +2128,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>37620988</t>
+          <t>1723956505</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37620988</t>
+          <t>https://m.place.naver.com/place/1723956505</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2122,29 +2150,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
+          <t>붙여핸썹</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>j2lang@naver.com</t>
+          <t>woowim@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1345-4179</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
+          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://instagram.com/today_nail_ichon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2154,7 +2178,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2175,17 +2199,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2194,12 +2218,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>21038031</t>
+          <t>1333965738</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21038031</t>
+          <t>https://m.place.naver.com/place/1333965738</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2216,30 +2240,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>재니네일한남</t>
+          <t>오렌지나무</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>evian___@naver.com</t>
+          <t>dew517@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1323-2154</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
+          <t>서울특별시 용산구 한남대로20길 13 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eKxmLxl</t>
+          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2260,7 +2288,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2269,13 +2297,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2284,12 +2312,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1593741438</t>
+          <t>1568164546</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593741438</t>
+          <t>https://m.place.naver.com/place/1568164546</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2306,29 +2334,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>이앤앤</t>
+          <t>토마네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>eyennail@naver.com</t>
+          <t>yeoooey@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1316-3771</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
+          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_eyennail_</t>
+          <t>https://www.instagram.com/to.ma.nail</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2363,13 +2387,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>594</v>
+        <v>123</v>
       </c>
       <c r="Q21" t="n">
-        <v>1334</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>1928</v>
+        <v>130</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2378,12 +2402,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>375707328</t>
+          <t>1701565426</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/375707328</t>
+          <t>https://m.place.naver.com/place/1701565426</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2400,29 +2424,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일삼각지</t>
+          <t>이앤앤</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nailsamgakji@naver.com</t>
+          <t>eyennail@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1316-2792</t>
+          <t>0507-1316-3771</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
+          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_samgakji</t>
+          <t>http://www.instagram.com/_eyennail_</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2448,7 +2472,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2457,13 +2481,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>17</v>
+        <v>594</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>1334</v>
       </c>
       <c r="R22" t="n">
-        <v>22</v>
+        <v>1928</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2472,12 +2496,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1872968588</t>
+          <t>375707328</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1872968588</t>
+          <t>https://m.place.naver.com/place/375707328</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2494,34 +2518,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>카밍네일</t>
+          <t>오늘도네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>daisoblog@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1357-1496</t>
+          <t>0507-1345-4179</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 42 1층</t>
+          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/calming_nail</t>
+          <t>http://instagram.com/today_nail_ichon</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2531,7 +2555,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2551,13 +2575,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>167</v>
+        <v>293</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>192</v>
+        <v>300</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2566,12 +2590,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1383549813</t>
+          <t>21038031</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383549813</t>
+          <t>https://m.place.naver.com/place/21038031</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2588,29 +2612,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>헤더네일</t>
+          <t>네일뮤지엄</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mmmmbin@naver.com</t>
+          <t>nail-museum@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1464-8960</t>
+          <t>070-7543-4009</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
+          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heathernail_102/</t>
+          <t>https://blog.naver.com/nail-museum</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2625,7 +2649,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2645,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>25</v>
+        <v>345</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="R24" t="n">
-        <v>27</v>
+        <v>705</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2660,12 +2684,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1399079243</t>
+          <t>1881584782</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399079243</t>
+          <t>https://m.place.naver.com/place/1881584782</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2682,29 +2706,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>플로르 네일 이태원점</t>
+          <t>우아엘뷰티</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>flornail@naver.com</t>
+          <t>commathemoon_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-790-4182</t>
+          <t>0507-1379-1978</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로 47 4층</t>
+          <t>서울특별시 용산구 효창원로 147 2층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/flornail</t>
+          <t>https://blog.naver.com/commathemoon_yongsan</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2739,13 +2763,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="n">
-        <v>163</v>
+        <v>27</v>
       </c>
       <c r="R25" t="n">
-        <v>280</v>
+        <v>127</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2754,12 +2778,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>32435712</t>
+          <t>1942029836</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32435712</t>
+          <t>https://m.place.naver.com/place/1942029836</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2776,25 +2800,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일월드</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>네일삼각지</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nailsamgakji@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02-715-9585</t>
+          <t>0507-1316-2792</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6</t>
+          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_samgakji</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2804,7 +2832,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2820,22 +2848,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2844,12 +2872,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1228817187</t>
+          <t>1872968588</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228817187</t>
+          <t>https://m.place.naver.com/place/1872968588</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2866,12 +2894,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일퀸</t>
+          <t>데코네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kfreebaby@naver.com</t>
+          <t>bambi_showpu@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2879,12 +2907,12 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 47</t>
+          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2894,7 +2922,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2915,17 +2943,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="R27" t="n">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2934,12 +2962,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1023738371</t>
+          <t>36812317</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023738371</t>
+          <t>https://m.place.naver.com/place/36812317</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2956,30 +2984,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>후암네일</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>디에고푸스 희네일 이촌점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jwkang3929@naver.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1301-4091</t>
+          <t>0507-1339-5732</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
+          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/huam_nail</t>
+          <t>https://www.instagram.com/heenail4345</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2989,7 +3021,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3009,13 +3041,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="R28" t="n">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3024,12 +3056,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2033884779</t>
+          <t>1972424680</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033884779</t>
+          <t>https://m.place.naver.com/place/1972424680</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3046,40 +3078,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>쵸민네일</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>네일바이르레</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>l5v2osh@naver.com</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1403-3417</t>
+          <t>0507-1312-9470</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
+          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_by_lerre</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3095,17 +3131,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3114,12 +3150,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1664663384</t>
+          <t>37818863</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664663384</t>
+          <t>https://m.place.naver.com/place/37818863</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3136,34 +3172,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일바이르레</t>
+          <t>네일테라피은</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>l5v2osh@naver.com</t>
+          <t>mountain__sun@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1312-9470</t>
+          <t>0507-1379-8496</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
+          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_by_lerre</t>
+          <t>https://www.instagram.com/nailtherapyeun</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3173,7 +3209,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3193,13 +3229,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>94</v>
+        <v>212</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3208,12 +3244,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>37818863</t>
+          <t>1180134699</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37818863</t>
+          <t>https://m.place.naver.com/place/1180134699</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3230,29 +3266,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>블랑</t>
+          <t>네일디렉터</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>hg6580@naver.com</t>
+          <t>naildirector@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02-790-8798</t>
+          <t>02-797-8188</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
+          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailist_blanc</t>
+          <t>https://blog.naver.com/naildirector</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3267,7 +3303,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3287,13 +3323,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R31" t="n">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3302,12 +3338,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>909330706</t>
+          <t>1487195546</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/909330706</t>
+          <t>https://m.place.naver.com/place/1487195546</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3324,40 +3360,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>티아라네일어반스파</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>마틸다네일M 한남점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>vin2roo@naver.com</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>02-790-7882</t>
+          <t>0507-1412-3082</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
+          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://matildanailshop-mo3.imweb.me/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3373,17 +3413,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3392,12 +3432,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>33213520</t>
+          <t>1798849933</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33213520</t>
+          <t>https://m.place.naver.com/place/1798849933</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3414,29 +3454,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>호박손톱</t>
+          <t>아드</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>appealogad@naver.com</t>
+          <t>adfontes_math@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>02-794-7958</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
+          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/a.th_kr</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3446,7 +3482,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3467,17 +3503,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="Q33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3486,12 +3522,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>35927853</t>
+          <t>1700535825</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35927853</t>
+          <t>https://m.place.naver.com/place/1700535825</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3508,12 +3544,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>마고뷰티</t>
+          <t>묘즈네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mago_smp@naver.com</t>
+          <t>xoxobloggirl@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -3521,12 +3557,12 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
+          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xjBnAn</t>
+          <t>http://pf.kakao.com/_WxedxgG</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3561,13 +3597,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="Q34" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="R34" t="n">
-        <v>155</v>
+        <v>57</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3576,12 +3612,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1939429266</t>
+          <t>1136869573</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939429266</t>
+          <t>https://m.place.naver.com/place/1136869573</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3598,25 +3634,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>제이비풋 굳은살&amp;발톱 케어</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>수아르네일</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>xxong_11@naver.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>02-794-8551</t>
+          <t>0507-1354-9689</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
+          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/swa_rnail</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3626,7 +3666,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3647,17 +3687,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>351</v>
+        <v>11</v>
       </c>
       <c r="Q35" t="n">
-        <v>179</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>530</v>
+        <v>14</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3666,12 +3706,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>12791408</t>
+          <t>21568200</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12791408</t>
+          <t>https://m.place.naver.com/place/21568200</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3688,25 +3728,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>오나네일</t>
+          <t>더네일바 2호점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1411-8549</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
+          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/o.nnail</t>
+          <t>http://www.instagram.com/thenailbar_hannam</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3741,13 +3785,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="R36" t="n">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3756,12 +3800,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1549497362</t>
+          <t>706072929</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549497362</t>
+          <t>https://m.place.naver.com/place/706072929</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3778,25 +3822,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일꾼</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>팝네일 신용산</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mhhj951026@naver.com</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1407-8585</t>
+          <t>0507-1345-7477</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
+          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/popnail_7477</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3806,7 +3854,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3822,22 +3870,22 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>28</v>
+        <v>316</v>
       </c>
       <c r="Q37" t="n">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="R37" t="n">
-        <v>162</v>
+        <v>363</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3846,12 +3894,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1395413071</t>
+          <t>1306229960</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395413071</t>
+          <t>https://m.place.naver.com/place/1306229960</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3868,12 +3916,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>더 트리니티 네일</t>
+          <t>수 네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dlfnfl0129@naver.com</t>
+          <t>qkrqhrdfrn@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3881,12 +3929,12 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
+          <t>서울특별시 용산구 만리재로 196 B1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the_trinity_nail/</t>
+          <t>https://blog.naver.com/qkrqhrdfrn</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3901,7 +3949,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3912,7 +3960,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3921,13 +3969,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="Q38" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="R38" t="n">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3936,12 +3984,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1060176123</t>
+          <t>1989007422</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060176123</t>
+          <t>https://m.place.naver.com/place/1989007422</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3958,29 +4006,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>또또네일</t>
+          <t>네일바라기</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>clsald30@naver.com</t>
+          <t>sydy8585@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1354-9049</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 200 1층</t>
+          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ttotto__nail</t>
+          <t>http://instagram.com/nail_baragi_</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4015,13 +4059,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="Q39" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R39" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4030,12 +4074,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2020672159</t>
+          <t>1091743517</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020672159</t>
+          <t>https://m.place.naver.com/place/1091743517</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4052,29 +4096,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일스눕</t>
+          <t>코코루네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>yseaeaho@naver.com</t>
+          <t>xanxixxanx@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1428-1646</t>
+          <t>0507-1390-4270</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로52길 38 202호</t>
+          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_snoope</t>
+          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4109,13 +4153,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>145</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4124,12 +4168,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1926501985</t>
+          <t>1768871817</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926501985</t>
+          <t>https://m.place.naver.com/place/1768871817</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4146,25 +4190,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일샵입니다</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>플리네일 용산해링턴점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>lamidays@naver.com</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1336-5457</t>
+          <t>0507-1406-7552</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
+          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shopnailshop/</t>
+          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4199,13 +4247,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>171</v>
+        <v>439</v>
       </c>
       <c r="Q41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="R41" t="n">
-        <v>206</v>
+        <v>454</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4214,12 +4262,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>954197461</t>
+          <t>2075608465</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/954197461</t>
+          <t>https://m.place.naver.com/place/2075608465</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4236,29 +4284,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>정원네일</t>
+          <t>위위즈 용산점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>pretty6144@naver.com</t>
+          <t>yigu8@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1406-7118</t>
+          <t>0507-1366-3547</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
+          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://instagram.com/jungwon_nail_</t>
+          <t>https://www.instagram.com/ouiouiznail</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4293,13 +4341,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>132</v>
+        <v>509</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R42" t="n">
-        <v>132</v>
+        <v>542</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4308,12 +4356,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1935294802</t>
+          <t>1557214777</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935294802</t>
+          <t>https://m.place.naver.com/place/1557214777</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4330,25 +4378,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>프로네일</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>오나네일</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>dong_fcpae@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1421-1525</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
+          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/itaewonpronail/</t>
+          <t>https://www.instagram.com/o.nnail</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4383,13 +4431,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>6</v>
+        <v>133</v>
       </c>
       <c r="Q43" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="R43" t="n">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4398,12 +4446,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>13028002</t>
+          <t>1549497362</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13028002</t>
+          <t>https://m.place.naver.com/place/1549497362</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4415,39 +4463,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>네일아트재료</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>켈리하우스 네일샵</t>
+          <t>메이크케이</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kellylove09@naver.com</t>
+          <t>kbanknow@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0507-1393-9967</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 49</t>
+          <t>서울특별시 용산구 청파로47길 56 1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kellylove09</t>
+          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4473,17 +4517,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4492,12 +4536,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>32875703</t>
+          <t>2081839313</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32875703</t>
+          <t>https://m.place.naver.com/place/2081839313</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4514,29 +4558,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>신데렐라</t>
+          <t>네일의날씨</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dracura10@naver.com</t>
+          <t>queen77577@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>02-790-3304</t>
+          <t>0507-1430-0707</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 61</t>
+          <t>서울특별시 용산구 한강대로 288-2 1층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_nalssi</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4546,7 +4590,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4562,22 +4606,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>497</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="R45" t="n">
-        <v>6</v>
+        <v>545</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4586,12 +4630,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>20662540</t>
+          <t>1050641028</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20662540</t>
+          <t>https://m.place.naver.com/place/1050641028</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4608,25 +4652,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일샵베이비</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>제이제이 네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>yang4550@naver.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1396-4649</t>
+          <t>0507-1411-8138</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로2길 19 1층</t>
+          <t>서울특별시 용산구 회나무로 32-3 2층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jjjjnail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4636,7 +4684,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4657,17 +4705,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4676,12 +4724,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1847608869</t>
+          <t>79017915</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847608869</t>
+          <t>https://m.place.naver.com/place/79017915</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4698,20 +4746,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>에일린</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>제이비풋 굳은살&amp;발톱 케어</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sunny_0225@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1445-2816</t>
+          <t>02-794-8551</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4751,13 +4803,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="Q47" t="n">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="R47" t="n">
-        <v>471</v>
+        <v>529</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4766,12 +4818,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1447531035</t>
+          <t>12791408</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447531035</t>
+          <t>https://m.place.naver.com/place/12791408</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4788,25 +4840,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>어서오손네일</t>
+          <t>헤더네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>funhanbro@naver.com</t>
+          <t>mmmmbin@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1464-8960</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/funhanbro</t>
+          <t>https://www.instagram.com/heathernail_102/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4821,7 +4877,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4841,13 +4897,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4856,12 +4912,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1030962704</t>
+          <t>1399079243</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030962704</t>
+          <t>https://m.place.naver.com/place/1399079243</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4878,29 +4934,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>춘희손톱</t>
+          <t>프로네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>chii0216@naver.com</t>
+          <t>sonvely89@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1306-7521</t>
+          <t>0507-1421-1525</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
+          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://instagram.com/choonheenail</t>
+          <t>http://www.instagram.com/itaewonpronail/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4935,13 +4991,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>196</v>
+        <v>6</v>
       </c>
       <c r="Q49" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="R49" t="n">
-        <v>295</v>
+        <v>111</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4950,12 +5006,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>20559743</t>
+          <t>13028002</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20559743</t>
+          <t>https://m.place.naver.com/place/13028002</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4972,21 +5028,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일바라기</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>청담네일박스 용산점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>smilehh406@naver.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1325-5985</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
+          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_baragi_</t>
+          <t>https://www.instagram.com/cheongdam_nailbox</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5012,7 +5076,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5021,13 +5085,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5036,12 +5100,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1091743517</t>
+          <t>2020464978</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091743517</t>
+          <t>https://m.place.naver.com/place/2020464978</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5058,25 +5122,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코코루네일</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>제이미 네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>see7833@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1390-4270</t>
+          <t>02-701-5602</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
+          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5086,7 +5154,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5107,17 +5175,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5126,12 +5194,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1768871817</t>
+          <t>255540367</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768871817</t>
+          <t>https://m.place.naver.com/place/255540367</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5148,25 +5216,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일더누브</t>
+          <t>루아드네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>hasom0304@naver.com</t>
+          <t>sumr2002@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1452-9237</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 210 1층</t>
+          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdFnxhn</t>
+          <t>http://pf.kakao.com/_xoEbJn/friend</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5201,13 +5273,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R52" t="n">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5216,12 +5288,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1146800442</t>
+          <t>2003721483</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1146800442</t>
+          <t>https://m.place.naver.com/place/2003721483</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5238,29 +5310,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>오드리네일</t>
+          <t>네일샵입니다</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ardusy@naver.com</t>
+          <t>yooawo@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1446-0227</t>
+          <t>0507-1336-5457</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
+          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oudreynail</t>
+          <t>https://www.instagram.com/shopnailshop/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5295,13 +5367,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R53" t="n">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5310,12 +5382,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1497063684</t>
+          <t>954197461</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1497063684</t>
+          <t>https://m.place.naver.com/place/954197461</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5332,29 +5404,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>오렌지나무</t>
+          <t>이촌 네일타임 LG프라자</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>dew517@naver.com</t>
+          <t>blingsea@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1323-2154</t>
+          <t>0507-1498-8612</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로20길 13 1층</t>
+          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5364,7 +5436,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5385,17 +5457,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5404,12 +5476,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1568164546</t>
+          <t>20064911</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568164546</t>
+          <t>https://m.place.naver.com/place/20064911</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5426,29 +5498,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일리모노 이태원점</t>
+          <t>바림</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>nailremono@naver.com</t>
+          <t>shgyfla1127@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1350-6775</t>
+          <t>02-318-2055</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
+          <t>서울특별시 용산구 두텁바위로 73</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailremono</t>
+          <t>http://instagram.com/Barim_nail</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5463,7 +5535,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5483,13 +5555,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>325</v>
+        <v>11</v>
       </c>
       <c r="Q55" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>344</v>
+        <v>13</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5498,12 +5570,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1785734080</t>
+          <t>1862156671</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785734080</t>
+          <t>https://m.place.naver.com/place/1862156671</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5520,29 +5592,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>메종드로르</t>
+          <t>네일헤라</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>stylechosun@naver.com</t>
+          <t>jiyeon6305@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1386-1014</t>
+          <t>0507-1334-2839</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
+          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
+          <t>http://instagram.com/nail.hera</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5577,13 +5649,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R56" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5592,12 +5664,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2029580174</t>
+          <t>1936017804</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029580174</t>
+          <t>https://m.place.naver.com/place/1936017804</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5614,29 +5686,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>버들네일</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>test_golry@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0507-1400-7111</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 147 1층</t>
+          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b_d_nail</t>
+          <t>http://instagram.com/nailclover_yongsan</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5671,13 +5739,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5686,12 +5754,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1127614127</t>
+          <t>32496791</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127614127</t>
+          <t>https://m.place.naver.com/place/32496791</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5708,29 +5776,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>오손내미오</t>
+          <t>유스뷰티</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>playnauts@naver.com</t>
+          <t>jyrif91@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1492-1340</t>
+          <t>0507-1422-3533</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
+          <t>서울특별시 용산구 이태원로20길 21 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oh_sonemio</t>
+          <t>https://www.instagram.com/youthnail/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5765,13 +5833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="R58" t="n">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5780,12 +5848,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1311070929</t>
+          <t>38467380</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311070929</t>
+          <t>https://m.place.naver.com/place/38467380</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5802,25 +5870,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>진주네 네일 효창공원점</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>네일리모노 이태원점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>nailremono@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1403-6610</t>
+          <t>0507-1350-6775</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
+          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jinjunenail</t>
+          <t>https://blog.naver.com/nailremono</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5835,7 +5907,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5855,13 +5927,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="Q59" t="n">
         <v>19</v>
       </c>
       <c r="R59" t="n">
-        <v>98</v>
+        <v>345</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5870,12 +5942,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2056938739</t>
+          <t>1785734080</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056938739</t>
+          <t>https://m.place.naver.com/place/1785734080</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5892,29 +5964,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>청담네일박스 용산점</t>
+          <t>아로하네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>smilehh406@naver.com</t>
+          <t>bbotive@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1325-5985</t>
+          <t>0507-1391-4369</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
+          <t>서울특별시 용산구 이태원로14길 10 2층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheongdam_nailbox</t>
+          <t>http://www.instagram.com/alohanail_chae</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5940,7 +6012,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5949,13 +6021,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5964,12 +6036,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2020464978</t>
+          <t>1264306160</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020464978</t>
+          <t>https://m.place.naver.com/place/1264306160</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -5986,25 +6058,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>투투네일</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>러블리핑크</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>kisever1@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1336-4546</t>
+          <t>02-704-8470</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
+          <t>서울특별시 용산구 청파로45길 27 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/twotwo_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6014,7 +6090,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6035,17 +6111,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6054,12 +6130,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1253759614</t>
+          <t>36901322</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253759614</t>
+          <t>https://m.place.naver.com/place/36901322</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6076,29 +6152,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Breathnailz</t>
+          <t>우아한 네일 살롱</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mooisu@naver.com</t>
+          <t>findmyperfectdays@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0507-1358-6853</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 36 1층</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/wooanail_salon</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6108,7 +6180,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6129,17 +6201,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6148,12 +6220,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1488241394</t>
+          <t>1370902820</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488241394</t>
+          <t>https://m.place.naver.com/place/1370902820</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6170,25 +6242,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>살롱드다한</t>
+          <t>네일가꿈</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ddalkong9830@naver.com</t>
+          <t>hyu3323@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1403-8723</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 257 2층</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
+          <t>http://www.instagram.com/e_nailshop_sj</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6223,13 +6299,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>229</v>
+        <v>474</v>
       </c>
       <c r="Q63" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="R63" t="n">
-        <v>282</v>
+        <v>549</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6238,12 +6314,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1917414808</t>
+          <t>1966796864</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917414808</t>
+          <t>https://m.place.naver.com/place/1966796864</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6260,25 +6336,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>센스</t>
+          <t>춘희손톱</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>showmblog@naver.com</t>
+          <t>chii0216@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1306-7521</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 140-1</t>
+          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/choonheenail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6288,7 +6368,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6309,17 +6389,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>4</v>
+        <v>196</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="R64" t="n">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6328,12 +6408,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1189922870</t>
+          <t>20559743</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189922870</t>
+          <t>https://m.place.naver.com/place/20559743</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6350,29 +6430,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>우아엘뷰티</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>commathemoon_yongsan@naver.com</t>
+          <t>jytgh@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1379-1978</t>
+          <t>0507-1416-0638</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 147 2층</t>
+          <t>서울특별시 용산구 새창로 70 상가-210</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/commathemoon_yongsan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6382,12 +6462,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6403,17 +6483,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6422,12 +6502,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1942029836</t>
+          <t>36629016</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942029836</t>
+          <t>https://m.place.naver.com/place/36629016</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6444,34 +6524,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>수아르네일</t>
+          <t>클리피</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>xxong_11@naver.com</t>
+          <t>seoul2gun@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1354-9689</t>
+          <t>1855-4010</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
+          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/swa_rnail</t>
+          <t>http://pf.kakao.com/_txcJCb</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6492,7 +6572,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6516,12 +6596,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>21568200</t>
+          <t>1546271749</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21568200</t>
+          <t>https://m.place.naver.com/place/1546271749</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6538,29 +6618,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>팁셋 네일 한남점</t>
+          <t>오드리네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>likelife_lovely@naver.com</t>
+          <t>ardusy@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1375-5705</t>
+          <t>0507-1446-0227</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
+          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tipset.seoul/</t>
+          <t>https://www.instagram.com/oudreynail</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6595,13 +6675,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6610,12 +6690,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1409853951</t>
+          <t>1497063684</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409853951</t>
+          <t>https://m.place.naver.com/place/1497063684</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6632,25 +6712,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일바래</t>
+          <t>네일월드</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>naillab20@naver.com</t>
+          <t>daisukitokyo@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02-715-9585</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 214-6 2층</t>
+          <t>서울특별시 용산구 효창원로8길 6</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailbarae_bboong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6660,7 +6744,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6681,17 +6765,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6700,12 +6784,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>835341707</t>
+          <t>1228817187</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/835341707</t>
+          <t>https://m.place.naver.com/place/1228817187</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6722,29 +6806,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일노마드 용산푸르지오써밋점</t>
+          <t>진주네 네일 효창공원점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kjr1212a@naver.com</t>
+          <t>thwjd91070@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1310-3658</t>
+          <t>0507-1403-6610</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
+          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailnomad_</t>
+          <t>https://www.instagram.com/jinjunenail</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6779,13 +6863,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>471</v>
+        <v>79</v>
       </c>
       <c r="Q69" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="R69" t="n">
-        <v>479</v>
+        <v>98</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6794,12 +6878,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1841821386</t>
+          <t>2056938739</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1841821386</t>
+          <t>https://m.place.naver.com/place/2056938739</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6816,29 +6900,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>이촌동 네일타임 삼익상가</t>
+          <t>플로르 네일 이태원점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>yjk2650@naver.com</t>
+          <t>flornail@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>02-749-8604</t>
+          <t>02-790-4182</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
+          <t>서울특별시 용산구 우사단로 47 4층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://youtube.com/@ichon_nail_time</t>
+          <t>https://blog.naver.com/flornail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6853,7 +6937,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6873,13 +6957,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="Q70" t="n">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="R70" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6888,12 +6972,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1281193252</t>
+          <t>32435712</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281193252</t>
+          <t>https://m.place.naver.com/place/32435712</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6910,29 +6994,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>벨르네이쳐</t>
+          <t>다교네일 한남</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dewsang@naver.com</t>
+          <t>oursophie@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1463-0395</t>
+          <t>0507-1339-1024</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pixftn/chat</t>
+          <t>http://pf.kakao.com/_VZqxfG/chat</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6967,13 +7051,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>57</v>
+        <v>338</v>
       </c>
       <c r="Q71" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="R71" t="n">
-        <v>65</v>
+        <v>374</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6982,12 +7066,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2043754067</t>
+          <t>37620988</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043754067</t>
+          <t>https://m.place.naver.com/place/37620988</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7004,29 +7088,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>손톱까끼</t>
+          <t>리라네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sinachoco@naver.com</t>
+          <t>kkmm_0707@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1310-9297</t>
+          <t>02-703-4125</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
+          <t>서울특별시 용산구 원효로41길 23</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kkakki_nail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7036,7 +7120,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7057,17 +7141,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7076,12 +7160,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>20939317</t>
+          <t>1131445662</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20939317</t>
+          <t>https://m.place.naver.com/place/1131445662</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7098,29 +7182,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일의날씨</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>queen77577@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1430-0707</t>
+          <t>070-8882-4343</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 288-2 1층</t>
+          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_nalssi</t>
+          <t>http://www.instagram.com/j_magic_nail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7146,7 +7230,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7155,13 +7239,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>497</v>
+        <v>65</v>
       </c>
       <c r="Q73" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R73" t="n">
-        <v>545</v>
+        <v>89</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7170,12 +7254,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1050641028</t>
+          <t>1438268528</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050641028</t>
+          <t>https://m.place.naver.com/place/1438268528</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7192,25 +7276,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>붙여핸썹</t>
+          <t>무구네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>woowim@naver.com</t>
+          <t>mugunail2025@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1353-2420</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
+          <t>서울특별시 용산구 새창로14길 46 2층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7220,7 +7308,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7241,17 +7329,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7260,12 +7348,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1333965738</t>
+          <t>2093535455</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333965738</t>
+          <t>https://m.place.naver.com/place/2093535455</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7282,12 +7370,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>컬러테일러</t>
+          <t>네일드모네</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ariarisom2@naver.com</t>
+          <t>2860126@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -7295,17 +7383,17 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
+          <t>서울특별시 용산구 독서당로 67 206호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_vpyXn</t>
+          <t>https://www.instagram.com/naildemonet</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7326,7 +7414,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7335,13 +7423,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>319</v>
+        <v>96</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R75" t="n">
-        <v>321</v>
+        <v>99</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7350,12 +7438,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1031854178</t>
+          <t>2062875678</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031854178</t>
+          <t>https://m.place.naver.com/place/2062875678</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7372,29 +7460,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>제이미 네일</t>
+          <t>후암네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>see7833@naver.com</t>
+          <t>dndud7532@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>02-701-5602</t>
+          <t>0507-1301-4091</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
+          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/huam_nail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7404,7 +7492,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7425,17 +7513,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7444,12 +7532,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>255540367</t>
+          <t>2033884779</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/255540367</t>
+          <t>https://m.place.naver.com/place/2033884779</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7466,29 +7554,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>덴드네일한남</t>
+          <t>블랑</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>eunii222@naver.com</t>
+          <t>hg6580@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1378-0596</t>
+          <t>02-790-8798</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eunii222</t>
+          <t>http://instagram.com/nailist_blanc</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7503,7 +7591,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7523,13 +7611,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="Q77" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7538,12 +7626,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1108900148</t>
+          <t>909330706</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108900148</t>
+          <t>https://m.place.naver.com/place/909330706</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7560,25 +7648,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>팝네일 신용산</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>네일바래</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>naillab20@naver.com</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0507-1345-7477</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
+          <t>서울특별시 용산구 원효로 214-6 2층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/popnail_7477</t>
+          <t>http://www.instagram.com/nailbarae_bboong</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7604,7 +7692,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7613,13 +7701,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>316</v>
+        <v>15</v>
       </c>
       <c r="Q78" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>363</v>
+        <v>18</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7628,12 +7716,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1306229960</t>
+          <t>835341707</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306229960</t>
+          <t>https://m.place.naver.com/place/835341707</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7650,24 +7738,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>리라네일</t>
+          <t>티아라네일어반스파</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kkmm_0707@naver.com</t>
+          <t>orora_1976@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>02-703-4125</t>
+          <t>02-790-7882</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 23</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7707,13 +7795,13 @@
         </is>
       </c>
       <c r="P79" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>1</v>
-      </c>
       <c r="R79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7722,12 +7810,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1131445662</t>
+          <t>33213520</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131445662</t>
+          <t>https://m.place.naver.com/place/33213520</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7744,21 +7832,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>네일드모네</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>네일꾼</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>jinheeloo@naver.com</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1407-8585</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 67 206호</t>
+          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildemonet</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7768,7 +7864,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7789,17 +7885,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="R80" t="n">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7808,12 +7904,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>2062875678</t>
+          <t>1395413071</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2062875678</t>
+          <t>https://m.place.naver.com/place/1395413071</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7830,29 +7926,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>네일뮤지엄</t>
+          <t>오손내미오</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>nail-museum@naver.com</t>
+          <t>playnauts@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>070-7543-4009</t>
+          <t>0507-1492-1340</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail-museum</t>
+          <t>https://www.instagram.com/oh_sonemio</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7867,7 +7963,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7887,13 +7983,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>345</v>
+        <v>7</v>
       </c>
       <c r="Q81" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>705</v>
+        <v>7</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7902,12 +7998,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1881584782</t>
+          <t>1311070929</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881584782</t>
+          <t>https://m.place.naver.com/place/1311070929</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -7924,29 +8020,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>네일린</t>
+          <t>몽드메리</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>cookyismylife@naver.com</t>
+          <t>happygirl223@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1344-8515</t>
+          <t>0507-1382-2264</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
+          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naileensalon</t>
+          <t>https://www.instagram.com/monde.mery</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7981,13 +8077,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R82" t="n">
-        <v>1</v>
+        <v>775</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -7996,12 +8092,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1996449351</t>
+          <t>1681006741</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996449351</t>
+          <t>https://m.place.naver.com/place/1681006741</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8018,29 +8114,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>네일가꿈</t>
+          <t>버들네일</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>hyu3323@naver.com</t>
+          <t>test_golry@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1403-8723</t>
+          <t>0507-1400-7111</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
+          <t>서울특별시 용산구 신흥로 147 1층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/e_nailshop_sj</t>
+          <t>https://www.instagram.com/b_d_nail</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8075,13 +8171,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>474</v>
+        <v>24</v>
       </c>
       <c r="Q83" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="R83" t="n">
-        <v>549</v>
+        <v>28</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8090,12 +8186,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1966796864</t>
+          <t>1127614127</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966796864</t>
+          <t>https://m.place.naver.com/place/1127614127</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8112,25 +8208,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>호박손톱</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>appealogad@naver.com</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>070-8882-4343</t>
+          <t>02-794-7958</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
+          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/j_magic_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8140,7 +8240,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8161,17 +8261,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="Q84" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="R84" t="n">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8180,12 +8280,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1438268528</t>
+          <t>35927853</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438268528</t>
+          <t>https://m.place.naver.com/place/35927853</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8202,34 +8302,34 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>클리피</t>
+          <t>네일린</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>seoul2gun@naver.com</t>
+          <t>cookyismylife@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1855-4010</t>
+          <t>0507-1344-8515</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
+          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_txcJCb</t>
+          <t>https://www.instagram.com/naileensalon</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8250,7 +8350,7 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8259,13 +8359,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R85" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8274,12 +8374,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1546271749</t>
+          <t>1996449351</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546271749</t>
+          <t>https://m.place.naver.com/place/1996449351</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8296,29 +8396,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>플리네일 용산해링턴점</t>
+          <t>네일샵베이비</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>lamidays@naver.com</t>
+          <t>zxlixz@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1406-7552</t>
+          <t>0507-1396-4649</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
+          <t>서울특별시 용산구 우사단로2길 19 1층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8328,7 +8428,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8349,17 +8449,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>438</v>
+        <v>38</v>
       </c>
       <c r="Q86" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>453</v>
+        <v>39</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8368,12 +8468,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>2075608465</t>
+          <t>1847608869</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075608465</t>
+          <t>https://m.place.naver.com/place/1847608869</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8390,30 +8490,30 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>뷰리뉼레</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>제이매직네일스</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>tlstnals1010@naver.com</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0507-1389-5562</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 후암로 28 1층</t>
+          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYhSdSVIw</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8439,17 +8539,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8458,12 +8558,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>33277553</t>
+          <t>1222846707</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33277553</t>
+          <t>https://m.place.naver.com/place/1222846707</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8480,29 +8580,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>네일래쉬</t>
+          <t>신용산네일라뜰리에왁싱</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>nailash@naver.com</t>
+          <t>hee_1220@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1371-0008</t>
+          <t>0507-1380-7730</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
+          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailash</t>
+          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8517,7 +8617,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8537,13 +8637,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8552,12 +8652,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1220901153</t>
+          <t>1054108199</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220901153</t>
+          <t>https://m.place.naver.com/place/1054108199</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8574,29 +8674,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>디에고푸스 희네일 이촌점</t>
+          <t>네일래쉬</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jwkang3929@naver.com</t>
+          <t>nailash@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1339-5732</t>
+          <t>0507-1371-0008</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
+          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heenail4345</t>
+          <t>https://blog.naver.com/nailash</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8611,7 +8711,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8631,13 +8731,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="Q89" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="R89" t="n">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8646,12 +8746,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1972424680</t>
+          <t>1220901153</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972424680</t>
+          <t>https://m.place.naver.com/place/1220901153</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8668,34 +8768,30 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>설화미</t>
+          <t>재니네일한남</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>who1who2@naver.com</t>
+          <t>evian___@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0507-1381-4227</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
+          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sulwhami_beauty/</t>
+          <t>http://pf.kakao.com/_eKxmLxl</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8716,7 +8812,7 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8725,13 +8821,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="Q90" t="n">
-        <v>288</v>
+        <v>44</v>
       </c>
       <c r="R90" t="n">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8740,12 +8836,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>33647337</t>
+          <t>1593741438</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33647337</t>
+          <t>https://m.place.naver.com/place/1593741438</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8762,44 +8858,44 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>쵸코네일</t>
+          <t>Breathnailz</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>boong27@naver.com</t>
+          <t>mooisu@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>02-749-7795</t>
+          <t>0507-1358-6853</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
+          <t>서울특별시 용산구 소월로20길 36 1층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8815,17 +8911,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R91" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8834,12 +8930,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>19490178</t>
+          <t>1488241394</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19490178</t>
+          <t>https://m.place.naver.com/place/1488241394</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8856,25 +8952,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>루아드네일</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>쵸코네일</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>boong27@naver.com</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1452-9237</t>
+          <t>02-749-7795</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
+          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xoEbJn/friend</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8889,7 +8989,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8900,7 +9000,7 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8909,13 +9009,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="Q92" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R92" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -8924,12 +9024,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>2003721483</t>
+          <t>19490178</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003721483</t>
+          <t>https://m.place.naver.com/place/19490178</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -8946,39 +9046,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>네일셀레나</t>
+          <t>신데렐라</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>na_young03@naver.com</t>
+          <t>dracura10@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>02-795-6529</t>
+          <t>02-790-3304</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
+          <t>서울특별시 용산구 보광로 61</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zJpfG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8994,22 +9094,22 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>387</v>
+        <v>4</v>
       </c>
       <c r="Q93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R93" t="n">
-        <v>392</v>
+        <v>6</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9018,12 +9118,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>35489351</t>
+          <t>20662540</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35489351</t>
+          <t>https://m.place.naver.com/place/20662540</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9040,29 +9140,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>몽드메리</t>
+          <t>설화미</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>happygirl223@naver.com</t>
+          <t>who1who2@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1382-2264</t>
+          <t>0507-1381-4227</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
+          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/monde.mery</t>
+          <t>https://www.instagram.com/sulwhami_beauty/</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9097,13 +9197,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>761</v>
+        <v>54</v>
       </c>
       <c r="Q94" t="n">
-        <v>14</v>
+        <v>288</v>
       </c>
       <c r="R94" t="n">
-        <v>775</v>
+        <v>342</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9112,12 +9212,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1681006741</t>
+          <t>33647337</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681006741</t>
+          <t>https://m.place.naver.com/place/33647337</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9134,12 +9234,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>우아한 네일 살롱</t>
+          <t>컬러테일러</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>findmyperfectdays@naver.com</t>
+          <t>ariarisom2@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -9147,17 +9247,17 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
+          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wooanail_salon</t>
+          <t>https://pf.kakao.com/_vpyXn</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9178,7 +9278,7 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9187,13 +9287,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>63</v>
+        <v>319</v>
       </c>
       <c r="Q95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
-        <v>64</v>
+        <v>321</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9202,12 +9302,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1370902820</t>
+          <t>1031854178</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370902820</t>
+          <t>https://m.place.naver.com/place/1031854178</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9224,29 +9324,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>제이제이 네일</t>
+          <t>메종드로르</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>stylechosun@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1411-8138</t>
+          <t>0507-1386-1014</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 회나무로 32-3 2층</t>
+          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjjjnail</t>
+          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9281,13 +9381,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9296,12 +9396,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>79017915</t>
+          <t>2029580174</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/79017915</t>
+          <t>https://m.place.naver.com/place/2029580174</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9318,24 +9418,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>네일휴</t>
+          <t>네일퀸</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>white5198@naver.com</t>
+          <t>kfreebaby@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>02-711-3646</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
+          <t>서울특별시 용산구 새창로14길 47</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9375,13 +9471,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9390,12 +9486,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1611951357</t>
+          <t>1023738371</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611951357</t>
+          <t>https://m.place.naver.com/place/1023738371</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9412,34 +9508,30 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>네일슈슈</t>
+          <t>네일더누브</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>brilliant14694@naver.com</t>
+          <t>hasom0304@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>0507-1435-9113</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
+          <t>서울특별시 용산구 원효로 210 1층</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_chouchou_</t>
+          <t>http://pf.kakao.com/_xdFnxhn</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9460,7 +9552,7 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9469,13 +9561,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>461</v>
+        <v>112</v>
       </c>
       <c r="Q98" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="R98" t="n">
-        <v>489</v>
+        <v>131</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9484,12 +9576,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1185094311</t>
+          <t>1146800442</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185094311</t>
+          <t>https://m.place.naver.com/place/1146800442</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9506,29 +9598,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>위위즈 용산점</t>
+          <t>루미가넷네일존 이마트 용산점</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>yigu8@naver.com</t>
+          <t>hyer2986@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1366-3547</t>
+          <t>0507-1401-9470</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
+          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ouiouiznail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9538,7 +9630,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -9559,17 +9651,17 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>509</v>
+        <v>84</v>
       </c>
       <c r="Q99" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="R99" t="n">
-        <v>542</v>
+        <v>86</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9578,12 +9670,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1557214777</t>
+          <t>1619342094</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557214777</t>
+          <t>https://m.place.naver.com/place/1619342094</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9600,34 +9692,30 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>무구네일</t>
+          <t>마고뷰티</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>mugunail2025@naver.com</t>
+          <t>mago_smp@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0507-1353-2420</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 46 2층</t>
+          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://pf.kakao.com/_xjBnAn</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -9648,7 +9736,7 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -9657,13 +9745,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>192</v>
+        <v>119</v>
       </c>
       <c r="Q100" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R100" t="n">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9672,12 +9760,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>2093535455</t>
+          <t>1939429266</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093535455</t>
+          <t>https://m.place.naver.com/place/1939429266</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9694,25 +9782,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>나비네일</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>봉선화물들이다</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>s8h6y@naver.com</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1416-0638</t>
+          <t>02-6203-5478</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가-210</t>
+          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/s8h6y</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9722,12 +9814,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9743,17 +9835,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="Q101" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R101" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9762,12 +9854,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>36629016</t>
+          <t>33618035</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36629016</t>
+          <t>https://m.place.naver.com/place/33618035</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -9784,29 +9876,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>봉선화물들이다</t>
+          <t>글로시블라썸 아이파크몰</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>s8h6y@naver.com</t>
+          <t>irumskin@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>02-6203-5478</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
+          <t>서울특별시 용산구 한강대로23길 55</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s8h6y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9816,12 +9904,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9837,17 +9925,17 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="Q102" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9856,12 +9944,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>33618035</t>
+          <t>1485867849</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33618035</t>
+          <t>https://m.place.naver.com/place/1485867849</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -9878,26 +9966,34 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>묘즈네일</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>네일슈슈</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>brilliant14694@naver.com</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1435-9113</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WxedxgG</t>
+          <t>https://www.instagram.com/nail_chouchou_</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -9918,7 +10014,7 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -9927,13 +10023,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>47</v>
+        <v>461</v>
       </c>
       <c r="Q103" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="R103" t="n">
-        <v>57</v>
+        <v>489</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -9942,12 +10038,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1136869573</t>
+          <t>1185094311</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136869573</t>
+          <t>https://m.place.naver.com/place/1185094311</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -9964,25 +10060,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>비비네일</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>쵸민네일</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>beczzam@naver.com</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>02-749-9134</t>
+          <t>0507-1403-3417</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
+          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/vivinail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9992,7 +10092,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10013,17 +10113,17 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>258</v>
+        <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>303</v>
+        <v>2</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10032,12 +10132,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>21834362</t>
+          <t>1664663384</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21834362</t>
+          <t>https://m.place.naver.com/place/1664663384</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10054,25 +10154,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>리네일</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>켈리하우스 네일샵</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>kellylove09@naver.com</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1421-7880</t>
+          <t>0507-1393-9967</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
+          <t>서울특별시 용산구 보광로 49</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>http://instagram.com/ri_nail7877</t>
+          <t>https://blog.naver.com/kellylove09</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10087,7 +10191,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10103,17 +10207,17 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="Q105" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R105" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10122,12 +10226,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>32244399</t>
+          <t>32875703</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32244399</t>
+          <t>https://m.place.naver.com/place/32875703</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10144,29 +10248,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>루미가넷네일존 이마트 용산점</t>
+          <t>손톱의취향 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>hyer2986@naver.com</t>
+          <t>tastein_nail_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0507-1401-9470</t>
+          <t>0507-1483-0870</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/taste_in_nail_</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10176,7 +10280,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -10197,17 +10301,17 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>84</v>
+        <v>475</v>
       </c>
       <c r="Q106" t="n">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="R106" t="n">
-        <v>86</v>
+        <v>762</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10216,12 +10320,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1619342094</t>
+          <t>2055593167</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619342094</t>
+          <t>https://m.place.naver.com/place/2055593167</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10238,29 +10342,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>마틸다네일M 한남점</t>
+          <t>뷰리뉼레</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>kimnr123@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1412-3082</t>
+          <t>0507-1389-5562</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
+          <t>서울특별시 용산구 후암로 28 1층</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://matildanailshop-mo3.imweb.me/</t>
+          <t>https://toss.place/_lb/TYhSdSVIw</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10270,12 +10374,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -10295,13 +10399,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="Q107" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="R107" t="n">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10310,12 +10414,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1798849933</t>
+          <t>33277553</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798849933</t>
+          <t>https://m.place.naver.com/place/33277553</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10332,25 +10436,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>데코네일</t>
+          <t>네일노마드 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>bambi_showpu@naver.com</t>
+          <t>kjr1212a@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0507-1310-3658</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
+          <t>https://www.instagram.com/nailnomad_</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10385,13 +10493,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>41</v>
+        <v>471</v>
       </c>
       <c r="Q108" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="R108" t="n">
-        <v>123</v>
+        <v>479</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10400,12 +10508,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>36812317</t>
+          <t>1841821386</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36812317</t>
+          <t>https://m.place.naver.com/place/1841821386</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10422,25 +10530,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>아드</t>
+          <t>빛나러오소문제성발관리 용산점</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>adfontes_math@naver.com</t>
+          <t>kknsky73@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0507-1419-6888</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
+          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.th_kr</t>
+          <t>https://youtube.com/@user-gc4wk2yn2b</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10466,7 +10578,7 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -10475,13 +10587,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>52</v>
+        <v>250</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="R109" t="n">
-        <v>52</v>
+        <v>416</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10490,12 +10602,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1700535825</t>
+          <t>1438224262</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700535825</t>
+          <t>https://m.place.naver.com/place/1438224262</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10512,29 +10624,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>진유진네일</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>seoul2816@naver.com</t>
+          <t>milkycoco95@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0507-1416-2081</t>
+          <t>02-749-9134</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 284</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/vivinail</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -10544,7 +10656,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -10565,17 +10677,17 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="Q110" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="R110" t="n">
-        <v>93</v>
+        <v>303</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10584,12 +10696,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>31574498</t>
+          <t>21834362</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31574498</t>
+          <t>https://m.place.naver.com/place/21834362</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10606,35 +10718,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
+          <t>이촌동 네일타임 삼익상가</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>tlstnals1010@naver.com</t>
+          <t>yjk2650@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>02-749-8604</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@ichon_nail_time</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -10655,17 +10771,17 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q111" t="n">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="R111" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10674,12 +10790,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1222846707</t>
+          <t>1281193252</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222846707</t>
+          <t>https://m.place.naver.com/place/1281193252</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10696,21 +10812,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>토마네일</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>덴드네일한남</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>eunii222@naver.com</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1378-0596</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
+          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/to.ma.nail</t>
+          <t>https://blog.naver.com/eunii222</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10725,7 +10849,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -10745,13 +10869,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q112" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R112" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10760,12 +10884,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1701565426</t>
+          <t>1108900148</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701565426</t>
+          <t>https://m.place.naver.com/place/1108900148</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -10782,29 +10906,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>레푸스 용산역점</t>
+          <t>카밍네일</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>refussyss@naver.com</t>
+          <t>daisoblog@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0507-1417-1074</t>
+          <t>0507-1357-1496</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
+          <t>서울특별시 용산구 소월로20길 42 1층</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://youtube.com/@레푸스용산역점</t>
+          <t>https://www.instagram.com/calming_nail</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10839,13 +10963,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>293</v>
+        <v>167</v>
       </c>
       <c r="Q113" t="n">
-        <v>190</v>
+        <v>25</v>
       </c>
       <c r="R113" t="n">
-        <v>483</v>
+        <v>192</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10854,12 +10978,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1153661148</t>
+          <t>1383549813</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153661148</t>
+          <t>https://m.place.naver.com/place/1383549813</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -10876,29 +11000,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>네일프롬다니</t>
+          <t>네일스눕</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>arielisflowery@naver.com</t>
+          <t>yseaeaho@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1349-9460</t>
+          <t>0507-1428-1646</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
+          <t>서울특별시 용산구 한강대로52길 38 202호</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
+          <t>https://www.instagram.com/nail_snoope</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10933,13 +11057,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R114" t="n">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -10948,12 +11072,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1774853191</t>
+          <t>1926501985</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774853191</t>
+          <t>https://m.place.naver.com/place/1926501985</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -10970,34 +11094,34 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>네일디렉터</t>
+          <t>네일셀레나</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>naildirector@naver.com</t>
+          <t>na_young03@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>02-797-8188</t>
+          <t>02-795-6529</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naildirector</t>
+          <t>http://pf.kakao.com/_zJpfG</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -11007,7 +11131,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11018,7 +11142,7 @@
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -11027,13 +11151,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>157</v>
+        <v>387</v>
       </c>
       <c r="Q115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R115" t="n">
-        <v>168</v>
+        <v>392</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11042,12 +11166,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1487195546</t>
+          <t>35489351</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487195546</t>
+          <t>https://m.place.naver.com/place/35489351</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -11064,29 +11188,25 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>손톱의취향 용산푸르지오써밋점</t>
+          <t>더 트리니티 네일</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>tastein_nail_yongsan@naver.com</t>
+          <t>dlfnfl0129@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>0507-1483-0870</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
+          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taste_in_nail_</t>
+          <t>https://www.instagram.com/the_trinity_nail/</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11121,13 +11241,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>475</v>
+        <v>59</v>
       </c>
       <c r="Q116" t="n">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="R116" t="n">
-        <v>762</v>
+        <v>157</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11136,12 +11256,12 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>2055593167</t>
+          <t>1060176123</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055593167</t>
+          <t>https://m.place.naver.com/place/1060176123</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -11158,29 +11278,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>비바이유 한남</t>
+          <t>정원네일</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>enoctobre-@naver.com</t>
+          <t>pretty6144@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0507-1371-9481</t>
+          <t>0507-1406-7118</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
+          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b.by_you</t>
+          <t>http://instagram.com/jungwon_nail_</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11215,13 +11335,13 @@
         </is>
       </c>
       <c r="P117" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>1</v>
-      </c>
       <c r="R117" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11230,12 +11350,12 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>2019591721</t>
+          <t>1935294802</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019591721</t>
+          <t>https://m.place.naver.com/place/1935294802</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">

--- a/naver-place-crawler/results_nail/용산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/용산_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V117"/>
+  <dimension ref="A1:V96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>메종드로르</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>stylechosun@naver.com</t>
-        </is>
-      </c>
+          <t>헤더네일</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1386-1014</t>
+          <t>0507-1464-8960</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/heathernail_102/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +632,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2029580174</t>
+          <t>1399079243</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029580174</t>
+          <t>https://m.place.naver.com/place/1399079243</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일린</t>
+          <t>네일휴</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cookyismylife@naver.com</t>
+          <t>white5198@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1344-8515</t>
+          <t>02-711-3646</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
+          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naileensalon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,7 +707,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -730,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1996449351</t>
+          <t>1611951357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996449351</t>
+          <t>https://m.place.naver.com/place/1611951357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +748,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>정원네일</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>pretty6144@naver.com</t>
-        </is>
-      </c>
+          <t>진유진네일</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1406-7118</t>
+          <t>0507-1416-2081</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
+          <t>서울특별시 용산구 한강대로 284</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/jungwon_nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +776,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,17 +797,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="R4" t="n">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +816,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1935294802</t>
+          <t>31574498</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935294802</t>
+          <t>https://m.place.naver.com/place/31574498</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +838,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일가꿈</t>
+          <t>봉선화물들이다</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hyu3323@naver.com</t>
+          <t>s8h6y@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1403-8723</t>
+          <t>02-6203-5478</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
+          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/e_nailshop_sj</t>
+          <t>https://blog.naver.com/s8h6y</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +875,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>475</v>
+        <v>110</v>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>550</v>
+        <v>125</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +910,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1966796864</t>
+          <t>33618035</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966796864</t>
+          <t>https://m.place.naver.com/place/33618035</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +932,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일꾼</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>jinheeloo@naver.com</t>
-        </is>
-      </c>
+          <t>비바이유 한남</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1407-8585</t>
+          <t>0507-1371-9481</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
+          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/b.by_you</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +960,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,17 +981,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1000,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1395413071</t>
+          <t>2019591721</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395413071</t>
+          <t>https://m.place.naver.com/place/2019591721</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,39 +1022,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>제이미 네일</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>see7833@naver.com</t>
-        </is>
-      </c>
+          <t>클리피</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-701-5602</t>
+          <t>1855-4010</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
+          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_txcJCb</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1082,22 +1066,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1090,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>255540367</t>
+          <t>1546271749</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/255540367</t>
+          <t>https://m.place.naver.com/place/1546271749</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1112,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>오렌지나무</t>
+          <t>청담네일박스 용산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kmaxim2@naver.com</t>
+          <t>smilehh406@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1323-2154</t>
+          <t>0507-1325-5985</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로20길 13 1층</t>
+          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
+          <t>https://www.instagram.com/cheongdam_nailbox</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1160,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1184,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1568164546</t>
+          <t>2020464978</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568164546</t>
+          <t>https://m.place.naver.com/place/2020464978</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,25 +1206,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일퀸</t>
+          <t>네일디렉터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kfreebaby@naver.com</t>
+          <t>naildirector@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>02-797-8188</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 47</t>
+          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/naildirector</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,12 +1238,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,17 +1259,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>168</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1278,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1023738371</t>
+          <t>1487195546</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023738371</t>
+          <t>https://m.place.naver.com/place/1487195546</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1312,29 +1300,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일휴</t>
+          <t>설화미</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>white5198@naver.com</t>
+          <t>who1who2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-711-3646</t>
+          <t>0507-1381-4227</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
+          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sulwhami_beauty/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,7 +1332,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1365,17 +1353,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>288</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>342</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1372,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1611951357</t>
+          <t>33647337</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611951357</t>
+          <t>https://m.place.naver.com/place/33647337</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1406,34 +1394,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>클리피</t>
+          <t>더네일바 2호점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>seoul2gun@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1855-4010</t>
+          <t>0507-1411-8549</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
+          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_txcJCb</t>
+          <t>http://www.instagram.com/thenailbar_hannam</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1454,7 +1442,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1451,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="R11" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1466,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1546271749</t>
+          <t>706072929</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546271749</t>
+          <t>https://m.place.naver.com/place/706072929</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1500,12 +1488,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일드모네</t>
+          <t>살롱드다한</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>themy1226@naver.com</t>
+          <t>ddalkong9830@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1513,12 +1501,12 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 67 206호</t>
+          <t>서울특별시 용산구 원효로 257 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildemonet</t>
+          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1541,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="R12" t="n">
-        <v>101</v>
+        <v>282</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,12 +1556,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2062875678</t>
+          <t>1917414808</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2062875678</t>
+          <t>https://m.place.naver.com/place/1917414808</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1590,29 +1578,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>켈리하우스 네일샵</t>
+          <t>이앤앤</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kellylove09@naver.com</t>
+          <t>eyennail@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1393-9967</t>
+          <t>0507-1316-3771</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 49</t>
+          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kellylove09</t>
+          <t>http://www.instagram.com/_eyennail_</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1627,7 +1615,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1643,17 +1631,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>594</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>1333</v>
       </c>
       <c r="R13" t="n">
-        <v>12</v>
+        <v>1927</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,12 +1650,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>32875703</t>
+          <t>375707328</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32875703</t>
+          <t>https://m.place.naver.com/place/375707328</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1684,34 +1672,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일노마드 용산푸르지오써밋점</t>
+          <t>재니네일한남</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kjr1212a@naver.com</t>
+          <t>evian___@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1310-3658</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
+          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailnomad_</t>
+          <t>http://pf.kakao.com/_eKxmLxl</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1732,7 +1716,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1741,13 +1725,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>471</v>
+        <v>33</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="R14" t="n">
-        <v>479</v>
+        <v>77</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,12 +1740,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1841821386</t>
+          <t>1593741438</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1841821386</t>
+          <t>https://m.place.naver.com/place/1593741438</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1773,34 +1757,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>네일아트재료</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>벨르네이쳐</t>
+          <t>메이크케이</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dewsang@naver.com</t>
+          <t>kbanknow@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1463-0395</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
+          <t>서울특별시 용산구 청파로47길 56 1층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pixftn/chat</t>
+          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1815,7 +1795,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1826,7 +1806,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1835,13 +1815,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,12 +1830,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2043754067</t>
+          <t>2081839313</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043754067</t>
+          <t>https://m.place.naver.com/place/2081839313</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1872,29 +1852,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>제이제이 네일</t>
+          <t>투투네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1411-8138</t>
+          <t>0507-1336-4546</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 회나무로 32-3 2층</t>
+          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjjjnail</t>
+          <t>https://www.instagram.com/twotwo_nail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1929,13 +1909,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,12 +1924,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>79017915</t>
+          <t>1253759614</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/79017915</t>
+          <t>https://m.place.naver.com/place/1253759614</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1966,29 +1946,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>후암네일</t>
+          <t>덴드네일한남</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dndud7532@naver.com</t>
+          <t>eunii222@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1301-4091</t>
+          <t>0507-1378-0596</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
+          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/huam_nail</t>
+          <t>https://blog.naver.com/eunii222</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2003,7 +1983,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2023,13 +2003,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="R17" t="n">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,12 +2018,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2033884779</t>
+          <t>1108900148</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033884779</t>
+          <t>https://m.place.naver.com/place/1108900148</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2060,29 +2040,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>리라네일</t>
+          <t>네일프롬다니</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kkmm_0707@naver.com</t>
+          <t>arielisflowery@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>02-703-4125</t>
+          <t>0507-1349-9460</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 23</t>
+          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2092,7 +2072,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2113,17 +2093,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,12 +2112,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1131445662</t>
+          <t>1774853191</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131445662</t>
+          <t>https://m.place.naver.com/place/1774853191</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2154,29 +2134,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>러블리핑크</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>kisever1@naver.com</t>
-        </is>
-      </c>
+          <t>네일바라기</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>02-704-8470</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 27 2층</t>
+          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_baragi_</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2186,7 +2158,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2207,17 +2179,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="R19" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,12 +2198,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36901322</t>
+          <t>1091743517</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36901322</t>
+          <t>https://m.place.naver.com/place/1091743517</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2248,29 +2220,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>수아르네일</t>
+          <t>손톱의취향 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>xxong_11@naver.com</t>
+          <t>tastein_nail_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1354-9689</t>
+          <t>0507-1483-0870</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/swa_rnail</t>
+          <t>https://www.instagram.com/taste_in_nail_</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2305,13 +2277,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11</v>
+        <v>479</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>290</v>
       </c>
       <c r="R20" t="n">
-        <v>14</v>
+        <v>769</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,12 +2292,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>21568200</t>
+          <t>2055593167</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21568200</t>
+          <t>https://m.place.naver.com/place/2055593167</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2342,29 +2314,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일바이르레</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>l5v2osh@naver.com</t>
-        </is>
-      </c>
+          <t>네일바래</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1312-9470</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
+          <t>서울특별시 용산구 원효로 214-6 2층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_by_lerre</t>
+          <t>http://www.instagram.com/nailbarae_bboong</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2399,13 +2363,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,12 +2378,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>37818863</t>
+          <t>835341707</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37818863</t>
+          <t>https://m.place.naver.com/place/835341707</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2436,25 +2400,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>수 네일</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>qkrqhrdfrn@naver.com</t>
-        </is>
-      </c>
+          <t>버들네일</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1400-7111</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 196 B1층</t>
+          <t>서울특별시 용산구 신흥로 147 1층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qkrqhrdfrn</t>
+          <t>https://www.instagram.com/b_d_nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2469,7 +2433,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2480,7 +2444,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2489,13 +2453,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,12 +2468,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1989007422</t>
+          <t>1127614127</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989007422</t>
+          <t>https://m.place.naver.com/place/1127614127</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2526,34 +2490,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>청담네일박스 용산점</t>
+          <t>네일셀레나</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>smilehh406@naver.com</t>
+          <t>na_young03@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1325-5985</t>
+          <t>02-795-6529</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheongdam_nailbox</t>
+          <t>http://pf.kakao.com/_zJpfG</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2583,13 +2547,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>6</v>
+        <v>389</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>6</v>
+        <v>394</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,12 +2562,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2020464978</t>
+          <t>35489351</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020464978</t>
+          <t>https://m.place.naver.com/place/35489351</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2620,29 +2584,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>더네일바 2호점</t>
+          <t>네일가꿈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>beczzam@naver.com</t>
+          <t>hyu3323@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1411-8549</t>
+          <t>0507-1403-8723</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/thenailbar_hannam</t>
+          <t>http://www.instagram.com/e_nailshop_sj</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2677,13 +2641,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>475</v>
       </c>
       <c r="Q24" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="R24" t="n">
-        <v>94</v>
+        <v>550</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,12 +2656,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>706072929</t>
+          <t>1966796864</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/706072929</t>
+          <t>https://m.place.naver.com/place/1966796864</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2714,29 +2678,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>오드리네일</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ardusy@naver.com</t>
+          <t>jytgh@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1446-0227</t>
+          <t>0507-1416-0638</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
+          <t>서울특별시 용산구 새창로 70 상가-210</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oudreynail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2746,7 +2710,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2767,17 +2731,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,12 +2750,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1497063684</t>
+          <t>36629016</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1497063684</t>
+          <t>https://m.place.naver.com/place/36629016</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2808,24 +2772,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에일린</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>myungae7@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1445-2816</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
+          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2865,13 +2825,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>472</v>
+        <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,12 +2840,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1447531035</t>
+          <t>1222846707</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447531035</t>
+          <t>https://m.place.naver.com/place/1222846707</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2902,29 +2862,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>오손내미오</t>
+          <t>리라네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>playnauts@naver.com</t>
+          <t>kkmm_0707@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1492-1340</t>
+          <t>02-703-4125</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
+          <t>서울특별시 용산구 원효로41길 23</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oh_sonemio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2934,7 +2894,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2955,17 +2915,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,12 +2934,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1311070929</t>
+          <t>1131445662</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311070929</t>
+          <t>https://m.place.naver.com/place/1131445662</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2996,25 +2956,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일바래</t>
+          <t>네일뮤지엄</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>naillab20@naver.com</t>
+          <t>nail-museum@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>070-7543-4009</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 214-6 2층</t>
+          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailbarae_bboong</t>
+          <t>https://blog.naver.com/nail-museum</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3029,7 +2993,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3049,13 +3013,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>15</v>
+        <v>345</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>360</v>
       </c>
       <c r="R28" t="n">
-        <v>18</v>
+        <v>705</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,12 +3028,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>835341707</t>
+          <t>1881584782</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/835341707</t>
+          <t>https://m.place.naver.com/place/1881584782</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3086,30 +3050,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>묘즈네일</t>
+          <t>네일스눕</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>xoxobloggirl@naver.com</t>
+          <t>graceham_@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1428-1646</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
+          <t>서울특별시 용산구 한강대로52길 38 202호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WxedxgG</t>
+          <t>https://www.instagram.com/nail_snoope</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3130,7 +3098,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3139,13 +3107,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3154,12 +3122,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1136869573</t>
+          <t>1926501985</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136869573</t>
+          <t>https://m.place.naver.com/place/1926501985</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3176,29 +3144,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>진유진네일</t>
+          <t>플로르 네일 이태원점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>seoul2816@naver.com</t>
+          <t>flornail@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1416-2081</t>
+          <t>02-790-4182</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 284</t>
+          <t>서울특별시 용산구 우사단로 47 4층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/flornail</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3208,12 +3176,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3229,17 +3197,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="Q30" t="n">
-        <v>52</v>
+        <v>163</v>
       </c>
       <c r="R30" t="n">
-        <v>93</v>
+        <v>281</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,12 +3216,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>31574498</t>
+          <t>32435712</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31574498</t>
+          <t>https://m.place.naver.com/place/32435712</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3270,29 +3238,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>이앤앤</t>
+          <t>센스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>eyennail@naver.com</t>
+          <t>showmblog@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1316-3771</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
+          <t>서울특별시 용산구 만리재로 140-1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_eyennail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3302,7 +3266,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3323,17 +3287,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>593</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>1334</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>1927</v>
+        <v>6</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3342,12 +3306,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>375707328</t>
+          <t>1189922870</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/375707328</t>
+          <t>https://m.place.naver.com/place/1189922870</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3364,34 +3328,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>반디인하우스 용산아이파크몰점</t>
+          <t>팁셋 네일 한남점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bandinhouse_yongsan@naver.com</t>
+          <t>likelife_lovely@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1472-1811</t>
+          <t>0507-1375-5705</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
+          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
+          <t>https://www.instagram.com/tipset.seoul/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3401,7 +3365,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3421,13 +3385,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1250</v>
+        <v>72</v>
       </c>
       <c r="Q32" t="n">
-        <v>189</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1439</v>
+        <v>75</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3436,12 +3400,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1049297184</t>
+          <t>1409853951</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049297184</t>
+          <t>https://m.place.naver.com/place/1409853951</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3458,29 +3422,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>코코루네일</t>
+          <t>후암네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>xanxixxanx@naver.com</t>
+          <t>dndud7532@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1390-4270</t>
+          <t>0507-1301-4091</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
+          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/huam_nail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3515,13 +3479,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3530,12 +3494,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1768871817</t>
+          <t>2033884779</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768871817</t>
+          <t>https://m.place.naver.com/place/2033884779</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3552,29 +3516,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일샵베이비</t>
+          <t>빛나러오소문제성발관리 용산점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>zxlixz@naver.com</t>
+          <t>kknsky73@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1396-4649</t>
+          <t>0507-1419-6888</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로2길 19 1층</t>
+          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@user-gc4wk2yn2b</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3584,7 +3548,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3600,22 +3564,22 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="R34" t="n">
-        <v>39</v>
+        <v>416</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3624,12 +3588,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1847608869</t>
+          <t>1438224262</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847608869</t>
+          <t>https://m.place.naver.com/place/1438224262</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3646,24 +3610,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>쵸민네일</t>
+          <t>제이미 네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>beczzam@naver.com</t>
+          <t>see7833@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1403-3417</t>
+          <t>02-701-5602</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
+          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3703,13 +3667,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3718,12 +3682,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1664663384</t>
+          <t>255540367</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664663384</t>
+          <t>https://m.place.naver.com/place/255540367</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3740,29 +3704,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>마틸다네일M 한남점</t>
+          <t>네일래쉬</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>nailash@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1412-3082</t>
+          <t>0507-1371-0008</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
+          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://matildanailshop-mo3.imweb.me/</t>
+          <t>https://blog.naver.com/nailash</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3797,13 +3761,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="R36" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,12 +3776,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1798849933</t>
+          <t>1220901153</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798849933</t>
+          <t>https://m.place.naver.com/place/1220901153</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3834,29 +3798,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>제이비풋 굳은살&amp;발톱 케어</t>
+          <t>또또네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sunny_0225@naver.com</t>
+          <t>clsald30@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>02-794-8551</t>
+          <t>0507-1354-9049</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
+          <t>서울특별시 용산구 원효로 200 1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ttotto__nail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3866,7 +3830,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3887,17 +3851,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="Q37" t="n">
-        <v>179</v>
+        <v>7</v>
       </c>
       <c r="R37" t="n">
-        <v>529</v>
+        <v>157</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3906,12 +3870,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>12791408</t>
+          <t>2020672159</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12791408</t>
+          <t>https://m.place.naver.com/place/2020672159</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3928,29 +3892,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>덴드네일한남</t>
+          <t>네일의날씨</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>eunii222@naver.com</t>
+          <t>queen77577@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1378-0596</t>
+          <t>0507-1430-0707</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
+          <t>서울특별시 용산구 한강대로 288-2 1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eunii222</t>
+          <t>http://instagram.com/nail_nalssi</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3965,7 +3929,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3976,7 +3940,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3985,13 +3949,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>124</v>
+        <v>497</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="R38" t="n">
-        <v>146</v>
+        <v>545</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4000,12 +3964,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1108900148</t>
+          <t>1050641028</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108900148</t>
+          <t>https://m.place.naver.com/place/1050641028</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4022,34 +3986,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>쵸코네일</t>
+          <t>춘희손톱</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>boong27@naver.com</t>
+          <t>chii0216@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>02-749-7795</t>
+          <t>0507-1306-7521</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
+          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>http://instagram.com/choonheenail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4059,7 +4023,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4079,13 +4043,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="R39" t="n">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4094,12 +4058,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>19490178</t>
+          <t>20559743</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19490178</t>
+          <t>https://m.place.naver.com/place/20559743</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4116,44 +4080,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일월드</t>
+          <t>반디인하우스 용산아이파크몰점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>daisukitokyo@naver.com</t>
+          <t>bandinhouse_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>02-715-9585</t>
+          <t>0507-1472-1811</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6</t>
+          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4169,17 +4133,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1253</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1442</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4188,12 +4152,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1228817187</t>
+          <t>1049297184</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228817187</t>
+          <t>https://m.place.naver.com/place/1049297184</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4210,29 +4174,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일래쉬</t>
+          <t>아드</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nailash@naver.com</t>
+          <t>adfontes_math@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1371-0008</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
+          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailash</t>
+          <t>https://www.instagram.com/a.th_kr</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,7 +4207,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4267,13 +4227,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="Q41" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4282,12 +4242,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1220901153</t>
+          <t>1700535825</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220901153</t>
+          <t>https://m.place.naver.com/place/1700535825</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4304,12 +4264,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일바라기</t>
+          <t>묘즈네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sydy8585@naver.com</t>
+          <t>xoxobloggirl@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4317,17 +4277,17 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
+          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_baragi_</t>
+          <t>http://pf.kakao.com/_WxedxgG</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4348,7 +4308,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4357,13 +4317,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R42" t="n">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4372,12 +4332,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1091743517</t>
+          <t>1136869573</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091743517</t>
+          <t>https://m.place.naver.com/place/1136869573</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4394,29 +4354,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일샵입니다</t>
+          <t>팝네일 신용산</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>yooawo@naver.com</t>
+          <t>mhhj951026@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1336-5457</t>
+          <t>0507-1345-7477</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
+          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shopnailshop/</t>
+          <t>https://www.instagram.com/popnail_7477</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4442,7 +4402,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4451,13 +4411,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>171</v>
+        <v>316</v>
       </c>
       <c r="Q43" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="R43" t="n">
-        <v>206</v>
+        <v>363</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4466,12 +4426,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>954197461</t>
+          <t>1306229960</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/954197461</t>
+          <t>https://m.place.naver.com/place/1306229960</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4488,29 +4448,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일뮤지엄</t>
+          <t>위위즈 용산점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nail-museum@naver.com</t>
+          <t>yigu8@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>070-7543-4009</t>
+          <t>0507-1366-3547</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
+          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail-museum</t>
+          <t>https://www.instagram.com/ouiouiznail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4525,7 +4485,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4545,13 +4505,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>345</v>
+        <v>509</v>
       </c>
       <c r="Q44" t="n">
-        <v>360</v>
+        <v>33</v>
       </c>
       <c r="R44" t="n">
-        <v>705</v>
+        <v>542</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4560,12 +4520,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1881584782</t>
+          <t>1557214777</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881584782</t>
+          <t>https://m.place.naver.com/place/1557214777</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4582,35 +4542,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>tlstnals1010@naver.com</t>
-        </is>
-      </c>
+          <t>다교네일 한남</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1339-1024</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_VZqxfG/chat</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4626,22 +4586,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>374</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,12 +4610,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1222846707</t>
+          <t>37620988</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222846707</t>
+          <t>https://m.place.naver.com/place/37620988</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4672,25 +4632,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>오나네일</t>
+          <t>디에고푸스 희네일 이촌점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>jwkang3929@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1339-5732</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
+          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/o.nnail</t>
+          <t>https://www.instagram.com/heenail4345</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4725,13 +4689,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="R46" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,12 +4704,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1549497362</t>
+          <t>1972424680</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549497362</t>
+          <t>https://m.place.naver.com/place/1972424680</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4762,25 +4726,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>살롱드다한</t>
+          <t>카밍네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ddalkong9830@naver.com</t>
+          <t>daisoblog@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1357-1496</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 257 2층</t>
+          <t>서울특별시 용산구 소월로20길 42 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/calming_nail</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4815,13 +4783,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="Q47" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="R47" t="n">
-        <v>282</v>
+        <v>192</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4830,12 +4798,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1917414808</t>
+          <t>1383549813</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917414808</t>
+          <t>https://m.place.naver.com/place/1383549813</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4852,34 +4820,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>버들네일</t>
+          <t>마고뷰티</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>mago_smp@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1400-7111</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 147 1층</t>
+          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b_d_nail</t>
+          <t>https://pf.kakao.com/_xjBnAn</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4900,7 +4864,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4909,13 +4873,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="R48" t="n">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4924,12 +4888,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1127614127</t>
+          <t>1939429266</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127614127</t>
+          <t>https://m.place.naver.com/place/1939429266</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4946,25 +4910,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>붙여핸썹</t>
+          <t>이촌동 네일타임 삼익상가</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>woowim@naver.com</t>
+          <t>yjk2650@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>02-749-8604</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@ichon_nail_time</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4974,7 +4942,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4995,17 +4963,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5014,12 +4982,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1333965738</t>
+          <t>1281193252</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333965738</t>
+          <t>https://m.place.naver.com/place/1281193252</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5036,29 +5004,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>바림</t>
+          <t>이촌 네일타임 LG프라자</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>virus8163@naver.com</t>
+          <t>blingsea@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>02-318-2055</t>
+          <t>0507-1498-8612</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로 73</t>
+          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://instagram.com/Barim_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5068,7 +5036,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5089,17 +5057,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R50" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5108,12 +5076,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1862156671</t>
+          <t>20064911</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862156671</t>
+          <t>https://m.place.naver.com/place/20064911</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5130,29 +5098,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>리네일</t>
+          <t>러블리핑크</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>dlwjddo7053@naver.com</t>
+          <t>kisever1@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1421-7880</t>
+          <t>02-704-8470</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
+          <t>서울특별시 용산구 청파로45길 27 2층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://instagram.com/ri_nail7877</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5162,7 +5130,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5183,17 +5151,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="Q51" t="n">
         <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,12 +5170,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>32244399</t>
+          <t>36901322</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32244399</t>
+          <t>https://m.place.naver.com/place/36901322</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5224,34 +5192,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>위위즈 용산점</t>
+          <t>마틸다네일M 한남점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>yigu8@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1366-3547</t>
+          <t>0507-1412-3082</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
+          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ouiouiznail</t>
+          <t>https://matildanailshop-mo3.imweb.me/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5261,7 +5229,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5281,13 +5249,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>509</v>
+        <v>92</v>
       </c>
       <c r="Q52" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="R52" t="n">
-        <v>542</v>
+        <v>111</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5296,12 +5264,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1557214777</t>
+          <t>1798849933</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557214777</t>
+          <t>https://m.place.naver.com/place/1798849933</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5318,29 +5286,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일셀레나</t>
+          <t>벨르네이쳐</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>na_young03@naver.com</t>
+          <t>dewsang@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>02-795-6529</t>
+          <t>0507-1463-0395</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
+          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zJpfG</t>
+          <t>http://pf.kakao.com/_pixftn/chat</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5375,13 +5343,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>388</v>
+        <v>59</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R53" t="n">
-        <v>393</v>
+        <v>67</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5390,12 +5358,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>35489351</t>
+          <t>2043754067</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35489351</t>
+          <t>https://m.place.naver.com/place/2043754067</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5412,34 +5380,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
+          <t>네일더누브</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>j2lang@naver.com</t>
+          <t>hasom0304@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1345-4179</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
+          <t>서울특별시 용산구 원효로 210 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://instagram.com/today_nail_ichon</t>
+          <t>http://pf.kakao.com/_xdFnxhn</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5460,7 +5424,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5469,13 +5433,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>293</v>
+        <v>112</v>
       </c>
       <c r="Q54" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="R54" t="n">
-        <v>300</v>
+        <v>131</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,12 +5448,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>21038031</t>
+          <t>1146800442</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21038031</t>
+          <t>https://m.place.naver.com/place/1146800442</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5506,25 +5470,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>아드</t>
+          <t>네일리모노 이태원점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>adfontes_math@naver.com</t>
+          <t>nailremono@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1350-6775</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
+          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.th_kr</t>
+          <t>https://blog.naver.com/nailremono</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5539,7 +5507,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5559,13 +5527,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>52</v>
+        <v>326</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R55" t="n">
-        <v>52</v>
+        <v>345</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5574,12 +5542,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1700535825</t>
+          <t>1785734080</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700535825</t>
+          <t>https://m.place.naver.com/place/1785734080</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5596,24 +5564,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>루미가넷네일존 이마트 용산점</t>
+          <t>붙여핸썹</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>hyer2986@naver.com</t>
+          <t>woowim@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1401-9470</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
+          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5653,13 +5617,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5668,12 +5632,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1619342094</t>
+          <t>1333965738</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619342094</t>
+          <t>https://m.place.naver.com/place/1333965738</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5690,29 +5654,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>신용산네일라뜰리에왁싱</t>
+          <t>네일슈슈</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>hee_1220@naver.com</t>
+          <t>brilliant14694@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1380-7730</t>
+          <t>0507-1435-9113</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
+          <t>https://www.instagram.com/nail_chouchou_</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5747,13 +5711,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="R57" t="n">
-        <v>2</v>
+        <v>489</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5762,12 +5726,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1054108199</t>
+          <t>1185094311</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054108199</t>
+          <t>https://m.place.naver.com/place/1185094311</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5784,29 +5748,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>블랑</t>
+          <t>정원네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>hg6580@naver.com</t>
+          <t>pretty6144@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02-790-8798</t>
+          <t>0507-1406-7118</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
+          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailist_blanc</t>
+          <t>http://instagram.com/jungwon_nail_</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5841,13 +5805,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5856,12 +5820,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>909330706</t>
+          <t>1935294802</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/909330706</t>
+          <t>https://m.place.naver.com/place/1935294802</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5878,29 +5842,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>신데렐라</t>
+          <t>네일테라피은</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dracura10@naver.com</t>
+          <t>mountain__sun@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>02-790-3304</t>
+          <t>0507-1379-8496</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 61</t>
+          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailtherapyeun</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5910,7 +5874,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5931,17 +5895,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>4</v>
+        <v>203</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R59" t="n">
-        <v>6</v>
+        <v>212</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5950,12 +5914,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>20662540</t>
+          <t>1180134699</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20662540</t>
+          <t>https://m.place.naver.com/place/1180134699</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5972,29 +5936,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>몽드메리</t>
+          <t>오나네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>happygirl223@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1382-2264</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
+          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/monde.mery</t>
+          <t>https://www.instagram.com/o.nnail</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6029,13 +5989,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>761</v>
+        <v>133</v>
       </c>
       <c r="Q60" t="n">
         <v>14</v>
       </c>
       <c r="R60" t="n">
-        <v>775</v>
+        <v>147</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6044,12 +6004,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1681006741</t>
+          <t>1549497362</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681006741</t>
+          <t>https://m.place.naver.com/place/1549497362</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6066,29 +6026,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>프로네일</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>sonvely89@naver.com</t>
-        </is>
-      </c>
+          <t>손톱까끼</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1421-1525</t>
+          <t>0507-1310-9297</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
+          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/itaewonpronail/</t>
+          <t>https://www.instagram.com/kkakki_nail/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6123,13 +6079,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="Q61" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="R61" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,12 +6094,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>13028002</t>
+          <t>20939317</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13028002</t>
+          <t>https://m.place.naver.com/place/20939317</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6160,29 +6116,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>플리네일 용산해링턴점</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>lamidays@naver.com</t>
-        </is>
-      </c>
+          <t>네일린</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1406-7552</t>
+          <t>0507-1344-8515</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
+          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/naileensalon</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6217,13 +6169,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>454</v>
+        <v>2</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,12 +6184,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2075608465</t>
+          <t>1996449351</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075608465</t>
+          <t>https://m.place.naver.com/place/1996449351</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6254,29 +6206,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>우아엘뷰티</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>commathemoon_yongsan@naver.com</t>
-        </is>
-      </c>
+          <t>바림</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1379-1978</t>
+          <t>02-318-2055</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 147 2층</t>
+          <t>서울특별시 용산구 두텁바위로 73</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/commathemoon_yongsan</t>
+          <t>http://instagram.com/Barim_nail</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6291,7 +6239,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6311,13 +6259,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="Q63" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>127</v>
+        <v>13</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,12 +6274,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1942029836</t>
+          <t>1862156671</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942029836</t>
+          <t>https://m.place.naver.com/place/1862156671</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6348,29 +6296,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>카밍네일</t>
+          <t>진주네 네일 효창공원점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>daisoblog@naver.com</t>
+          <t>thwjd91070@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1357-1496</t>
+          <t>0507-1403-6610</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 42 1층</t>
+          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/calming_nail</t>
+          <t>https://www.instagram.com/jinjunenail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6405,13 +6353,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="Q64" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="R64" t="n">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,12 +6368,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1383549813</t>
+          <t>2056938739</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383549813</t>
+          <t>https://m.place.naver.com/place/2056938739</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6442,29 +6390,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>플로르 네일 이태원점</t>
+          <t>몽드메리</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>flornail@naver.com</t>
+          <t>happygirl223@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>02-790-4182</t>
+          <t>0507-1382-2264</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로 47 4층</t>
+          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/flornail</t>
+          <t>https://www.instagram.com/monde.mery</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6479,7 +6427,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6499,13 +6447,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>117</v>
+        <v>761</v>
       </c>
       <c r="Q65" t="n">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="R65" t="n">
-        <v>280</v>
+        <v>775</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6514,12 +6462,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>32435712</t>
+          <t>1681006741</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32435712</t>
+          <t>https://m.place.naver.com/place/1681006741</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6536,39 +6484,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>뷰리뉼레</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>kimnr123@naver.com</t>
-        </is>
-      </c>
+          <t>토마네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1389-5562</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 후암로 28 1층</t>
+          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYhSdSVIw</t>
+          <t>https://www.instagram.com/to.ma.nail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6593,13 +6533,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R66" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,12 +6548,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>33277553</t>
+          <t>1701565426</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33277553</t>
+          <t>https://m.place.naver.com/place/1701565426</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6630,30 +6570,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일더누브</t>
+          <t>메종드로르</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>hasom0304@naver.com</t>
+          <t>stylechosun@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1386-1014</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 210 1층</t>
+          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdFnxhn</t>
+          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6674,7 +6618,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6683,13 +6627,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="Q67" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6698,12 +6642,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1146800442</t>
+          <t>2029580174</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1146800442</t>
+          <t>https://m.place.naver.com/place/2029580174</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6720,29 +6664,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>이촌 네일타임 LG프라자</t>
+          <t>네일삼각지</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>blingsea@naver.com</t>
+          <t>nailsamgakji@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1498-8612</t>
+          <t>0507-1316-2792</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
+          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_samgakji</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6752,7 +6696,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6768,22 +6712,22 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6792,12 +6736,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>20064911</t>
+          <t>1872968588</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20064911</t>
+          <t>https://m.place.naver.com/place/1872968588</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6814,34 +6758,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>무구네일</t>
+          <t>쿠로키네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>mugunail2025@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1353-2420</t>
+          <t>0507-1481-2893</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 46 2층</t>
+          <t>서울특별시 용산구 신흥로 19-2 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://pf.kakao.com/_xaxcxeBG</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6862,7 +6806,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6871,13 +6815,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="Q69" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="R69" t="n">
-        <v>235</v>
+        <v>165</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6886,12 +6830,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2093535455</t>
+          <t>1723956505</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093535455</t>
+          <t>https://m.place.naver.com/place/1723956505</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6908,25 +6852,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일클로버</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>bongbong323@naver.com</t>
-        </is>
-      </c>
+          <t>네일꾼</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1407-8585</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
+          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailclover_yongsan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6936,7 +6880,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6957,17 +6901,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="R70" t="n">
-        <v>9</v>
+        <v>162</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6976,12 +6920,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>32496791</t>
+          <t>1395413071</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32496791</t>
+          <t>https://m.place.naver.com/place/1395413071</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6998,29 +6942,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>티아라네일어반스파</t>
+          <t>우아엘뷰티</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>esthii@naver.com</t>
+          <t>commathemoon_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>02-790-7882</t>
+          <t>0507-1379-1978</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
+          <t>서울특별시 용산구 효창원로 147 2층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/commathemoon_yongsan</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7030,12 +6974,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7051,17 +6995,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7070,12 +7014,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>33213520</t>
+          <t>1942029836</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33213520</t>
+          <t>https://m.place.naver.com/place/1942029836</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7092,25 +7036,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>더 트리니티 네일</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>dlfnfl0129@naver.com</t>
-        </is>
-      </c>
+          <t>네일퀸</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
+          <t>서울특별시 용산구 새창로14길 47</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the_trinity_nail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7120,7 +7060,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7141,17 +7081,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="Q72" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7160,12 +7100,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1060176123</t>
+          <t>1023738371</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060176123</t>
+          <t>https://m.place.naver.com/place/1023738371</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7182,34 +7122,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>디에고푸스 희네일 이촌점</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>jwkang3929@naver.com</t>
-        </is>
-      </c>
+          <t>컬러테일러</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0507-1339-5732</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
+          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heenail4345</t>
+          <t>https://pf.kakao.com/_vpyXn</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7230,7 +7162,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7239,13 +7171,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="Q73" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>157</v>
+        <v>322</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7254,12 +7186,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1972424680</t>
+          <t>1031854178</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972424680</t>
+          <t>https://m.place.naver.com/place/1031854178</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7276,30 +7208,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>마고뷰티</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>mago_smp@naver.com</t>
-        </is>
-      </c>
+          <t>네일드모네</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
+          <t>서울특별시 용산구 독서당로 67 206호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xjBnAn</t>
+          <t>https://www.instagram.com/naildemonet</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7320,7 +7248,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7329,13 +7257,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="Q74" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7344,12 +7272,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1939429266</t>
+          <t>2062875678</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939429266</t>
+          <t>https://m.place.naver.com/place/2062875678</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7366,29 +7294,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>팝네일 신용산</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>mhhj951026@naver.com</t>
-        </is>
-      </c>
+          <t>플리네일 용산해링턴점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1345-7477</t>
+          <t>0507-1406-7552</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
+          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/popnail_7477</t>
+          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7414,7 +7338,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7423,13 +7347,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>316</v>
+        <v>439</v>
       </c>
       <c r="Q75" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="R75" t="n">
-        <v>363</v>
+        <v>454</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7438,12 +7362,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1306229960</t>
+          <t>2075608465</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306229960</t>
+          <t>https://m.place.naver.com/place/2075608465</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7460,29 +7384,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>유스뷰티</t>
+          <t>레푸스 용산역점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jyrif91@naver.com</t>
+          <t>refussyss@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1422-3533</t>
+          <t>0507-1417-1074</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로20길 21 1층</t>
+          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youthnail/</t>
+          <t>https://youtube.com/@레푸스용산역점</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7517,13 +7441,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4</v>
+        <v>293</v>
       </c>
       <c r="Q76" t="n">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="R76" t="n">
-        <v>121</v>
+        <v>484</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7532,12 +7456,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>38467380</t>
+          <t>1153661148</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38467380</t>
+          <t>https://m.place.naver.com/place/1153661148</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7554,39 +7478,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>쿠로키네일</t>
+          <t>네일월드</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>daisukitokyo@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1481-2893</t>
+          <t>02-715-9585</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 19-2 1층</t>
+          <t>서울특별시 용산구 효창원로8길 6</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xaxcxeBG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7602,22 +7526,22 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7626,12 +7550,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1723956505</t>
+          <t>1228817187</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723956505</t>
+          <t>https://m.place.naver.com/place/1228817187</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7648,29 +7572,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>진주네 네일 효창공원점</t>
+          <t>데코네일</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>thwjd91070@naver.com</t>
+          <t>shwimlove@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0507-1403-6610</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
+          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jinjunenail</t>
+          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7705,13 +7625,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="Q78" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="R78" t="n">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7720,12 +7640,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2056938739</t>
+          <t>36812317</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056938739</t>
+          <t>https://m.place.naver.com/place/36812317</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7742,34 +7662,34 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>루아드네일</t>
+          <t>프로네일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>sumr2002@naver.com</t>
+          <t>sonvely89@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1452-9237</t>
+          <t>0507-1421-1525</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
+          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xoEbJn/friend</t>
+          <t>http://www.instagram.com/itaewonpronail/</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7790,7 +7710,7 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7799,13 +7719,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="Q79" t="n">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="R79" t="n">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7814,12 +7734,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>2003721483</t>
+          <t>13028002</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003721483</t>
+          <t>https://m.place.naver.com/place/13028002</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7836,29 +7756,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>네일삼각지</t>
+          <t>Breathnailz</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>nailsamgakji@naver.com</t>
+          <t>mooisu@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1316-2792</t>
+          <t>0507-1358-6853</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
+          <t>서울특별시 용산구 소월로20길 36 1층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_samgakji</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7868,7 +7788,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7884,22 +7804,22 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R80" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7908,12 +7828,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1872968588</t>
+          <t>1488241394</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1872968588</t>
+          <t>https://m.place.naver.com/place/1488241394</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7930,29 +7850,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Breathnailz</t>
+          <t>리네일</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>mooisu@naver.com</t>
+          <t>dlwjddo7053@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1358-6853</t>
+          <t>0507-1421-7880</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 36 1층</t>
+          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/ri_nail7877</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7962,7 +7882,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7983,17 +7903,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q81" t="n">
         <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8002,12 +7922,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1488241394</t>
+          <t>32244399</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488241394</t>
+          <t>https://m.place.naver.com/place/32244399</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8024,39 +7944,35 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>비바이유 한남</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>enoctobre-@naver.com</t>
-        </is>
-      </c>
+          <t>뷰리뉼레</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1371-9481</t>
+          <t>0507-1389-5562</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
+          <t>서울특별시 용산구 후암로 28 1층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/b.by_you</t>
+          <t>https://toss.place/_lb/TYhSdSVIw</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8081,13 +7997,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R82" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8096,12 +8012,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2019591721</t>
+          <t>33277553</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019591721</t>
+          <t>https://m.place.naver.com/place/33277553</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8113,30 +8029,30 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>네일아트재료</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>메이크케이</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>kbanknow@naver.com</t>
-        </is>
-      </c>
+          <t>루아드네일</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1452-9237</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 56 1층</t>
+          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
+          <t>http://pf.kakao.com/_xoEbJn/friend</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8151,7 +8067,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8162,7 +8078,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8171,13 +8087,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8186,12 +8102,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>2081839313</t>
+          <t>2003721483</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2081839313</t>
+          <t>https://m.place.naver.com/place/2003721483</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8208,29 +8124,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>설화미</t>
+          <t>네일헤라</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>who1who2@naver.com</t>
+          <t>heranaillash@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1381-4227</t>
+          <t>0507-1334-2839</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
+          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sulwhami_beauty/</t>
+          <t>http://instagram.com/nail.hera</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8265,13 +8181,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="Q84" t="n">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="R84" t="n">
-        <v>342</v>
+        <v>8</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8280,12 +8196,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>33647337</t>
+          <t>1936017804</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33647337</t>
+          <t>https://m.place.naver.com/place/1936017804</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8302,29 +8218,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>아로하네일</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>bbotive@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1391-4369</t>
+          <t>070-8882-4343</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로14길 10 2층</t>
+          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/alohanail_chae</t>
+          <t>http://www.instagram.com/j_magic_nail</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8359,13 +8275,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Q85" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="R85" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8374,12 +8290,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1264306160</t>
+          <t>1438268528</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264306160</t>
+          <t>https://m.place.naver.com/place/1438268528</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8396,29 +8312,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>tlstnals1010@naver.com</t>
-        </is>
-      </c>
+          <t>코코루네일</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>070-8882-4343</t>
+          <t>0507-1390-4270</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
+          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/j_magic_nail</t>
+          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8453,13 +8365,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="Q86" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8468,12 +8380,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1438268528</t>
+          <t>1768871817</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438268528</t>
+          <t>https://m.place.naver.com/place/1768871817</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8490,29 +8402,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>춘희손톱</t>
+          <t>네일샵입니다</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>chii0216@naver.com</t>
+          <t>yooawo@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1306-7521</t>
+          <t>0507-1336-5457</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
+          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>http://instagram.com/choonheenail</t>
+          <t>https://www.instagram.com/shopnailshop/</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8547,13 +8459,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="Q87" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="R87" t="n">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8562,12 +8474,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>20559743</t>
+          <t>954197461</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20559743</t>
+          <t>https://m.place.naver.com/place/954197461</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8584,29 +8496,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>네일디렉터</t>
+          <t>제이비풋 굳은살&amp;발톱 케어</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>naildirector@naver.com</t>
+          <t>sunny_0225@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>02-797-8188</t>
+          <t>02-794-8551</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naildirector</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8616,12 +8528,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8637,17 +8549,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>157</v>
+        <v>350</v>
       </c>
       <c r="Q88" t="n">
-        <v>11</v>
+        <v>179</v>
       </c>
       <c r="R88" t="n">
-        <v>168</v>
+        <v>529</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8656,12 +8568,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1487195546</t>
+          <t>12791408</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487195546</t>
+          <t>https://m.place.naver.com/place/12791408</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8678,29 +8590,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>이촌동 네일타임 삼익상가</t>
+          <t>네일노마드 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>yjk2650@naver.com</t>
+          <t>kjr1212a@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>02-749-8604</t>
+          <t>0507-1310-3658</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://youtube.com/@ichon_nail_time</t>
+          <t>https://www.instagram.com/nailnomad_</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8735,13 +8647,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>128</v>
+        <v>471</v>
       </c>
       <c r="Q89" t="n">
-        <v>122</v>
+        <v>8</v>
       </c>
       <c r="R89" t="n">
-        <v>250</v>
+        <v>479</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8750,12 +8662,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1281193252</t>
+          <t>1841821386</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281193252</t>
+          <t>https://m.place.naver.com/place/1841821386</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8772,29 +8684,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>네일헤라</t>
+          <t>무구네일</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jiyeon6305@naver.com</t>
+          <t>mugunail2025@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1334-2839</t>
+          <t>0507-1353-2420</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
+          <t>서울특별시 용산구 새창로14길 46 2층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.hera</t>
+          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8829,13 +8741,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="Q90" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="R90" t="n">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8844,12 +8756,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1936017804</t>
+          <t>2093535455</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1936017804</t>
+          <t>https://m.place.naver.com/place/2093535455</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8866,29 +8778,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>네일테라피은</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>mountain__sun@naver.com</t>
-        </is>
-      </c>
+          <t>아로하네일</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1379-8496</t>
+          <t>0507-1391-4369</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
+          <t>서울특별시 용산구 이태원로14길 10 2층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailtherapyeun</t>
+          <t>http://www.instagram.com/alohanail_chae</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8923,13 +8831,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>203</v>
+        <v>75</v>
       </c>
       <c r="Q91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8938,12 +8846,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1180134699</t>
+          <t>1264306160</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180134699</t>
+          <t>https://m.place.naver.com/place/1264306160</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8960,29 +8868,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>봉선화물들이다</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>s8h6y@naver.com</t>
-        </is>
-      </c>
+          <t>에일린</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>02-6203-5478</t>
+          <t>0507-1445-2816</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
+          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s8h6y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8992,12 +8896,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9013,17 +8917,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>110</v>
+        <v>394</v>
       </c>
       <c r="Q92" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="R92" t="n">
-        <v>125</v>
+        <v>471</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9032,12 +8936,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>33618035</t>
+          <t>1447531035</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33618035</t>
+          <t>https://m.place.naver.com/place/1447531035</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9054,12 +8958,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>데코네일</t>
+          <t>수 네일</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>shwimlove@naver.com</t>
+          <t>qkrqhrdfrn@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -9067,12 +8971,12 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
+          <t>서울특별시 용산구 만리재로 196 B1층</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
+          <t>https://blog.naver.com/qkrqhrdfrn</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9087,7 +8991,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9098,7 +9002,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9107,13 +9011,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q93" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="R93" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9122,12 +9026,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>36812317</t>
+          <t>1989007422</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36812317</t>
+          <t>https://m.place.naver.com/place/1989007422</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9144,29 +9048,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>또또네일</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>clsald30@naver.com</t>
-        </is>
-      </c>
+          <t>오드리네일</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1354-9049</t>
+          <t>0507-1446-0227</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 200 1층</t>
+          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ttotto__nail</t>
+          <t>https://www.instagram.com/oudreynail</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9201,13 +9101,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="Q94" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>157</v>
+        <v>30</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9216,12 +9116,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>2020672159</t>
+          <t>1497063684</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020672159</t>
+          <t>https://m.place.naver.com/place/1497063684</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9238,29 +9138,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>빛나러오소문제성발관리 용산점</t>
+          <t>루미가넷네일존 이마트 용산점</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>kknsky73@naver.com</t>
+          <t>hyer2986@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1419-6888</t>
+          <t>0507-1401-9470</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
+          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://youtube.com/@user-gc4wk2yn2b</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9270,7 +9170,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9286,22 +9186,22 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>250</v>
+        <v>84</v>
       </c>
       <c r="Q95" t="n">
-        <v>166</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
-        <v>416</v>
+        <v>86</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9310,12 +9210,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1438224262</t>
+          <t>1619342094</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438224262</t>
+          <t>https://m.place.naver.com/place/1619342094</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9332,29 +9232,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>나비네일</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>jytgh@naver.com</t>
-        </is>
-      </c>
+          <t>오늘도네일</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1416-0638</t>
+          <t>0507-1345-4179</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가-210</t>
+          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/today_nail_ichon</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9364,7 +9260,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9385,17 +9281,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>5</v>
+        <v>293</v>
       </c>
       <c r="Q96" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R96" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9404,1961 +9300,15 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>36629016</t>
+          <t>21038031</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36629016</t>
+          <t>https://m.place.naver.com/place/21038031</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>손톱의취향 용산푸르지오써밋점</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>tastein_nail_yongsan@naver.com</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>0507-1483-0870</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/taste_in_nail_</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P97" t="n">
-        <v>479</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>290</v>
-      </c>
-      <c r="R97" t="n">
-        <v>769</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>2055593167</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2055593167</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>네일스눕</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>yseaeaho@naver.com</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>0507-1428-1646</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 한강대로52길 38 202호</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nail_snoope</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P98" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>6</v>
-      </c>
-      <c r="R98" t="n">
-        <v>151</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>1926501985</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1926501985</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>토마네일</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>yeoooey@naver.com</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/to.ma.nail</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P99" t="n">
-        <v>123</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>7</v>
-      </c>
-      <c r="R99" t="n">
-        <v>130</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>1701565426</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1701565426</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>컬러테일러</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>ariarisom2@naver.com</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>https://pf.kakao.com/_vpyXn</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P100" t="n">
-        <v>320</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>2</v>
-      </c>
-      <c r="R100" t="n">
-        <v>322</v>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>1031854178</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1031854178</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>어서오손네일</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>funhanbro@naver.com</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/funhanbro</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P101" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>12</v>
-      </c>
-      <c r="R101" t="n">
-        <v>23</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>1030962704</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1030962704</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>우아한 네일 살롱</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>findmyperfectdays@naver.com</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/wooanail_salon</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P102" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>1</v>
-      </c>
-      <c r="R102" t="n">
-        <v>64</v>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>1370902820</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1370902820</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>레푸스 용산역점</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>refussyss@naver.com</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0507-1417-1074</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@레푸스용산역점</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P103" t="n">
-        <v>293</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>190</v>
-      </c>
-      <c r="R103" t="n">
-        <v>483</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>1153661148</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1153661148</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>비비네일</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>milkycoco95@naver.com</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>02-749-9134</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>http://www.instagram.com/vivinail</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P104" t="n">
-        <v>258</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>45</v>
-      </c>
-      <c r="R104" t="n">
-        <v>303</v>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>21834362</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/21834362</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>센스</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>showmblog@naver.com</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 만리재로 140-1</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P105" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>2</v>
-      </c>
-      <c r="R105" t="n">
-        <v>6</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>1189922870</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1189922870</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>네일슈슈</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>brilliant14694@naver.com</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>0507-1435-9113</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nail_chouchou_</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P106" t="n">
-        <v>461</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>28</v>
-      </c>
-      <c r="R106" t="n">
-        <v>489</v>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>1185094311</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1185094311</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>글로시블라썸 아이파크몰</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>irumskin@naver.com</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 한강대로23길 55</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P107" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>54</v>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>1485867849</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1485867849</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>헤더네일</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>mmmmbin@naver.com</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>0507-1464-8960</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/heathernail_102/</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P108" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>2</v>
-      </c>
-      <c r="R108" t="n">
-        <v>27</v>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>1399079243</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1399079243</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>네일리모노 이태원점</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>nailremono@naver.com</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>0507-1350-6775</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/nailremono</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P109" t="n">
-        <v>326</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>19</v>
-      </c>
-      <c r="R109" t="n">
-        <v>345</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>1785734080</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1785734080</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>네일의날씨</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>queen77577@naver.com</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0507-1430-0707</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 한강대로 288-2 1층</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>http://instagram.com/nail_nalssi</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P110" t="n">
-        <v>497</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>48</v>
-      </c>
-      <c r="R110" t="n">
-        <v>545</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>1050641028</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1050641028</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>손톱까끼</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>sinachoco@naver.com</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0507-1310-9297</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/kkakki_nail/</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P111" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>7</v>
-      </c>
-      <c r="R111" t="n">
-        <v>56</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>20939317</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/20939317</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>네일프롬다니</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>arielisflowery@naver.com</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>0507-1349-9460</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P112" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>17</v>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>1774853191</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1774853191</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>투투네일</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>vin2roo@naver.com</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>0507-1336-4546</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/twotwo_nail</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P113" t="n">
-        <v>102</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>5</v>
-      </c>
-      <c r="R113" t="n">
-        <v>107</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>1253759614</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1253759614</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>팁셋 네일 한남점</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>likelife_lovely@naver.com</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>0507-1375-5705</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tipset.seoul/</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P114" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>3</v>
-      </c>
-      <c r="R114" t="n">
-        <v>74</v>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>1409853951</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1409853951</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>호박손톱</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>bomi3692@naver.com</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>02-794-7958</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P115" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>13</v>
-      </c>
-      <c r="R115" t="n">
-        <v>30</v>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>35927853</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/35927853</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>재니네일한남</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>evian___@naver.com</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>http://pf.kakao.com/_eKxmLxl</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P116" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>44</v>
-      </c>
-      <c r="R116" t="n">
-        <v>77</v>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>1593741438</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1593741438</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>다교네일 한남</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>swih@naver.com</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>0507-1339-1024</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>http://pf.kakao.com/_VZqxfG/chat</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P117" t="n">
-        <v>338</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>36</v>
-      </c>
-      <c r="R117" t="n">
-        <v>374</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>37620988</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37620988</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_nail/용산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/용산_네일샵.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>재니네일한남</t>
+          <t>팁셋 네일 한남점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>evian___@naver.com</t>
+          <t>likelife_lovely@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1375-5705</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
+          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/tipset.seoul/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -608,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="Q2" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1593741438</t>
+          <t>1409853951</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593741438</t>
+          <t>https://m.place.naver.com/place/1409853951</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -654,20 +658,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>더 트리니티 네일</t>
+          <t>네일꾼</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dlfnfl0129@naver.com</t>
+          <t>jinheeloo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1407-8585</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
+          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -692,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41f8b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -707,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="R3" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1060176123</t>
+          <t>1395413071</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060176123</t>
+          <t>https://m.place.naver.com/place/1395413071</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -748,25 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>센스</t>
+          <t>팝네일 신용산</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>showmblog@naver.com</t>
+          <t>mhhj951026@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1345-7477</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 140-1</t>
+          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/popnail_7477</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -776,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -792,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>316</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>363</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1189922870</t>
+          <t>1306229960</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189922870</t>
+          <t>https://m.place.naver.com/place/1306229960</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -838,44 +846,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바림</t>
+          <t>반디인하우스 용산아이파크몰점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>virus8163@naver.com</t>
+          <t>bandinhouse_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02-318-2055</t>
+          <t>0507-1472-1811</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로 73</t>
+          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -895,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>1254</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>189</v>
       </c>
       <c r="R5" t="n">
-        <v>13</v>
+        <v>1443</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1862156671</t>
+          <t>1049297184</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862156671</t>
+          <t>https://m.place.naver.com/place/1049297184</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -932,35 +940,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일퀸</t>
+          <t>다교네일 한남</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kfreebaby@naver.com</t>
+          <t>swih@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1339-1024</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 47</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_VZqxfG/chat</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -976,22 +988,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>338</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>374</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1000,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1023738371</t>
+          <t>37620988</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023738371</t>
+          <t>https://m.place.naver.com/place/37620988</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1022,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>팁셋 네일 한남점</t>
+          <t>비바이유 한남</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>likelife_lovely@naver.com</t>
+          <t>enoctobre-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1375-5705</t>
+          <t>0507-1371-9481</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
+          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/b.by_you</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1054,7 +1066,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wvdcyx7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1083,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1409853951</t>
+          <t>2019591721</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409853951</t>
+          <t>https://m.place.naver.com/place/2019591721</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1120,24 +1128,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일헤라</t>
+          <t>호박손톱</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>heranaillash@naver.com</t>
+          <t>bomi3692@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1334-2839</t>
+          <t>02-794-7958</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
+          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1173,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1936017804</t>
+          <t>35927853</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1936017804</t>
+          <t>https://m.place.naver.com/place/35927853</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1214,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일프롬다니</t>
+          <t>네일래쉬</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>arielisflowery@naver.com</t>
+          <t>nailash@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1349-9460</t>
+          <t>0507-1371-0008</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
+          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nailash</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1246,12 +1254,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R9" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1774853191</t>
+          <t>1220901153</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774853191</t>
+          <t>https://m.place.naver.com/place/1220901153</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>위위즈 용산점</t>
+          <t>네일노마드 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yigu8@naver.com</t>
+          <t>kjr1212a@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1366-3547</t>
+          <t>0507-1310-3658</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailnomad_</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1340,7 +1348,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1365,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>509</v>
+        <v>471</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>542</v>
+        <v>479</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1557214777</t>
+          <t>1841821386</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557214777</t>
+          <t>https://m.place.naver.com/place/1841821386</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>몽드메리</t>
+          <t>춘희손톱</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>happygirl223@naver.com</t>
+          <t>pskk0000@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1382-2264</t>
+          <t>0507-1306-7521</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
+          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/choonheenail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1434,7 +1442,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1444,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqmw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>761</v>
+        <v>196</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="R11" t="n">
-        <v>775</v>
+        <v>295</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1681006741</t>
+          <t>20559743</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681006741</t>
+          <t>https://m.place.naver.com/place/20559743</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1500,35 +1504,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>토마네일</t>
+          <t>네일셀레나</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>yeoooey@naver.com</t>
+          <t>soeyn92@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02-795-6529</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_zJpfG</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1544,7 +1552,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1553,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>123</v>
+        <v>396</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>130</v>
+        <v>401</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1701565426</t>
+          <t>35489351</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701565426</t>
+          <t>https://m.place.naver.com/place/35489351</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1590,34 +1598,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>반디인하우스 용산아이파크몰점</t>
+          <t>진주네 네일 효창공원점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bandinhouse_yongsan@naver.com</t>
+          <t>jiana2002@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1472-1811</t>
+          <t>0507-1403-6610</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
+          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
+          <t>https://www.instagram.com/jinjunenail</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1627,19 +1635,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4oyxx</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1647,17 +1651,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1254</v>
+        <v>79</v>
       </c>
       <c r="Q13" t="n">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>1443</v>
+        <v>98</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1049297184</t>
+          <t>2056938739</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049297184</t>
+          <t>https://m.place.naver.com/place/2056938739</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1688,25 +1692,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
+          <t>오드리네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tlstnals1010@naver.com</t>
+          <t>ardusy@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1446-0227</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
+          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oudreynail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1716,7 +1724,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1737,17 +1745,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,12 +1764,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1222846707</t>
+          <t>1497063684</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222846707</t>
+          <t>https://m.place.naver.com/place/1497063684</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1778,25 +1786,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>마고뷰티</t>
+          <t>네일가꿈</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mago_smp@naver.com</t>
+          <t>hyu3323@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1403-8723</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/e_nailshop_sj</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1806,7 +1818,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1816,17 +1828,13 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v3xa</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1835,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>119</v>
+        <v>475</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="R15" t="n">
-        <v>155</v>
+        <v>550</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,12 +1858,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1939429266</t>
+          <t>1966796864</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939429266</t>
+          <t>https://m.place.naver.com/place/1966796864</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1872,24 +1880,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>또또네일</t>
+          <t>붙여핸썹</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>clsald30@naver.com</t>
+          <t>woowim@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1354-9049</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 200 1층</t>
+          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1914,14 +1918,10 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wal8cit</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>X</t>
@@ -1929,17 +1929,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,12 +1948,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2020672159</t>
+          <t>1333965738</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020672159</t>
+          <t>https://m.place.naver.com/place/1333965738</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1970,29 +1970,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일리모노 이태원점</t>
+          <t>네일디렉터</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nailremono@naver.com</t>
+          <t>naildirector@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1350-6775</t>
+          <t>02-797-8188</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
+          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/naildirector</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2002,24 +2002,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4c298</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>X</t>
@@ -2031,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>326</v>
+        <v>158</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R17" t="n">
-        <v>345</v>
+        <v>169</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,12 +2042,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1785734080</t>
+          <t>1487195546</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785734080</t>
+          <t>https://m.place.naver.com/place/1487195546</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2068,24 +2064,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>덴드네일한남</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>eunii222@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1378-0596</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
+          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2121,17 +2113,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,12 +2132,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1108900148</t>
+          <t>1222846707</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108900148</t>
+          <t>https://m.place.naver.com/place/1222846707</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2162,25 +2154,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>아드</t>
+          <t>네일린</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>adfontes_math@naver.com</t>
+          <t>cookyismylife@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1344-8515</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
+          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/naileensalon</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2190,7 +2186,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2200,14 +2196,10 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcl18no</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>X</t>
@@ -2219,13 +2211,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,12 +2226,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1700535825</t>
+          <t>1996449351</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700535825</t>
+          <t>https://m.place.naver.com/place/1996449351</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2256,29 +2248,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>호박손톱</t>
+          <t>네일의날씨</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bomi3692@naver.com</t>
+          <t>queen77577@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02-794-7958</t>
+          <t>0507-1430-0707</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
+          <t>서울특별시 용산구 한강대로 288-2 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_nalssi</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2288,7 +2280,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2304,22 +2296,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>497</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="R20" t="n">
-        <v>30</v>
+        <v>545</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2328,12 +2320,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>35927853</t>
+          <t>1050641028</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35927853</t>
+          <t>https://m.place.naver.com/place/1050641028</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2350,25 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>데코네일</t>
+          <t>카밍네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>vivianmall@naver.com</t>
+          <t>ynh3377@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1357-1496</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
+          <t>서울특별시 용산구 소월로20길 42 1층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/calming_nail</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2378,7 +2374,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2388,14 +2384,10 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wybgknv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>X</t>
@@ -2407,13 +2399,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="Q21" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="R21" t="n">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2422,12 +2414,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>36812317</t>
+          <t>1383549813</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36812317</t>
+          <t>https://m.place.naver.com/place/1383549813</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2444,39 +2436,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>쵸코네일</t>
+          <t>묘즈네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>boong27@naver.com</t>
+          <t>kaeh5173907@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>02-749-7795</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
+          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_WxedxgG</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2492,22 +2480,22 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R22" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2516,12 +2504,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>19490178</t>
+          <t>1136869573</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19490178</t>
+          <t>https://m.place.naver.com/place/1136869573</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2538,25 +2526,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>수 네일</t>
+          <t>정원네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>qkrqhrdfrn@naver.com</t>
+          <t>pretty6144@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1406-7118</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 196 B1층</t>
+          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/jungwon_nail_</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2566,7 +2558,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2576,17 +2568,13 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47r14</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2595,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2610,12 +2598,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1989007422</t>
+          <t>1935294802</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989007422</t>
+          <t>https://m.place.naver.com/place/1935294802</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2632,29 +2620,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>티아라네일어반스파</t>
+          <t>코코루네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>orora_1976@naver.com</t>
+          <t>everydayenn@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02-790-7882</t>
+          <t>0507-1390-4270</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
+          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2664,7 +2652,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2685,17 +2673,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2704,12 +2692,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>33213520</t>
+          <t>1768871817</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33213520</t>
+          <t>https://m.place.naver.com/place/1768871817</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2726,29 +2714,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>나비네일</t>
+          <t>네일슈슈</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>shinding7610@naver.com</t>
+          <t>brilliant14694@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1416-0638</t>
+          <t>0507-1435-9113</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가-210</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_chouchou_</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2758,7 +2746,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2779,17 +2767,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>461</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="R25" t="n">
-        <v>10</v>
+        <v>489</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2798,12 +2786,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36629016</t>
+          <t>1185094311</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36629016</t>
+          <t>https://m.place.naver.com/place/1185094311</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2820,39 +2808,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>수아르네일</t>
+          <t>컬러테일러</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>swa_r@naver.com</t>
+          <t>ariarisom2@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1354-9689</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
+          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_vpyXn</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2868,7 +2852,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2877,13 +2861,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>11</v>
+        <v>322</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>14</v>
+        <v>324</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2892,12 +2876,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>21568200</t>
+          <t>1031854178</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21568200</t>
+          <t>https://m.place.naver.com/place/1031854178</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2914,39 +2898,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>손톱의취향 용산푸르지오써밋점</t>
+          <t>뷰리뉼레</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>tastein_nail_yongsan@naver.com</t>
+          <t>kimnr123@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1483-0870</t>
+          <t>0507-1389-5562</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
+          <t>서울특별시 용산구 후암로 28 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taste_in_nail_</t>
+          <t>https://toss.place/_lb/TYhSdSVIw</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2971,13 +2955,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>481</v>
+        <v>136</v>
       </c>
       <c r="Q27" t="n">
-        <v>290</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>771</v>
+        <v>142</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2986,12 +2970,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2055593167</t>
+          <t>33277553</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055593167</t>
+          <t>https://m.place.naver.com/place/33277553</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3008,24 +2992,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일셀레나</t>
+          <t>네일휴</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>soeyn92@naver.com</t>
+          <t>white5198@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02-795-6529</t>
+          <t>02-711-3646</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
+          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3050,32 +3034,28 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wasqu44</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>395</v>
+        <v>2</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3084,12 +3064,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>35489351</t>
+          <t>1611951357</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35489351</t>
+          <t>https://m.place.naver.com/place/1611951357</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3106,29 +3086,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일디렉터</t>
+          <t>아드</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>naildirector@naver.com</t>
+          <t>adfontes_math@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>02-797-8188</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
+          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naildirector</t>
+          <t>https://www.instagram.com/a.th_kr</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3143,7 +3119,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3163,13 +3139,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>157</v>
+        <v>52</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3178,12 +3154,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1487195546</t>
+          <t>1700535825</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487195546</t>
+          <t>https://m.place.naver.com/place/1700535825</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3200,29 +3176,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>리네일</t>
+          <t>청담네일박스 용산점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dlwjddo7053@naver.com</t>
+          <t>smilehh406@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1421-7880</t>
+          <t>0507-1325-5985</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
+          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cheongdam_nailbox</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3232,7 +3208,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3242,17 +3218,13 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5y9ij</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3261,13 +3233,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3276,12 +3248,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>32244399</t>
+          <t>2020464978</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32244399</t>
+          <t>https://m.place.naver.com/place/2020464978</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3298,29 +3270,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>벨르네이쳐</t>
+          <t>덴드네일한남</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dewsang@naver.com</t>
+          <t>eunii222@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1463-0395</t>
+          <t>0507-1378-0596</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
+          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/eunii222</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3330,12 +3302,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3346,7 +3318,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3355,13 +3327,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="R31" t="n">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3370,12 +3342,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2043754067</t>
+          <t>1108900148</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043754067</t>
+          <t>https://m.place.naver.com/place/1108900148</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3392,24 +3364,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일월드</t>
+          <t>루미가넷네일존 이마트 용산점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ellykwak@naver.com</t>
+          <t>hyer2986@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>02-715-9585</t>
+          <t>0507-1401-9470</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6</t>
+          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3449,13 +3421,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3464,12 +3436,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1228817187</t>
+          <t>1619342094</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228817187</t>
+          <t>https://m.place.naver.com/place/1619342094</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3486,29 +3458,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>리라네일</t>
+          <t>설화미</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kkmm_0707@naver.com</t>
+          <t>who1who2@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>02-703-4125</t>
+          <t>0507-1381-4227</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 23</t>
+          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sulwhami_beauty/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3518,7 +3490,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3539,17 +3511,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3558,12 +3530,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1131445662</t>
+          <t>33647337</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131445662</t>
+          <t>https://m.place.naver.com/place/33647337</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3580,29 +3552,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
+          <t>오나네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>j2lang@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1345-4179</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
+          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/o.nnail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3612,7 +3580,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3622,14 +3590,10 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zprq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>X</t>
@@ -3641,13 +3605,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>293</v>
+        <v>133</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R34" t="n">
-        <v>300</v>
+        <v>147</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3656,12 +3620,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>21038031</t>
+          <t>1549497362</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21038031</t>
+          <t>https://m.place.naver.com/place/1549497362</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3678,29 +3642,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>아로하네일</t>
+          <t>네일헤라</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>bbotive@naver.com</t>
+          <t>heranaillash@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1391-4369</t>
+          <t>0507-1334-2839</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로14길 10 2층</t>
+          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail.hera</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3710,7 +3674,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3720,14 +3684,10 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4swbk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>X</t>
@@ -3739,13 +3699,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3754,12 +3714,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1264306160</t>
+          <t>1936017804</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264306160</t>
+          <t>https://m.place.naver.com/place/1936017804</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3776,29 +3736,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>쿠로키네일</t>
+          <t>네일프롬다니</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kurokinail@naver.com</t>
+          <t>arielisflowery@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1481-2893</t>
+          <t>0507-1349-9460</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 19-2 1층</t>
+          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3808,7 +3768,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3818,17 +3778,13 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5z5mm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3837,13 +3793,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3852,12 +3808,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1723956505</t>
+          <t>1774853191</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723956505</t>
+          <t>https://m.place.naver.com/place/1774853191</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3874,29 +3830,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>진주네 네일 효창공원점</t>
+          <t>토마네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>thwjd91070@naver.com</t>
+          <t>yeoooey@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0507-1403-6610</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
+          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/to.ma.nail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3906,7 +3858,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3931,13 +3883,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="Q37" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="R37" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3946,12 +3898,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2056938739</t>
+          <t>1701565426</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056938739</t>
+          <t>https://m.place.naver.com/place/1701565426</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3968,29 +3920,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>네일린</t>
+          <t>디에고푸스 희네일 이촌점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cookyismylife@naver.com</t>
+          <t>jwkang3929@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1344-8515</t>
+          <t>0507-1339-5732</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
+          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/heenail4345</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4000,7 +3952,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4010,14 +3962,10 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zm9q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -4029,13 +3977,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>157</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4044,12 +3992,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1996449351</t>
+          <t>1972424680</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996449351</t>
+          <t>https://m.place.naver.com/place/1972424680</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4066,29 +4014,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>오드리네일</t>
+          <t>바림</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ardusy@naver.com</t>
+          <t>virus8163@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1446-0227</t>
+          <t>02-318-2055</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
+          <t>서울특별시 용산구 두텁바위로 73</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/Barim_nail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4098,7 +4046,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4108,14 +4056,10 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5xtse</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>X</t>
@@ -4127,13 +4071,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4142,12 +4086,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1497063684</t>
+          <t>1862156671</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1497063684</t>
+          <t>https://m.place.naver.com/place/1862156671</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4164,29 +4108,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>플리네일 용산해링턴점</t>
+          <t>블랑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>lamidays@naver.com</t>
+          <t>hg6580@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1406-7552</t>
+          <t>02-790-8798</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nailist_blanc</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4196,7 +4140,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4206,14 +4150,10 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wl1i419</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4225,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>439</v>
+        <v>7</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>454</v>
+        <v>8</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4240,12 +4180,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2075608465</t>
+          <t>909330706</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075608465</t>
+          <t>https://m.place.naver.com/place/909330706</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4262,29 +4202,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일테라피은</t>
+          <t>몽드메리</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mountain__sun@naver.com</t>
+          <t>soul-bi@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1379-8496</t>
+          <t>0507-1382-2264</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
+          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailtherapyeun</t>
+          <t>https://www.instagram.com/monde.mery</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4319,13 +4259,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>203</v>
+        <v>764</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R41" t="n">
-        <v>212</v>
+        <v>778</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4334,12 +4274,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1180134699</t>
+          <t>1681006741</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180134699</t>
+          <t>https://m.place.naver.com/place/1681006741</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4356,39 +4296,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>오렌지나무</t>
+          <t>쿠로키네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kmaxim2@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1323-2154</t>
+          <t>0507-1481-2893</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로20길 13 1층</t>
+          <t>서울특별시 용산구 신흥로 19-2 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xaxcxeBG</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4404,7 +4344,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4413,13 +4353,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R42" t="n">
-        <v>15</v>
+        <v>166</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4428,12 +4368,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1568164546</t>
+          <t>1723956505</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568164546</t>
+          <t>https://m.place.naver.com/place/1723956505</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4450,24 +4390,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>제이제이 네일</t>
+          <t>러블리핑크</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>kisever1@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1411-8138</t>
+          <t>02-704-8470</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 회나무로 32-3 2층</t>
+          <t>서울특별시 용산구 청파로45길 27 2층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4503,17 +4443,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q43" t="n">
         <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4522,12 +4462,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>79017915</t>
+          <t>36901322</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/79017915</t>
+          <t>https://m.place.naver.com/place/36901322</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4544,29 +4484,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일삼각지</t>
+          <t>무구네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nailsamgakji@naver.com</t>
+          <t>mugunail2025@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1316-2792</t>
+          <t>0507-1353-2420</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
+          <t>서울특별시 용산구 새창로14길 46 2층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4576,7 +4516,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4592,7 +4532,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4601,13 +4541,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>17</v>
+        <v>194</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="R44" t="n">
-        <v>22</v>
+        <v>237</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4616,12 +4556,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1872968588</t>
+          <t>2093535455</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1872968588</t>
+          <t>https://m.place.naver.com/place/2093535455</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4633,49 +4573,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>네일아트재료</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>메종드로르</t>
+          <t>메이크케이</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>stylechosun@naver.com</t>
+          <t>kbanknow@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1386-1014</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
+          <t>서울특별시 용산구 청파로47길 56 1층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4695,13 +4631,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4710,12 +4646,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2029580174</t>
+          <t>2081839313</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029580174</t>
+          <t>https://m.place.naver.com/place/2081839313</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4732,12 +4668,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>묘즈네일</t>
+          <t>더 트리니티 네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kaeh5173907@naver.com</t>
+          <t>dlfnfl0129@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4745,12 +4681,12 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
+          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/the_trinity_nail/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4760,7 +4696,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4776,7 +4712,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4785,13 +4721,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="R46" t="n">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4800,12 +4736,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1136869573</t>
+          <t>1060176123</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136869573</t>
+          <t>https://m.place.naver.com/place/1060176123</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4822,29 +4758,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>유스뷰티</t>
+          <t>진유진네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jyrif91@naver.com</t>
+          <t>seoul2816@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1422-3533</t>
+          <t>0507-1416-2081</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로20길 21 1층</t>
+          <t>서울특별시 용산구 한강대로 284</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youthnail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4854,7 +4790,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4875,17 +4811,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="Q47" t="n">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="R47" t="n">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4894,12 +4830,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>38467380</t>
+          <t>31574498</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38467380</t>
+          <t>https://m.place.naver.com/place/31574498</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4916,20 +4852,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>오나네일</t>
+          <t>제이비풋 굳은살&amp;발톱 케어</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>sunny_0225@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>02-794-8551</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4965,17 +4905,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>133</v>
+        <v>350</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="R48" t="n">
-        <v>147</v>
+        <v>529</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4984,12 +4924,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1549497362</t>
+          <t>12791408</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549497362</t>
+          <t>https://m.place.naver.com/place/12791408</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5006,29 +4946,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>비바이유 한남</t>
+          <t>프로네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>enoctobre-@naver.com</t>
+          <t>sonvely89@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1371-9481</t>
+          <t>0507-1421-1525</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
+          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/itaewonpronail/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5038,7 +4978,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5063,13 +5003,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5078,12 +5018,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2019591721</t>
+          <t>13028002</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019591721</t>
+          <t>https://m.place.naver.com/place/13028002</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5100,29 +5040,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>팝네일 신용산</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mhhj951026@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1345-7477</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
+          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nailclover_yongsan</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5132,7 +5068,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5142,17 +5078,13 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fow3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5161,13 +5093,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>316</v>
+        <v>8</v>
       </c>
       <c r="Q50" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>363</v>
+        <v>9</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5176,12 +5108,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1306229960</t>
+          <t>32496791</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306229960</t>
+          <t>https://m.place.naver.com/place/32496791</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5198,29 +5130,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>루미가넷네일존 이마트 용산점</t>
+          <t>오늘도네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>hyer2986@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1401-9470</t>
+          <t>0507-1345-4179</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
+          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/today_nail_ichon</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5230,7 +5162,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5251,17 +5183,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R51" t="n">
-        <v>86</v>
+        <v>300</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5270,12 +5202,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1619342094</t>
+          <t>21038031</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619342094</t>
+          <t>https://m.place.naver.com/place/21038031</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5292,29 +5224,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일슈슈</t>
+          <t>헤더네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>brilliant14694@naver.com</t>
+          <t>mmmmbin@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1435-9113</t>
+          <t>0507-1464-8960</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/heathernail_102/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5324,7 +5256,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5334,14 +5266,10 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ko6p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5353,13 +5281,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>461</v>
+        <v>25</v>
       </c>
       <c r="Q52" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>489</v>
+        <v>27</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5368,12 +5296,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1185094311</t>
+          <t>1399079243</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185094311</t>
+          <t>https://m.place.naver.com/place/1399079243</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5390,29 +5318,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>정원네일</t>
+          <t>네일삼각지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>pretty6144@naver.com</t>
+          <t>nailsamgakji@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1406-7118</t>
+          <t>0507-1316-2792</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
+          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_samgakji</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5422,7 +5350,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5432,17 +5360,13 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4snrh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5451,13 +5375,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5466,12 +5390,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1935294802</t>
+          <t>1872968588</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935294802</t>
+          <t>https://m.place.naver.com/place/1872968588</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5488,29 +5412,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일꾼</t>
+          <t>수 네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jinheeloo@naver.com</t>
+          <t>qkrqhrdfrn@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1407-8585</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
+          <t>서울특별시 용산구 만리재로 196 B1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/qkrqhrdfrn</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5520,12 +5440,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5536,22 +5456,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q54" t="n">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="R54" t="n">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5560,12 +5480,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1395413071</t>
+          <t>1989007422</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395413071</t>
+          <t>https://m.place.naver.com/place/1989007422</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5582,29 +5502,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>봉선화물들이다</t>
+          <t>유스뷰티</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>s8h6y@naver.com</t>
+          <t>jyrif91@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>02-6203-5478</t>
+          <t>0507-1422-3533</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
+          <t>서울특별시 용산구 이태원로20길 21 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/youthnail/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5614,7 +5534,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5639,13 +5559,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="R55" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5654,12 +5574,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>33618035</t>
+          <t>38467380</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33618035</t>
+          <t>https://m.place.naver.com/place/38467380</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5676,20 +5596,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>컬러테일러</t>
+          <t>리라네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ariarisom2@naver.com</t>
+          <t>kkmm_0707@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02-703-4125</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
+          <t>서울특별시 용산구 원효로41길 23</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5720,22 +5644,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>322</v>
+        <v>1</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5744,12 +5668,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1031854178</t>
+          <t>1131445662</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031854178</t>
+          <t>https://m.place.naver.com/place/1131445662</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5766,44 +5690,44 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>프로네일</t>
+          <t>마틸다네일M 한남점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sonvely89@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1421-1525</t>
+          <t>0507-1412-3082</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
+          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://matildanailshop-mo3.imweb.me/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5823,10 +5747,10 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="Q57" t="n">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="R57" t="n">
         <v>111</v>
@@ -5838,12 +5762,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13028002</t>
+          <t>1798849933</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13028002</t>
+          <t>https://m.place.naver.com/place/1798849933</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5860,24 +5784,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>우아엘뷰티</t>
+          <t>네일퀸</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>commathemoon_yongsan@naver.com</t>
+          <t>kfreebaby@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0507-1379-1978</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 147 2층</t>
+          <t>서울특별시 용산구 새창로14길 47</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5902,14 +5822,10 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5xabi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>X</t>
@@ -5917,17 +5833,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="Q58" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5936,12 +5852,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1942029836</t>
+          <t>1023738371</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942029836</t>
+          <t>https://m.place.naver.com/place/1023738371</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5958,29 +5874,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일스눕</t>
+          <t>네일바이르레</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>graceham_@naver.com</t>
+          <t>l5v2osh@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1428-1646</t>
+          <t>0507-1312-9470</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로52길 38 202호</t>
+          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_by_lerre</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5990,7 +5906,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6015,13 +5931,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="Q59" t="n">
         <v>6</v>
       </c>
       <c r="R59" t="n">
-        <v>151</v>
+        <v>93</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6030,12 +5946,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1926501985</t>
+          <t>37818863</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926501985</t>
+          <t>https://m.place.naver.com/place/37818863</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6052,39 +5968,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>레푸스 용산역점</t>
+          <t>재니네일한남</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>refussyss@naver.com</t>
+          <t>evian___@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1417-1074</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
+          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_eKxmLxl</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6094,17 +6006,13 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5iw5q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6113,13 +6021,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>293</v>
+        <v>33</v>
       </c>
       <c r="Q60" t="n">
-        <v>191</v>
+        <v>44</v>
       </c>
       <c r="R60" t="n">
-        <v>484</v>
+        <v>77</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6128,12 +6036,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1153661148</t>
+          <t>1593741438</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153661148</t>
+          <t>https://m.place.naver.com/place/1593741438</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6150,29 +6058,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일가꿈</t>
+          <t>또또네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hyu3323@naver.com</t>
+          <t>clsald30@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1403-8723</t>
+          <t>0507-1354-9049</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
+          <t>서울특별시 용산구 원효로 200 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ttotto__nail</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6182,7 +6090,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6192,14 +6100,10 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcf6ev</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>X</t>
@@ -6211,13 +6115,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>475</v>
+        <v>150</v>
       </c>
       <c r="Q61" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="R61" t="n">
-        <v>550</v>
+        <v>157</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6226,12 +6130,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1966796864</t>
+          <t>2020672159</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966796864</t>
+          <t>https://m.place.naver.com/place/2020672159</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6248,29 +6152,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>마틸다네일M 한남점</t>
+          <t>리네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>dlwjddo7053@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1412-3082</t>
+          <t>0507-1421-7880</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
+          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://matildanailshop-mo3.imweb.me/</t>
+          <t>http://instagram.com/ri_nail7877</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6285,7 +6189,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6305,13 +6209,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6320,12 +6224,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1798849933</t>
+          <t>32244399</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798849933</t>
+          <t>https://m.place.naver.com/place/32244399</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6342,44 +6246,44 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>뷰리뉼레</t>
+          <t>켈리하우스 네일샵</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kimnr123@naver.com</t>
+          <t>kellylove09@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1389-5562</t>
+          <t>0507-1393-9967</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 후암로 28 1층</t>
+          <t>서울특별시 용산구 보광로 49</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYhSdSVIw</t>
+          <t>https://blog.naver.com/kellylove09</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6395,17 +6299,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>136</v>
+        <v>7</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6414,12 +6318,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>33277553</t>
+          <t>32875703</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33277553</t>
+          <t>https://m.place.naver.com/place/32875703</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6436,29 +6340,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>제이제이 네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>02-749-9134</t>
+          <t>0507-1411-8138</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
+          <t>서울특별시 용산구 회나무로 32-3 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jjjjnail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6468,7 +6372,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6478,14 +6382,10 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w48ses</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>X</t>
@@ -6497,13 +6397,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>258</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>303</v>
+        <v>3</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6512,12 +6412,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>21834362</t>
+          <t>79017915</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21834362</t>
+          <t>https://m.place.naver.com/place/79017915</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6534,24 +6434,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>후암네일</t>
+          <t>글로시블라썸 아이파크몰</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>dndud7532@naver.com</t>
+          <t>irumskin@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0507-1301-4091</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
+          <t>서울특별시 용산구 한강대로23길 55</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6576,14 +6472,10 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7alem9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>X</t>
@@ -6591,17 +6483,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6610,12 +6502,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2033884779</t>
+          <t>1485867849</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033884779</t>
+          <t>https://m.place.naver.com/place/1485867849</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6632,24 +6524,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일휴</t>
+          <t>이촌 네일타임 LG프라자</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>white5198@naver.com</t>
+          <t>blingsea@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>02-711-3646</t>
+          <t>0507-1498-8612</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
+          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6689,13 +6581,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R66" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6704,12 +6596,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1611951357</t>
+          <t>20064911</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611951357</t>
+          <t>https://m.place.naver.com/place/20064911</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6726,20 +6618,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>글로시블라썸 아이파크몰</t>
+          <t>네일월드</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>irumskin@naver.com</t>
+          <t>bongbong0401@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>02-715-9585</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55</t>
+          <t>서울특별시 용산구 효창원로8길 6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6779,13 +6675,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6794,12 +6690,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1485867849</t>
+          <t>1228817187</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485867849</t>
+          <t>https://m.place.naver.com/place/1228817187</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6816,29 +6712,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>쵸민네일</t>
+          <t>수아르네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sunday020@naver.com</t>
+          <t>xxong_11@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1403-3417</t>
+          <t>0507-1354-9689</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
+          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/swa_rnail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6848,7 +6744,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6858,14 +6754,10 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ua47</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6873,17 +6765,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6892,12 +6784,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1664663384</t>
+          <t>21568200</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664663384</t>
+          <t>https://m.place.naver.com/place/21568200</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6914,29 +6806,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일샵베이비</t>
+          <t>네일테라피은</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>zxlixz@naver.com</t>
+          <t>anrgudtkd@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1396-4649</t>
+          <t>0507-1379-8496</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로2길 19 1층</t>
+          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailtherapyeun</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6946,7 +6838,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6956,14 +6848,10 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40tj2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>X</t>
@@ -6971,17 +6859,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>38</v>
+        <v>203</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R69" t="n">
-        <v>39</v>
+        <v>212</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6990,12 +6878,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1847608869</t>
+          <t>1180134699</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847608869</t>
+          <t>https://m.place.naver.com/place/1180134699</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7012,25 +6900,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일클로버</t>
+          <t>이앤앤</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>eyennail@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1316-3771</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
+          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/_eyennail_</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7040,7 +6932,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7065,13 +6957,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>8</v>
+        <v>599</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>1333</v>
       </c>
       <c r="R70" t="n">
-        <v>9</v>
+        <v>1932</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7080,12 +6972,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>32496791</t>
+          <t>375707328</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32496791</t>
+          <t>https://m.place.naver.com/place/375707328</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7102,25 +6994,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일바라기</t>
+          <t>플로르 네일 이태원점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sydy8585@naver.com</t>
+          <t>flornail@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>02-790-4182</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
+          <t>서울특별시 용산구 우사단로 47 4층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/flornail</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7130,12 +7026,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7155,13 +7051,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="Q71" t="n">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="R71" t="n">
-        <v>105</v>
+        <v>281</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7170,12 +7066,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1091743517</t>
+          <t>32435712</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091743517</t>
+          <t>https://m.place.naver.com/place/32435712</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7192,29 +7088,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>코코루네일</t>
+          <t>네일샵입니다</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>xanxixxanx@naver.com</t>
+          <t>yooawo@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1390-4270</t>
+          <t>0507-1336-5457</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
+          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/shopnailshop/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7224,7 +7120,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7234,14 +7130,10 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wyj7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>X</t>
@@ -7253,13 +7145,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="Q72" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="R72" t="n">
-        <v>8</v>
+        <v>206</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7268,12 +7160,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1768871817</t>
+          <t>954197461</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768871817</t>
+          <t>https://m.place.naver.com/place/954197461</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7285,25 +7177,29 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>네일아트재료</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>메이크케이</t>
+          <t>신데렐라</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>kbanknow@naver.com</t>
+          <t>dracura10@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>02-790-3304</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 56 1층</t>
+          <t>서울특별시 용산구 보광로 61</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7343,13 +7239,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7358,12 +7254,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2081839313</t>
+          <t>20662540</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2081839313</t>
+          <t>https://m.place.naver.com/place/20662540</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7380,29 +7276,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>켈리하우스 네일샵</t>
+          <t>빛나러오소문제성발관리 용산점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kellylove09@naver.com</t>
+          <t>kknsky73@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1393-9967</t>
+          <t>0507-1419-6888</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 49</t>
+          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@user-gc4wk2yn2b</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7412,7 +7308,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7428,22 +7324,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>7</v>
+        <v>250</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>166</v>
       </c>
       <c r="R74" t="n">
-        <v>12</v>
+        <v>416</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7452,12 +7348,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>32875703</t>
+          <t>1438224262</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32875703</t>
+          <t>https://m.place.naver.com/place/1438224262</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7474,39 +7370,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>무구네일</t>
+          <t>네일더누브</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>mugunail2025@naver.com</t>
+          <t>hasom0304@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1353-2420</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 46 2층</t>
+          <t>서울특별시 용산구 원효로 210 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xdFnxhn</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7516,17 +7408,13 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wrh8pod</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7535,13 +7423,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="Q75" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="R75" t="n">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7550,12 +7438,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2093535455</t>
+          <t>1146800442</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093535455</t>
+          <t>https://m.place.naver.com/place/1146800442</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7572,29 +7460,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>러블리핑크</t>
+          <t>데코네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kisever1@naver.com</t>
+          <t>shwimlove@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>02-704-8470</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 27 2층</t>
+          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7604,7 +7488,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7625,17 +7509,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="R76" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7644,12 +7528,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>36901322</t>
+          <t>36812317</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36901322</t>
+          <t>https://m.place.naver.com/place/36812317</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7666,29 +7550,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>청담네일박스 용산점</t>
+          <t>위위즈 용산점</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>smilehh406@naver.com</t>
+          <t>yigu8@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1325-5985</t>
+          <t>0507-1366-3547</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
+          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ouiouiznail</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7698,7 +7582,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7708,17 +7592,13 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w1fw0g2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7727,13 +7607,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>6</v>
+        <v>510</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R77" t="n">
-        <v>6</v>
+        <v>543</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7742,12 +7622,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>2020464978</t>
+          <t>1557214777</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020464978</t>
+          <t>https://m.place.naver.com/place/1557214777</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7764,29 +7644,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Breathnailz</t>
+          <t>오렌지나무</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>mooisu@naver.com</t>
+          <t>kmaxim2@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1358-6853</t>
+          <t>0507-1323-2154</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 36 1층</t>
+          <t>서울특별시 용산구 한남대로20길 13 1층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7796,7 +7676,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7821,13 +7701,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q78" t="n">
         <v>2</v>
       </c>
       <c r="R78" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7836,12 +7716,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1488241394</t>
+          <t>1568164546</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488241394</t>
+          <t>https://m.place.naver.com/place/1568164546</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7858,39 +7738,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>디에고푸스 희네일 이촌점</t>
+          <t>벨르네이쳐</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jwkang3929@naver.com</t>
+          <t>dewsang@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1339-5732</t>
+          <t>0507-1463-0395</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
+          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_pixftn/chat</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7906,7 +7786,7 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7915,13 +7795,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q79" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="R79" t="n">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7930,12 +7810,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1972424680</t>
+          <t>2043754067</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972424680</t>
+          <t>https://m.place.naver.com/place/2043754067</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7952,25 +7832,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>어서오손네일</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>funhanbro@naver.com</t>
+          <t>jytgh@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1416-0638</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
+          <t>서울특별시 용산구 새창로 70 상가-210</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/funhanbro</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7980,12 +7864,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8001,17 +7885,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q80" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R80" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8020,12 +7904,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1030962704</t>
+          <t>36629016</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030962704</t>
+          <t>https://m.place.naver.com/place/36629016</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8042,29 +7926,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>이촌 네일타임 LG프라자</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>blingsea@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1498-8612</t>
+          <t>070-8882-4343</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
+          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/j_magic_nail</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8074,7 +7958,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -8095,17 +7979,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="Q81" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="R81" t="n">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8114,12 +7998,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>20064911</t>
+          <t>1438268528</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20064911</t>
+          <t>https://m.place.naver.com/place/1438268528</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8136,24 +8020,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>이앤앤</t>
+          <t>제이미 네일</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>eyennail@naver.com</t>
+          <t>see7833@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1316-3771</t>
+          <t>02-701-5602</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
+          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8178,14 +8062,10 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc6bbh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>X</t>
@@ -8193,17 +8073,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>594</v>
+        <v>29</v>
       </c>
       <c r="Q82" t="n">
-        <v>1333</v>
+        <v>2</v>
       </c>
       <c r="R82" t="n">
-        <v>1927</v>
+        <v>31</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8212,12 +8092,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>375707328</t>
+          <t>255540367</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/375707328</t>
+          <t>https://m.place.naver.com/place/255540367</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8234,25 +8114,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>붙여핸썹</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>woowim@naver.com</t>
+          <t>milkycoco95@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>02-749-9134</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/vivinail</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8262,7 +8146,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8283,17 +8167,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8302,12 +8186,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1333965738</t>
+          <t>21834362</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333965738</t>
+          <t>https://m.place.naver.com/place/21834362</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8324,20 +8208,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>살롱드다한</t>
+          <t>네일샵베이비</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ddalkong9830@naver.com</t>
+          <t>zxlixz@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1396-4649</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 257 2층</t>
+          <t>서울특별시 용산구 우사단로2길 19 1층</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8373,17 +8261,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>229</v>
+        <v>38</v>
       </c>
       <c r="Q84" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>282</v>
+        <v>39</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8392,12 +8280,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1917414808</t>
+          <t>1847608869</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917414808</t>
+          <t>https://m.place.naver.com/place/1847608869</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8414,24 +8302,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>제이비풋 굳은살&amp;발톱 케어</t>
+          <t>Breathnailz</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>sunny_0225@naver.com</t>
+          <t>mooisu@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>02-794-8551</t>
+          <t>0507-1358-6853</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
+          <t>서울특별시 용산구 소월로20길 36 1층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8471,13 +8359,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>179</v>
+        <v>2</v>
       </c>
       <c r="R85" t="n">
-        <v>529</v>
+        <v>2</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8486,12 +8374,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>12791408</t>
+          <t>1488241394</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12791408</t>
+          <t>https://m.place.naver.com/place/1488241394</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8508,29 +8396,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>춘희손톱</t>
+          <t>투투네일</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>chii0216@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1306-7521</t>
+          <t>0507-1336-4546</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
+          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/twotwo_nail</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8540,7 +8428,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8550,14 +8438,10 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc1bsb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>X</t>
@@ -8569,13 +8453,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="Q86" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>295</v>
+        <v>107</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8584,12 +8468,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>20559743</t>
+          <t>1253759614</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20559743</t>
+          <t>https://m.place.naver.com/place/1253759614</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8606,29 +8490,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>네일샵입니다</t>
+          <t>아로하네일</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>yooawo@naver.com</t>
+          <t>bbotive@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1336-5457</t>
+          <t>0507-1391-4369</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
+          <t>서울특별시 용산구 이태원로14길 10 2층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/alohanail_chae</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8638,7 +8522,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8663,13 +8547,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="Q87" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="R87" t="n">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8678,12 +8562,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>954197461</t>
+          <t>1264306160</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/954197461</t>
+          <t>https://m.place.naver.com/place/1264306160</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8700,29 +8584,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>네일뮤지엄</t>
+          <t>메종드로르</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>nail-museum@naver.com</t>
+          <t>stylechosun@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>070-7543-4009</t>
+          <t>0507-1386-1014</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
+          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8732,7 +8616,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8742,14 +8626,10 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wch6zi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>X</t>
@@ -8761,13 +8641,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>345</v>
+        <v>30</v>
       </c>
       <c r="Q88" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>705</v>
+        <v>30</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8776,12 +8656,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1881584782</t>
+          <t>2029580174</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881584782</t>
+          <t>https://m.place.naver.com/place/2029580174</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8798,25 +8678,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>네일더누브</t>
+          <t>버들네일</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>hasom0304@naver.com</t>
+          <t>ynh3377@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1400-7111</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 210 1층</t>
+          <t>서울특별시 용산구 신흥로 147 1층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/b_d_nail</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8826,7 +8710,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8842,7 +8726,7 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8851,13 +8735,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="Q89" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="R89" t="n">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8866,12 +8750,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1146800442</t>
+          <t>1127614127</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1146800442</t>
+          <t>https://m.place.naver.com/place/1127614127</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8888,29 +8772,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>제이미 네일</t>
+          <t>살롱드다한</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>see7833@naver.com</t>
+          <t>ddalkong9830@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>02-701-5602</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
+          <t>서울특별시 용산구 원효로 257 2층</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8920,7 +8800,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8941,17 +8821,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>29</v>
+        <v>229</v>
       </c>
       <c r="Q90" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="R90" t="n">
-        <v>31</v>
+        <v>282</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8960,12 +8840,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>255540367</t>
+          <t>1917414808</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/255540367</t>
+          <t>https://m.place.naver.com/place/1917414808</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8982,39 +8862,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
+          <t>마고뷰티</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>tlstnals1010@naver.com</t>
+          <t>mago_smp@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>070-8882-4343</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
+          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xjBnAn</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -9030,7 +8906,7 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9039,13 +8915,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="Q91" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R91" t="n">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9054,12 +8930,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1438268528</t>
+          <t>1939429266</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438268528</t>
+          <t>https://m.place.naver.com/place/1939429266</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9076,34 +8952,34 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>빛나러오소문제성발관리 용산점</t>
+          <t>루아드네일</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>kknsky73@naver.com</t>
+          <t>sumr2002@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1419-6888</t>
+          <t>0507-1452-9237</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
+          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://youtube.com/@user-gc4wk2yn2b</t>
+          <t>http://pf.kakao.com/_xoEbJn/friend</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9133,13 +9009,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>250</v>
+        <v>73</v>
       </c>
       <c r="Q92" t="n">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="R92" t="n">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9148,12 +9024,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1438224262</t>
+          <t>2003721483</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438224262</t>
+          <t>https://m.place.naver.com/place/2003721483</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9170,29 +9046,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>클리피</t>
+          <t>우아엘뷰티</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>seoul2gun@naver.com</t>
+          <t>commathemoon_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1855-4010</t>
+          <t>0507-1379-1978</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
+          <t>서울특별시 용산구 효창원로 147 2층</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/commathemoon_yongsan</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9202,12 +9078,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9218,7 +9094,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9227,13 +9103,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="Q93" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="R93" t="n">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9242,12 +9118,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1546271749</t>
+          <t>1942029836</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546271749</t>
+          <t>https://m.place.naver.com/place/1942029836</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9264,29 +9140,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>네일래쉬</t>
+          <t>네일뮤지엄</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>nailash@naver.com</t>
+          <t>nail-museum@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1371-0008</t>
+          <t>070-7543-4009</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
+          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nail-museum</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9296,24 +9172,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4itvj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>X</t>
@@ -9325,13 +9197,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>27</v>
+        <v>345</v>
       </c>
       <c r="Q94" t="n">
-        <v>49</v>
+        <v>360</v>
       </c>
       <c r="R94" t="n">
-        <v>76</v>
+        <v>705</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9340,12 +9212,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1220901153</t>
+          <t>1881584782</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220901153</t>
+          <t>https://m.place.naver.com/place/1881584782</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9362,29 +9234,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>오손내미오</t>
+          <t>레푸스 용산역점</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>playnauts@naver.com</t>
+          <t>refussyss@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1492-1340</t>
+          <t>0507-1417-1074</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
+          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@레푸스용산역점</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9394,7 +9266,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9419,13 +9291,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>7</v>
+        <v>293</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="R95" t="n">
-        <v>7</v>
+        <v>485</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9434,12 +9306,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1311070929</t>
+          <t>1153661148</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311070929</t>
+          <t>https://m.place.naver.com/place/1153661148</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9456,12 +9328,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>우아한 네일 살롱</t>
+          <t>어서오손네일</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>findmyperfectdays@naver.com</t>
+          <t>funhanbro@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -9469,12 +9341,12 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
+          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wooanail_salon</t>
+          <t>https://blog.naver.com/funhanbro</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9489,7 +9361,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9509,13 +9381,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R96" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9524,12 +9396,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1370902820</t>
+          <t>1030962704</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370902820</t>
+          <t>https://m.place.naver.com/place/1030962704</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9546,24 +9418,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>손톱까끼</t>
+          <t>티아라네일어반스파</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>sinachoco@naver.com</t>
+          <t>orora_1976@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1310-9297</t>
+          <t>02-790-7882</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9588,14 +9460,10 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w15n7bp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>X</t>
@@ -9603,17 +9471,17 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="Q97" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9622,12 +9490,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>20939317</t>
+          <t>33213520</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20939317</t>
+          <t>https://m.place.naver.com/place/33213520</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9644,29 +9512,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>투투네일</t>
+          <t>네일바래</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>naillab20@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>0507-1336-4546</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
+          <t>서울특별시 용산구 원효로 214-6 2층</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nailbarae_bboong</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9676,7 +9540,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9701,13 +9565,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="Q98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R98" t="n">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9716,12 +9580,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1253759614</t>
+          <t>835341707</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253759614</t>
+          <t>https://m.place.naver.com/place/835341707</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9738,25 +9602,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>네일드모네</t>
+          <t>손톱의취향 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>themy1226@naver.com</t>
+          <t>tastein_nail_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1483-0870</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 67 206호</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/taste_in_nail_</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9766,7 +9634,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -9791,13 +9659,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>98</v>
+        <v>481</v>
       </c>
       <c r="Q99" t="n">
-        <v>3</v>
+        <v>293</v>
       </c>
       <c r="R99" t="n">
-        <v>101</v>
+        <v>774</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9806,12 +9674,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>2062875678</t>
+          <t>2055593167</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2062875678</t>
+          <t>https://m.place.naver.com/place/2055593167</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9828,29 +9696,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>루아드네일</t>
+          <t>네일스눕</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>sumr2002@naver.com</t>
+          <t>graceham_@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1452-9237</t>
+          <t>0507-1428-1646</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
+          <t>서울특별시 용산구 한강대로52길 38 202호</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_snoope</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9860,7 +9728,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9870,17 +9738,13 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa539rh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -9889,13 +9753,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="Q100" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R100" t="n">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9904,12 +9768,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>2003721483</t>
+          <t>1926501985</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003721483</t>
+          <t>https://m.place.naver.com/place/1926501985</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9926,29 +9790,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>설화미</t>
+          <t>더네일바 2호점</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>who1who2@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1381-4227</t>
+          <t>0507-1411-8549</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
+          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/thenailbar_hannam</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9958,7 +9822,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9968,14 +9832,10 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4krlm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>X</t>
@@ -9987,13 +9847,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="Q101" t="n">
-        <v>288</v>
+        <v>88</v>
       </c>
       <c r="R101" t="n">
-        <v>342</v>
+        <v>94</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -10002,12 +9862,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>33647337</t>
+          <t>706072929</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33647337</t>
+          <t>https://m.place.naver.com/place/706072929</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -10024,29 +9884,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>네일노마드 용산푸르지오써밋점</t>
+          <t>신용산네일라뜰리에왁싱</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>kjr1212a@naver.com</t>
+          <t>hee_1220@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0507-1310-3658</t>
+          <t>0507-1380-7730</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
+          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10056,7 +9916,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10066,14 +9926,10 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qmrz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>X</t>
@@ -10085,13 +9941,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>471</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R102" t="n">
-        <v>479</v>
+        <v>2</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -10100,12 +9956,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1841821386</t>
+          <t>1054108199</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1841821386</t>
+          <t>https://m.place.naver.com/place/1054108199</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -10122,29 +9978,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>플로르 네일 이태원점</t>
+          <t>봉선화물들이다</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>flornail@naver.com</t>
+          <t>s8h6y@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>02-790-4182</t>
+          <t>02-6203-5478</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로 47 4층</t>
+          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/s8h6y</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10154,12 +10010,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10179,13 +10035,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="Q103" t="n">
-        <v>163</v>
+        <v>15</v>
       </c>
       <c r="R103" t="n">
-        <v>281</v>
+        <v>127</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10194,12 +10050,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>32435712</t>
+          <t>33618035</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32435712</t>
+          <t>https://m.place.naver.com/place/33618035</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -10216,29 +10072,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>이촌동 네일타임 삼익상가</t>
+          <t>네일리모노 이태원점</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>yjk2650@naver.com</t>
+          <t>nailremono@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>02-749-8604</t>
+          <t>0507-1350-6775</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
+          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nailremono</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10248,24 +10104,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43tew</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>X</t>
@@ -10277,13 +10129,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="Q104" t="n">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="R104" t="n">
-        <v>250</v>
+        <v>345</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10292,12 +10144,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1281193252</t>
+          <t>1785734080</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281193252</t>
+          <t>https://m.place.naver.com/place/1785734080</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10314,29 +10166,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>네일바이르레</t>
+          <t>이촌동 네일타임 삼익상가</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>l5v2osh@naver.com</t>
+          <t>yjk2650@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1312-9470</t>
+          <t>02-749-8604</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@ichon_nail_time</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10346,7 +10198,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10371,13 +10223,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="Q105" t="n">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="R105" t="n">
-        <v>93</v>
+        <v>250</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10386,12 +10238,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>37818863</t>
+          <t>1281193252</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37818863</t>
+          <t>https://m.place.naver.com/place/1281193252</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10408,20 +10260,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>네일바래</t>
+          <t>쵸민네일</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>naillab20@naver.com</t>
+          <t>sunday020@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0507-1403-3417</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 214-6 2층</t>
+          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10457,17 +10313,17 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10476,12 +10332,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>835341707</t>
+          <t>1664663384</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/835341707</t>
+          <t>https://m.place.naver.com/place/1664663384</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10498,29 +10354,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>진유진네일</t>
+          <t>오손내미오</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>seoul2816@naver.com</t>
+          <t>playnauts@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1416-2081</t>
+          <t>0507-1492-1340</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 284</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oh_sonemio</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10530,7 +10386,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -10551,17 +10407,17 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="Q107" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10570,12 +10426,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>31574498</t>
+          <t>1311070929</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31574498</t>
+          <t>https://m.place.naver.com/place/1311070929</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10592,29 +10448,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>에일린</t>
+          <t>우아한 네일 살롱</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>myungae7@naver.com</t>
+          <t>findmyperfectdays@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>0507-1445-2816</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/wooanail_salon</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10624,7 +10476,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -10645,17 +10497,17 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>394</v>
+        <v>63</v>
       </c>
       <c r="Q108" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="R108" t="n">
-        <v>471</v>
+        <v>64</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10664,12 +10516,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>1447531035</t>
+          <t>1370902820</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447531035</t>
+          <t>https://m.place.naver.com/place/1370902820</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10686,29 +10538,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>신용산네일라뜰리에왁싱</t>
+          <t>후암네일</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>hee_1220@naver.com</t>
+          <t>dndud7532@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0507-1380-7730</t>
+          <t>0507-1301-4091</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
+          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/huam_nail</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10718,7 +10570,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -10743,13 +10595,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R109" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10758,12 +10610,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1054108199</t>
+          <t>2033884779</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054108199</t>
+          <t>https://m.place.naver.com/place/2033884779</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10780,39 +10632,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>헤더네일</t>
+          <t>클리피</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>mmmmbin@naver.com</t>
+          <t>seoul2gun@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0507-1464-8960</t>
+          <t>1855-4010</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
+          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_txcJCb</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -10822,17 +10674,13 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5x7xu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -10841,13 +10689,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="Q110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10856,12 +10704,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1399079243</t>
+          <t>1546271749</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399079243</t>
+          <t>https://m.place.naver.com/place/1546271749</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10878,24 +10726,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>네일의날씨</t>
+          <t>센스</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>queen77577@naver.com</t>
+          <t>showmblog@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0507-1430-0707</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 288-2 1층</t>
+          <t>서울특별시 용산구 만리재로 140-1</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10920,32 +10764,28 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4yz4o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>497</v>
+        <v>4</v>
       </c>
       <c r="Q111" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="R111" t="n">
-        <v>545</v>
+        <v>6</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10954,12 +10794,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1050641028</t>
+          <t>1189922870</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050641028</t>
+          <t>https://m.place.naver.com/place/1189922870</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10976,29 +10816,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>더네일바 2호점</t>
+          <t>네일드모네</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>thenailbar@naver.com</t>
+          <t>themy1226@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>0507-1411-8549</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
+          <t>서울특별시 용산구 독서당로 67 206호</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/naildemonet</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -11008,7 +10844,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -11033,13 +10869,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="Q112" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="R112" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -11048,12 +10884,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>706072929</t>
+          <t>2062875678</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/706072929</t>
+          <t>https://m.place.naver.com/place/2062875678</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -11070,24 +10906,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>카밍네일</t>
+          <t>에일린</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>myungae7@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0507-1357-1496</t>
+          <t>0507-1445-2816</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 42 1층</t>
+          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -11112,14 +10948,10 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qpdf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>X</t>
@@ -11127,17 +10959,17 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>167</v>
+        <v>395</v>
       </c>
       <c r="Q113" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="R113" t="n">
-        <v>192</v>
+        <v>472</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -11146,12 +10978,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1383549813</t>
+          <t>1447531035</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383549813</t>
+          <t>https://m.place.naver.com/place/1447531035</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -11168,29 +11000,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>버들네일</t>
+          <t>플리네일 용산해링턴점</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>lamidays@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1400-7111</t>
+          <t>0507-1406-7552</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 147 1층</t>
+          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11200,7 +11032,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -11225,13 +11057,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>24</v>
+        <v>442</v>
       </c>
       <c r="Q114" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R114" t="n">
-        <v>28</v>
+        <v>457</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11240,12 +11072,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1127614127</t>
+          <t>2075608465</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127614127</t>
+          <t>https://m.place.naver.com/place/2075608465</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -11262,29 +11094,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>블랑</t>
+          <t>손톱까끼</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>white9651@naver.com</t>
+          <t>sinachoco@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>02-790-8798</t>
+          <t>0507-1310-9297</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
+          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kkakki_nail/</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11294,7 +11126,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -11319,13 +11151,13 @@
         </is>
       </c>
       <c r="P115" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q115" t="n">
         <v>7</v>
       </c>
-      <c r="Q115" t="n">
-        <v>1</v>
-      </c>
       <c r="R115" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11334,12 +11166,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>909330706</t>
+          <t>20939317</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/909330706</t>
+          <t>https://m.place.naver.com/place/20939317</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -11356,44 +11188,44 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>신데렐라</t>
+          <t>쵸코네일</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>dracura10@naver.com</t>
+          <t>boong27@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>02-790-3304</t>
+          <t>02-749-7795</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 61</t>
+          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -11409,17 +11241,17 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="Q116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R116" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11428,12 +11260,12 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>20662540</t>
+          <t>19490178</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20662540</t>
+          <t>https://m.place.naver.com/place/19490178</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -11450,29 +11282,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>다교네일 한남</t>
+          <t>네일바라기</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>dakyonail@naver.com</t>
+          <t>sydy8585@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>0507-1339-1024</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
+          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_baragi_</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11482,7 +11310,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -11498,7 +11326,7 @@
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -11507,13 +11335,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>338</v>
+        <v>89</v>
       </c>
       <c r="Q117" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="R117" t="n">
-        <v>374</v>
+        <v>105</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11522,12 +11350,12 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>37620988</t>
+          <t>1091743517</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37620988</t>
+          <t>https://m.place.naver.com/place/1091743517</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">

--- a/naver-place-crawler/results_nail/용산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/용산_네일샵.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>프로네일</t>
+          <t>리네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sonvely89@naver.com</t>
+          <t>dlwjddo7053@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1421-1525</t>
+          <t>0507-1421-7880</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
+          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/itaewonpronail/</t>
+          <t>http://instagram.com/ri_nail7877</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="Q2" t="n">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13028002</t>
+          <t>32244399</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13028002</t>
+          <t>https://m.place.naver.com/place/32244399</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>정원네일</t>
+          <t>청담네일박스 용산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pretty6144@naver.com</t>
+          <t>smilehh406@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1406-7118</t>
+          <t>0507-1325-5985</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
+          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cheongdam_nailbox</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,17 +700,13 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4snrh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1935294802</t>
+          <t>2020464978</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935294802</t>
+          <t>https://m.place.naver.com/place/2020464978</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>플로르 네일 이태원점</t>
+          <t>몽드메리</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flornail@naver.com</t>
+          <t>soul-bi@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-790-4182</t>
+          <t>0507-1382-2264</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로 47 4층</t>
+          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/monde.mery</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>118</v>
+        <v>764</v>
       </c>
       <c r="Q4" t="n">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>281</v>
+        <v>778</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>32435712</t>
+          <t>1681006741</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32435712</t>
+          <t>https://m.place.naver.com/place/1681006741</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오손내미오</t>
+          <t>투투네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>playnauts@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1492-1340</t>
+          <t>0507-1336-4546</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
+          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/twotwo_nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -907,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1311070929</t>
+          <t>1253759614</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311070929</t>
+          <t>https://m.place.naver.com/place/1253759614</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헤더네일</t>
+          <t>네일가꿈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mmmmbin@naver.com</t>
+          <t>hyu3323@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1464-8960</t>
+          <t>0507-1403-8723</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/e_nailshop_sj</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -986,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5x7xu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1005,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>475</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="R6" t="n">
-        <v>27</v>
+        <v>550</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1399079243</t>
+          <t>1966796864</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399079243</t>
+          <t>https://m.place.naver.com/place/1966796864</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1042,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일리모노 이태원점</t>
+          <t>네일래쉬</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nailremono@naver.com</t>
+          <t>nailash@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1350-6775</t>
+          <t>0507-1371-0008</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
+          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nailash</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1074,24 +1066,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4c298</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1103,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>326</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="R7" t="n">
-        <v>345</v>
+        <v>76</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1785734080</t>
+          <t>1220901153</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785734080</t>
+          <t>https://m.place.naver.com/place/1220901153</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,20 +1128,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일퀸</t>
+          <t>네일꾼</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kfreebaby@naver.com</t>
+          <t>jinheeloo@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1407-8585</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 47</t>
+          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1193,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>162</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1023738371</t>
+          <t>1395413071</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023738371</t>
+          <t>https://m.place.naver.com/place/1395413071</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
+          <t>네일헤라</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>j2lang@naver.com</t>
+          <t>heranaillash@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1345-4179</t>
+          <t>0507-1334-2839</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
+          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail.hera</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1262,7 +1254,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1272,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zprq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1291,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>301</v>
+        <v>8</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>21038031</t>
+          <t>1936017804</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21038031</t>
+          <t>https://m.place.naver.com/place/1936017804</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1328,24 +1316,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>디에고푸스 희네일 이촌점</t>
+          <t>붙여핸썹</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jwkang3929@naver.com</t>
+          <t>woowim@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1339-5732</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
+          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1381,17 +1365,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1972424680</t>
+          <t>1333965738</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972424680</t>
+          <t>https://m.place.naver.com/place/1333965738</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1422,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일슈슈</t>
+          <t>네일스눕</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>brilliant14694@naver.com</t>
+          <t>graceham_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1435-9113</t>
+          <t>0507-1428-1646</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
+          <t>서울특별시 용산구 한강대로52길 38 202호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_snoope</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1454,7 +1438,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1464,14 +1448,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ko6p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1483,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>461</v>
+        <v>145</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>489</v>
+        <v>151</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1185094311</t>
+          <t>1926501985</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185094311</t>
+          <t>https://m.place.naver.com/place/1926501985</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1520,24 +1500,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>다교네일 한남</t>
+          <t>네일월드</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dakyonail@naver.com</t>
+          <t>daisukitokyo@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1339-1024</t>
+          <t>02-715-9585</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
+          <t>서울특별시 용산구 효창원로8길 6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1568,22 +1548,22 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1592,12 +1572,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>37620988</t>
+          <t>1228817187</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37620988</t>
+          <t>https://m.place.naver.com/place/1228817187</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1614,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>비바이유 한남</t>
+          <t>무구네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>enoctobre-@naver.com</t>
+          <t>mugunail2025@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1371-9481</t>
+          <t>0507-1353-2420</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
+          <t>서울특별시 용산구 새창로14길 46 2층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1646,7 +1626,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1671,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1686,12 +1666,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2019591721</t>
+          <t>2093535455</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019591721</t>
+          <t>https://m.place.naver.com/place/2093535455</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1708,39 +1688,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일꾼</t>
+          <t>묘즈네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jinheeloo@naver.com</t>
+          <t>kaeh5173907@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1407-8585</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 1층101-1호</t>
+          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_WxedxgG</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1756,22 +1732,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="Q14" t="n">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>162</v>
+        <v>58</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1780,12 +1756,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1395413071</t>
+          <t>1136869573</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395413071</t>
+          <t>https://m.place.naver.com/place/1136869573</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1802,24 +1778,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>봉선화물들이다</t>
+          <t>네일퀸</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>s8h6y@naver.com</t>
+          <t>kfreebaby@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>02-6203-5478</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
+          <t>서울특별시 용산구 새창로14길 47</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1855,17 +1827,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1874,12 +1846,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>33618035</t>
+          <t>1023738371</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33618035</t>
+          <t>https://m.place.naver.com/place/1023738371</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1896,29 +1868,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>호박손톱</t>
+          <t>수아르네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bomi3692@naver.com</t>
+          <t>xxong_11@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>02-794-7958</t>
+          <t>0507-1354-9689</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
+          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/swa_rnail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1928,7 +1900,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1949,17 +1921,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1968,12 +1940,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>35927853</t>
+          <t>21568200</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35927853</t>
+          <t>https://m.place.naver.com/place/21568200</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1990,29 +1962,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Breathnailz</t>
+          <t>팝네일 신용산</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>syhong0120@naver.com</t>
+          <t>mhhj951026@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1358-6853</t>
+          <t>0507-1345-7477</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 36 1층</t>
+          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/popnail_7477</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2022,7 +1994,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2038,7 +2010,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2047,13 +2019,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>363</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2062,12 +2034,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1488241394</t>
+          <t>1306229960</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488241394</t>
+          <t>https://m.place.naver.com/place/1306229960</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2084,29 +2056,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>쵸코네일</t>
+          <t>더네일바 2호점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>boong27@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>02-749-7795</t>
+          <t>0507-1411-8549</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
+          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/thenailbar_hannam</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2116,7 +2088,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2137,17 +2109,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="R18" t="n">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2156,12 +2128,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>19490178</t>
+          <t>706072929</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19490178</t>
+          <t>https://m.place.naver.com/place/706072929</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2178,29 +2150,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>블랑</t>
+          <t>네일의날씨</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>white9651@naver.com</t>
+          <t>queen77577@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02-790-8798</t>
+          <t>0507-1430-0707</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
+          <t>서울특별시 용산구 한강대로 288-2 1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_nalssi</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2210,7 +2182,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2226,7 +2198,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2235,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>497</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>545</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2250,12 +2222,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>909330706</t>
+          <t>1050641028</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/909330706</t>
+          <t>https://m.place.naver.com/place/1050641028</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2272,29 +2244,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일가꿈</t>
+          <t>토마네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hyu3323@naver.com</t>
+          <t>yeoooey@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1403-8723</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이 D동 113호</t>
+          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/to.ma.nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2304,7 +2272,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2314,14 +2282,10 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcf6ev</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>X</t>
@@ -2333,13 +2297,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>475</v>
+        <v>122</v>
       </c>
       <c r="Q20" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>550</v>
+        <v>129</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2348,12 +2312,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1966796864</t>
+          <t>1701565426</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966796864</t>
+          <t>https://m.place.naver.com/place/1701565426</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2370,29 +2334,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>무구네일</t>
+          <t>덴드네일한남</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mugunail2025@naver.com</t>
+          <t>eunii222@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1353-2420</t>
+          <t>0507-1378-0596</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로14길 46 2층</t>
+          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mugunail?igsh=MXVyaXlwcGo3bWtybQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/eunii222</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2407,7 +2371,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2427,13 +2391,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>194</v>
+        <v>124</v>
       </c>
       <c r="Q21" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="R21" t="n">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2442,12 +2406,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2093535455</t>
+          <t>1108900148</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093535455</t>
+          <t>https://m.place.naver.com/place/1108900148</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2464,20 +2428,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
+          <t>진유진네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>tlstnals1010@naver.com</t>
+          <t>seoul2816@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1416-2081</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
+          <t>서울특별시 용산구 한강대로 284</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2517,13 +2485,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2532,12 +2500,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1222846707</t>
+          <t>31574498</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222846707</t>
+          <t>https://m.place.naver.com/place/31574498</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2554,25 +2522,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>더 트리니티 네일</t>
+          <t>이촌동 네일타임 삼익상가</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dlfnfl0129@naver.com</t>
+          <t>yjk2650@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>02-749-8604</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@ichon_nail_time</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2582,7 +2554,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2592,14 +2564,10 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41f8b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>X</t>
@@ -2611,13 +2579,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="Q23" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="R23" t="n">
-        <v>157</v>
+        <v>250</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2626,12 +2594,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1060176123</t>
+          <t>1281193252</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060176123</t>
+          <t>https://m.place.naver.com/place/1281193252</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2648,29 +2616,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>제이매직네일스</t>
+          <t>네일린</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>tlstnals1010@naver.com</t>
+          <t>cookyismylife@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>070-8882-4343</t>
+          <t>0507-1344-8515</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
+          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/j_magic_nail</t>
+          <t>https://www.instagram.com/naileensalon</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2705,13 +2673,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2720,12 +2688,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1438268528</t>
+          <t>1996449351</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438268528</t>
+          <t>https://m.place.naver.com/place/1996449351</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2742,29 +2710,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>제이비풋 굳은살&amp;발톱 케어</t>
+          <t>오늘도네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sunny_0225@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-794-8551</t>
+          <t>0507-1345-4179</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
+          <t>서울특별시 용산구 이촌로77길 19 내제6호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/today_nail_ichon</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2774,7 +2742,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2795,17 +2763,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="Q25" t="n">
-        <v>179</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>529</v>
+        <v>301</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2814,12 +2782,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>12791408</t>
+          <t>21038031</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12791408</t>
+          <t>https://m.place.naver.com/place/21038031</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2836,29 +2804,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일셀레나</t>
+          <t>네일디렉터</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>na_young03@naver.com</t>
+          <t>naildirector@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02-795-6529</t>
+          <t>02-797-8188</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
+          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/naildirector</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2868,27 +2836,23 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wasqu44</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2897,13 +2861,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>396</v>
+        <v>158</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R26" t="n">
-        <v>401</v>
+        <v>169</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2912,12 +2876,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>35489351</t>
+          <t>1487195546</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35489351</t>
+          <t>https://m.place.naver.com/place/1487195546</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2934,24 +2898,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>손톱까끼</t>
+          <t>센스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sinachoco@naver.com</t>
+          <t>showmblog@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0507-1310-9297</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
+          <t>서울특별시 용산구 만리재로 140-1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2976,14 +2936,10 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w15n7bp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>X</t>
@@ -2991,17 +2947,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3010,12 +2966,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>20939317</t>
+          <t>1189922870</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20939317</t>
+          <t>https://m.place.naver.com/place/1189922870</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3032,29 +2988,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일헤라</t>
+          <t>신용산네일라뜰리에왁싱</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>heranaillash@naver.com</t>
+          <t>hee_1220@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1334-2839</t>
+          <t>0507-1380-7730</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 313 208동 지하3층 116-1호 네일헤라</t>
+          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/latelier_beauty_bonnie</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3064,7 +3020,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3089,13 +3045,13 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>6</v>
-      </c>
       <c r="R28" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3104,12 +3060,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1936017804</t>
+          <t>1054108199</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1936017804</t>
+          <t>https://m.place.naver.com/place/1054108199</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3126,25 +3082,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일바라기</t>
+          <t>정원네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sydy8585@naver.com</t>
+          <t>pretty6144@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1406-7118</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
+          <t>서울특별시 용산구 원효로 51 삼성테마트 1층 104호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_baragi_</t>
+          <t>http://instagram.com/jungwon_nail_</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3179,13 +3139,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3194,12 +3154,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1091743517</t>
+          <t>1935294802</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091743517</t>
+          <t>https://m.place.naver.com/place/1935294802</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3216,29 +3176,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아로하네일</t>
+          <t>헤더네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bbotive@naver.com</t>
+          <t>mmmmbin@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1391-4369</t>
+          <t>0507-1464-8960</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로14길 10 2층</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 2층 21호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/heathernail_102/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3248,7 +3208,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3258,14 +3218,10 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4swbk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>X</t>
@@ -3277,13 +3233,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3292,12 +3248,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1264306160</t>
+          <t>1399079243</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264306160</t>
+          <t>https://m.place.naver.com/place/1399079243</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3314,29 +3270,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>손톱의취향 용산푸르지오써밋점</t>
+          <t>설화미</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>tastein_nail_yongsan@naver.com</t>
+          <t>who1who2@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1483-0870</t>
+          <t>0507-1381-4227</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
+          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sulwhami_beauty/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3346,7 +3302,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3356,14 +3312,10 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wn2l5gm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3375,13 +3327,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>482</v>
+        <v>54</v>
       </c>
       <c r="Q31" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="R31" t="n">
-        <v>775</v>
+        <v>342</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3390,12 +3342,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2055593167</t>
+          <t>33647337</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055593167</t>
+          <t>https://m.place.naver.com/place/33647337</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3412,29 +3364,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>청담네일박스 용산점</t>
+          <t>네일바래</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>smilehh406@naver.com</t>
+          <t>naillab20@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1325-5985</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 B동 110호</t>
+          <t>서울특별시 용산구 원효로 214-6 2층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nailbarae_bboong</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3444,7 +3392,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3454,17 +3402,13 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w1fw0g2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3473,13 +3417,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3488,12 +3432,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2020464978</t>
+          <t>835341707</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020464978</t>
+          <t>https://m.place.naver.com/place/835341707</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3510,44 +3454,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>진유진네일</t>
+          <t>마틸다네일M 한남점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>seoul2816@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1416-2081</t>
+          <t>0507-1412-3082</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 284</t>
+          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://matildanailshop-mo3.imweb.me/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3563,17 +3507,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="Q33" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="R33" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3582,12 +3526,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>31574498</t>
+          <t>1798849933</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31574498</t>
+          <t>https://m.place.naver.com/place/1798849933</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3604,29 +3548,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>러블리핑크</t>
+          <t>네일바라기</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kisever1@naver.com</t>
+          <t>sydy8585@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>02-704-8470</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 27 2층</t>
+          <t>서울특별시 용산구 새창로 98 1층 네일바라기</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_baragi_</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3636,7 +3576,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3657,17 +3597,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="R34" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3676,12 +3616,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>36901322</t>
+          <t>1091743517</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36901322</t>
+          <t>https://m.place.naver.com/place/1091743517</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3698,44 +3638,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일테라피은</t>
+          <t>쵸코네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>anrgudtkd@naver.com</t>
+          <t>boong27@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1379-8496</t>
+          <t>02-749-7795</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
+          <t>서울특별시 용산구 한강대로 95 용산래미안 더센트럴 지하2층 234호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3755,13 +3695,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3770,12 +3710,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1180134699</t>
+          <t>19490178</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180134699</t>
+          <t>https://m.place.naver.com/place/19490178</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3792,24 +3732,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>후암네일</t>
+          <t>티아라네일어반스파</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dndud7532@naver.com</t>
+          <t>orora_1976@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1301-4091</t>
+          <t>02-790-7882</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3834,14 +3774,10 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7alem9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>X</t>
@@ -3849,17 +3785,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3868,12 +3804,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2033884779</t>
+          <t>33213520</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033884779</t>
+          <t>https://m.place.naver.com/place/33213520</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3890,29 +3826,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>우아엘뷰티</t>
+          <t>플로르 네일 이태원점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>commathemoon_yongsan@naver.com</t>
+          <t>flornail@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1379-1978</t>
+          <t>02-790-4182</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 147 2층</t>
+          <t>서울특별시 용산구 우사단로 47 4층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/flornail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3922,24 +3858,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5xabi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>X</t>
@@ -3951,13 +3883,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="Q37" t="n">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="R37" t="n">
-        <v>127</v>
+        <v>281</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3966,12 +3898,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1942029836</t>
+          <t>32435712</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942029836</t>
+          <t>https://m.place.naver.com/place/32435712</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3988,12 +3920,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>붙여핸썹</t>
+          <t>데코네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>woowim@naver.com</t>
+          <t>jessygod@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -4001,12 +3933,12 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로 227 한빛내과 건물</t>
+          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4016,7 +3948,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4037,17 +3969,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4056,12 +3988,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1333965738</t>
+          <t>36812317</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333965738</t>
+          <t>https://m.place.naver.com/place/36812317</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4078,29 +4010,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일노마드 용산푸르지오써밋점</t>
+          <t>네일테라피은</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kjr1212a@naver.com</t>
+          <t>anrgudtkd@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1310-3658</t>
+          <t>0507-1379-8496</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
+          <t>서울특별시 용산구 효창원로 4 1층 1호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailtherapyeun</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4110,7 +4042,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4120,14 +4052,10 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qmrz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>X</t>
@@ -4139,13 +4067,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>471</v>
+        <v>203</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>479</v>
+        <v>212</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4154,12 +4082,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1841821386</t>
+          <t>1180134699</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1841821386</t>
+          <t>https://m.place.naver.com/place/1180134699</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4176,29 +4104,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일린</t>
+          <t>카밍네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>cookyismylife@naver.com</t>
+          <t>ynh3377@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1344-8515</t>
+          <t>0507-1357-1496</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 53 1층 (힐링약국옆)</t>
+          <t>서울특별시 용산구 소월로20길 42 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/calming_nail</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4208,7 +4136,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4218,14 +4146,10 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4zm9q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4237,13 +4161,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4252,12 +4176,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1996449351</t>
+          <t>1383549813</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996449351</t>
+          <t>https://m.place.naver.com/place/1383549813</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4274,29 +4198,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>리네일</t>
+          <t>디에고푸스 희네일 이촌점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dlwjddo7053@naver.com</t>
+          <t>jwkang3929@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1421-7880</t>
+          <t>0507-1339-5732</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가 1층 110호 리네일</t>
+          <t>서울특별시 용산구 이촌로 200 엘지프라자 제지하층 107호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/heenail4345</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4306,7 +4230,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4316,14 +4240,10 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5y9ij</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4335,13 +4255,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="R41" t="n">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4350,12 +4270,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>32244399</t>
+          <t>1972424680</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32244399</t>
+          <t>https://m.place.naver.com/place/1972424680</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4372,29 +4292,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일샵베이비</t>
+          <t>네일리모노 이태원점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>zxlixz@naver.com</t>
+          <t>nailremono@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1396-4649</t>
+          <t>0507-1350-6775</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 우사단로2길 19 1층</t>
+          <t>서울특별시 용산구 녹사평대로40가길 3-3 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nailremono</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4404,24 +4324,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40tj2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>X</t>
@@ -4429,17 +4345,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>38</v>
+        <v>326</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="R42" t="n">
-        <v>39</v>
+        <v>345</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4448,12 +4364,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1847608869</t>
+          <t>1785734080</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847608869</t>
+          <t>https://m.place.naver.com/place/1785734080</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4470,29 +4386,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>신데렐라</t>
+          <t>진주네 네일 효창공원점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dracura10@naver.com</t>
+          <t>jiana2002@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>02-790-3304</t>
+          <t>0507-1403-6610</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 61</t>
+          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jinjunenail</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4502,7 +4418,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4523,17 +4439,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R43" t="n">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4542,12 +4458,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>20662540</t>
+          <t>2056938739</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20662540</t>
+          <t>https://m.place.naver.com/place/2056938739</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4564,12 +4480,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>글로시블라썸 아이파크몰</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>irumskin@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4577,12 +4493,12 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55</t>
+          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nailclover_yongsan</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4592,7 +4508,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4613,17 +4529,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4632,12 +4548,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1485867849</t>
+          <t>32496791</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485867849</t>
+          <t>https://m.place.naver.com/place/32496791</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4654,24 +4570,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일디렉터</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>naildirector@naver.com</t>
+          <t>052young@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>02-797-8188</t>
+          <t>0507-1416-0638</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 제지하1층 B163호</t>
+          <t>서울특별시 용산구 새창로 70 상가-210</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4696,14 +4612,10 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjten8b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>X</t>
@@ -4711,17 +4623,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R45" t="n">
-        <v>169</v>
+        <v>10</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4730,12 +4642,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1487195546</t>
+          <t>36629016</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487195546</t>
+          <t>https://m.place.naver.com/place/36629016</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4752,29 +4664,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>제이미 네일</t>
+          <t>살롱드다한</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>see7833@naver.com</t>
+          <t>ddalkong9830@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>02-701-5602</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
+          <t>서울특별시 용산구 원효로 257 2층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dahan_nail/?igsh=aXRnbWdmYnJjZ2tw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4784,7 +4692,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4805,17 +4713,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>29</v>
+        <v>229</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="R46" t="n">
-        <v>31</v>
+        <v>282</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4824,12 +4732,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>255540367</t>
+          <t>1917414808</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/255540367</t>
+          <t>https://m.place.naver.com/place/1917414808</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4846,24 +4754,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>투투네일</t>
+          <t>Breathnailz</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>syhong0120@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1336-4546</t>
+          <t>0507-1358-6853</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로77길 10 용산빌리지 201호</t>
+          <t>서울특별시 용산구 소월로20길 36 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4899,17 +4807,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4918,12 +4826,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1253759614</t>
+          <t>1488241394</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253759614</t>
+          <t>https://m.place.naver.com/place/1488241394</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4940,25 +4848,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>우아한 네일 살롱</t>
+          <t>네일샵입니다</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>findmyperfectdays@naver.com</t>
+          <t>yooawo@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1336-5457</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
+          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/shopnailshop/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4968,7 +4880,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4993,13 +4905,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>63</v>
+        <v>171</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R48" t="n">
-        <v>64</v>
+        <v>206</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5008,12 +4920,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1370902820</t>
+          <t>954197461</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370902820</t>
+          <t>https://m.place.naver.com/place/954197461</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5030,29 +4942,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>오드리네일</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ardusy@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1446-0227</t>
+          <t>070-8882-4343</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
+          <t>서울특별시 용산구 백범로 341 용산 문배동 리첸시아 상가A동 310호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oudreynail</t>
+          <t>http://www.instagram.com/j_magic_nail</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5087,13 +4999,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="R49" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5102,12 +5014,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1497063684</t>
+          <t>1438268528</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1497063684</t>
+          <t>https://m.place.naver.com/place/1438268528</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5124,24 +5036,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>위위즈 용산점</t>
+          <t>글로시블라썸 아이파크몰</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>yigu8@naver.com</t>
+          <t>irumskin@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1366-3547</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
+          <t>서울특별시 용산구 한강대로23길 55</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5177,17 +5085,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>510</v>
+        <v>54</v>
       </c>
       <c r="Q50" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>543</v>
+        <v>54</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5196,12 +5104,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1557214777</t>
+          <t>1485867849</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557214777</t>
+          <t>https://m.place.naver.com/place/1485867849</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5218,29 +5126,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>바림</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>virus8163@naver.com</t>
-        </is>
-      </c>
+          <t>오렌지나무</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>02-318-2055</t>
+          <t>0507-1323-2154</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 두텁바위로 73</t>
+          <t>서울특별시 용산구 한남대로20길 13 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/orangetree_hannam?igshid=i928yr0jsd8h</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5250,7 +5154,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5275,13 +5179,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q51" t="n">
         <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5290,12 +5194,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1862156671</t>
+          <t>1568164546</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862156671</t>
+          <t>https://m.place.naver.com/place/1568164546</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5312,25 +5216,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일클로버</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>bongbong323@naver.com</t>
-        </is>
-      </c>
+          <t>아드</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 211 102동 111호</t>
+          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/a.th_kr</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5340,7 +5240,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5365,13 +5265,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5380,12 +5280,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>32496791</t>
+          <t>1700535825</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32496791</t>
+          <t>https://m.place.naver.com/place/1700535825</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5402,24 +5302,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>춘희손톱</t>
+          <t>에일린</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>chii0216@naver.com</t>
+          <t>myungae7@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1306-7521</t>
+          <t>0507-1445-2816</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
+          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5444,14 +5344,10 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc1bsb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>X</t>
@@ -5459,17 +5355,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>196</v>
+        <v>395</v>
       </c>
       <c r="Q53" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="R53" t="n">
-        <v>295</v>
+        <v>472</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5478,12 +5374,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>20559743</t>
+          <t>1447531035</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20559743</t>
+          <t>https://m.place.naver.com/place/1447531035</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5500,34 +5396,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>이촌동 네일타임 삼익상가</t>
+          <t>뷰리뉼레</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>yjk2650@naver.com</t>
+          <t>kimnr123@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>02-749-8604</t>
+          <t>0507-1389-5562</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가 지하1층 12호 네일타임</t>
+          <t>서울특별시 용산구 후암로 28 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://toss.place/_lb/TYhSdSVIw</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5542,14 +5438,10 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43tew</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>X</t>
@@ -5561,13 +5453,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="Q54" t="n">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>250</v>
+        <v>142</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5576,12 +5468,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1281193252</t>
+          <t>33277553</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281193252</t>
+          <t>https://m.place.naver.com/place/33277553</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5598,24 +5490,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일래쉬</t>
+          <t>이촌 네일타임 LG프라자</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>nailash@naver.com</t>
+          <t>blingsea@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1371-0008</t>
+          <t>0507-1498-8612</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로90길 74 이안용산1차 101동 107호</t>
+          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5640,14 +5532,10 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4itvj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>X</t>
@@ -5655,17 +5543,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="Q55" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="R55" t="n">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5674,12 +5562,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1220901153</t>
+          <t>20064911</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220901153</t>
+          <t>https://m.place.naver.com/place/20064911</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5696,12 +5584,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>수 네일</t>
+          <t>네일더누브</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>qkrqhrdfrn@naver.com</t>
+          <t>hasom0304@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -5709,22 +5597,22 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 196 B1층</t>
+          <t>서울특별시 용산구 원효로 210 1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xdFnxhn</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5734,14 +5622,10 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47r14</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>O</t>
@@ -5753,13 +5637,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R56" t="n">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5768,12 +5652,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1989007422</t>
+          <t>1146800442</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989007422</t>
+          <t>https://m.place.naver.com/place/1146800442</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5790,29 +5674,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>수아르네일</t>
+          <t>우아한 네일 살롱</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>swa_r@naver.com</t>
+          <t>findmyperfectdays@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0507-1354-9689</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로26가길 13 1층</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 지하 1층 118호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/wooanail_salon</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5822,7 +5702,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5847,13 +5727,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5862,12 +5742,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>21568200</t>
+          <t>1370902820</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21568200</t>
+          <t>https://m.place.naver.com/place/1370902820</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5884,25 +5764,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>살롱드다한</t>
+          <t>네일삼각지</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ddalkong9830@naver.com</t>
+          <t>nailsamgakji@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1316-2792</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 257 2층</t>
+          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_samgakji</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5912,7 +5796,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5928,7 +5812,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5937,13 +5821,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="Q58" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>282</v>
+        <v>22</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5952,12 +5836,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1917414808</t>
+          <t>1872968588</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917414808</t>
+          <t>https://m.place.naver.com/place/1872968588</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5974,29 +5858,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>신용산네일라뜰리에왁싱</t>
+          <t>켈리하우스 네일샵</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>hee_1220@naver.com</t>
+          <t>kellylove09@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1380-7730</t>
+          <t>0507-1393-9967</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 해링턴스퀘어 105동 상가 2층 28호</t>
+          <t>서울특별시 용산구 보광로 49</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/kellylove09</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6006,12 +5890,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6027,17 +5911,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R59" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6046,12 +5930,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1054108199</t>
+          <t>32875703</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054108199</t>
+          <t>https://m.place.naver.com/place/32875703</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6068,29 +5952,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>더네일바 2호점</t>
+          <t>수 네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>beczzam@naver.com</t>
+          <t>qkrqhrdfrn@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1411-8549</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로55나길 6 B1</t>
+          <t>서울특별시 용산구 만리재로 196 B1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/thenailbar_hannam</t>
+          <t>https://blog.naver.com/qkrqhrdfrn</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6105,7 +5985,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6116,7 +5996,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6125,13 +6005,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="Q60" t="n">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="R60" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6140,12 +6020,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>706072929</t>
+          <t>1989007422</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/706072929</t>
+          <t>https://m.place.naver.com/place/1989007422</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6162,24 +6042,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>오렌지나무</t>
+          <t>신데렐라</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kmaxim2@naver.com</t>
+          <t>dracura10@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1323-2154</t>
+          <t>02-790-3304</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로20길 13 1층</t>
+          <t>서울특별시 용산구 보광로 61</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6215,17 +6095,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q61" t="n">
         <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6234,12 +6114,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1568164546</t>
+          <t>20662540</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568164546</t>
+          <t>https://m.place.naver.com/place/20662540</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6256,29 +6136,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일바이르레</t>
+          <t>비바이유 한남</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>l5v2osh@naver.com</t>
+          <t>enoctobre-@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1312-9470</t>
+          <t>0507-1371-9481</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
+          <t>서울특별시 용산구 한남대로46길 2-7 3층 301호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/b.by_you</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6288,7 +6168,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6313,13 +6193,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6328,12 +6208,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>37818863</t>
+          <t>2019591721</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37818863</t>
+          <t>https://m.place.naver.com/place/2019591721</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6350,29 +6230,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일프롬다니</t>
+          <t>네일슈슈</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>arielisflowery@naver.com</t>
+          <t>brilliant14694@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1349-9460</t>
+          <t>0507-1435-9113</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
+          <t>서울특별시 용산구 이촌로 248 한강맨션 21동 101-1호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_chouchou_</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6382,7 +6262,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6407,13 +6287,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>17</v>
+        <v>461</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R63" t="n">
-        <v>17</v>
+        <v>489</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6422,12 +6302,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1774853191</t>
+          <t>1185094311</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774853191</t>
+          <t>https://m.place.naver.com/place/1185094311</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6444,29 +6324,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>버들네일</t>
+          <t>더 트리니티 네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>test_golry@naver.com</t>
+          <t>dlfnfl0129@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0507-1400-7111</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 147 1층</t>
+          <t>서울특별시 용산구 유엔빌리지길 20 1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/the_trinity_nail/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6476,7 +6352,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6501,13 +6377,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="R64" t="n">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6516,12 +6392,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1127614127</t>
+          <t>1060176123</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127614127</t>
+          <t>https://m.place.naver.com/place/1060176123</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6538,12 +6414,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일드모네</t>
+          <t>오나네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>themy1226@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -6551,12 +6427,12 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 67 206호</t>
+          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naildemonet</t>
+          <t>https://www.instagram.com/o.nnail</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6591,13 +6467,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="R65" t="n">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6606,12 +6482,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2062875678</t>
+          <t>1549497362</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2062875678</t>
+          <t>https://m.place.naver.com/place/1549497362</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6628,29 +6504,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일스눕</t>
+          <t>위위즈 용산점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>graceham_@naver.com</t>
+          <t>yigu8@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1428-1646</t>
+          <t>0507-1366-3547</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로52길 38 202호</t>
+          <t>서울특별시 용산구 서빙고로 17 해링턴스퀘어 102동 상가 1층 142호 위위즈</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ouiouiznail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6660,7 +6536,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6685,13 +6561,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>145</v>
+        <v>510</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="R66" t="n">
-        <v>151</v>
+        <v>543</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6700,12 +6576,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1926501985</t>
+          <t>1557214777</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926501985</t>
+          <t>https://m.place.naver.com/place/1557214777</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6722,25 +6598,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>오나네일</t>
+          <t>블랑</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>hg6580@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>02-790-8798</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로81길 3 시온캐슬 2층 201호</t>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크 헤링턴스퀘어 A몰 2062</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nailist_blanc</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6750,7 +6630,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6775,13 +6655,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6790,12 +6670,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1549497362</t>
+          <t>909330706</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1549497362</t>
+          <t>https://m.place.naver.com/place/909330706</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6812,29 +6692,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일삼각지</t>
+          <t>레푸스 용산역점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>nailsamgakji@naver.com</t>
+          <t>refussyss@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1316-2792</t>
+          <t>0507-1417-1074</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로62다길 10 101호</t>
+          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@레푸스용산역점</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6844,7 +6724,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6860,7 +6740,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6869,13 +6749,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>17</v>
+        <v>293</v>
       </c>
       <c r="Q68" t="n">
-        <v>5</v>
+        <v>192</v>
       </c>
       <c r="R68" t="n">
-        <v>22</v>
+        <v>485</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6884,12 +6764,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1872968588</t>
+          <t>1153661148</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1872968588</t>
+          <t>https://m.place.naver.com/place/1153661148</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6906,39 +6786,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일샵입니다</t>
+          <t>마고뷰티</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yooawo@naver.com</t>
+          <t>mago_smp@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0507-1336-5457</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 신성미소시티 1층 108-1호</t>
+          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xjBnAn</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6954,7 +6830,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6963,13 +6839,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="Q69" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R69" t="n">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6978,12 +6854,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>954197461</t>
+          <t>1939429266</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/954197461</t>
+          <t>https://m.place.naver.com/place/1939429266</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7000,20 +6876,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>아드</t>
+          <t>네일샵베이비</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>adfontes_math@naver.com</t>
+          <t>zxlixz@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1396-4649</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로42나길 22 1층 아드</t>
+          <t>서울특별시 용산구 우사단로2길 19 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7038,14 +6918,10 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcl18no</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>X</t>
@@ -7053,17 +6929,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7072,12 +6948,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1700535825</t>
+          <t>1847608869</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700535825</t>
+          <t>https://m.place.naver.com/place/1847608869</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7094,34 +6970,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>유스뷰티</t>
+          <t>반디인하우스 용산아이파크몰점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jyrif91@naver.com</t>
+          <t>bandinhouse_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1422-3533</t>
+          <t>0507-1472-1811</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로20길 21 1층</t>
+          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youthnail/</t>
+          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7131,7 +7007,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7151,13 +7027,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4</v>
+        <v>1254</v>
       </c>
       <c r="Q71" t="n">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="R71" t="n">
-        <v>121</v>
+        <v>1443</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7166,12 +7042,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>38467380</t>
+          <t>1049297184</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38467380</t>
+          <t>https://m.place.naver.com/place/1049297184</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7188,25 +7064,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>묘즈네일</t>
+          <t>춘희손톱</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kaeh5173907@naver.com</t>
+          <t>pskk0000@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1306-7521</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로80길 21-9 남영빌딩 4층 404호</t>
+          <t>서울특별시 용산구 대사관로24길 15 지하1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/choonheenail</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7216,7 +7096,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7232,7 +7112,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7241,13 +7121,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="R72" t="n">
-        <v>58</v>
+        <v>295</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7256,12 +7136,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1136869573</t>
+          <t>20559743</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136869573</t>
+          <t>https://m.place.naver.com/place/20559743</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7278,25 +7158,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>어서오손네일</t>
+          <t>플리네일 용산해링턴점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>funhanbro@naver.com</t>
+          <t>lamidays@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1406-7552</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
+          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/plry_nail?igsh=b2wzMXcxczY4ZWNz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7306,7 +7190,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7331,13 +7215,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>11</v>
+        <v>442</v>
       </c>
       <c r="Q73" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R73" t="n">
-        <v>23</v>
+        <v>457</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7346,12 +7230,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1030962704</t>
+          <t>2075608465</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030962704</t>
+          <t>https://m.place.naver.com/place/2075608465</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7368,35 +7252,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>마고뷰티</t>
+          <t>클리피</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>mago_smp@naver.com</t>
+          <t>seoul2gun@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1855-4010</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 115 지하1층 109호</t>
+          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_txcJCb</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7406,14 +7294,10 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v3xa</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>O</t>
@@ -7425,13 +7309,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="Q74" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7440,12 +7324,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1939429266</t>
+          <t>1546271749</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939429266</t>
+          <t>https://m.place.naver.com/place/1546271749</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7462,34 +7346,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>반디인하우스 용산아이파크몰점</t>
+          <t>손톱까끼</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>bandinhouse_yongsan@naver.com</t>
+          <t>sinachoco@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1472-1811</t>
+          <t>0507-1310-9297</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 에이치디씨 아이파크몰 리빙파크 8층</t>
+          <t>서울특별시 용산구 청파로45길 12-1 1층 손톱까끼</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/bandinhouseyongsan</t>
+          <t>https://www.instagram.com/kkakki_nail/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7499,19 +7383,15 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4oyxx</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>X</t>
@@ -7519,17 +7399,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1254</v>
+        <v>49</v>
       </c>
       <c r="Q75" t="n">
-        <v>189</v>
+        <v>7</v>
       </c>
       <c r="R75" t="n">
-        <v>1443</v>
+        <v>56</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7538,12 +7418,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1049297184</t>
+          <t>20939317</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049297184</t>
+          <t>https://m.place.naver.com/place/20939317</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7560,29 +7440,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>이촌 네일타임 LG프라자</t>
+          <t>코코루네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>blingsea@naver.com</t>
+          <t>xanxixxanx@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1498-8612</t>
+          <t>0507-1390-4270</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 200 LG프라자 지하층 118호 네일타임</t>
+          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kokoroo__nail?igsh=YzVkODRmOTdmMw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7592,7 +7472,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7613,17 +7493,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
         <v>5</v>
       </c>
       <c r="R76" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7632,12 +7512,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>20064911</t>
+          <t>1768871817</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20064911</t>
+          <t>https://m.place.naver.com/place/1768871817</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7654,39 +7534,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>팁셋 네일 한남점</t>
+          <t>벨르네이쳐</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>likelife_lovely@naver.com</t>
+          <t>dewsang@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1375-5705</t>
+          <t>0507-1463-0395</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
+          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_pixftn/chat</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7696,17 +7576,13 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wvdcyx7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7715,13 +7591,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="Q77" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R77" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7730,12 +7606,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1409853951</t>
+          <t>2043754067</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1409853951</t>
+          <t>https://m.place.naver.com/place/2043754067</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7752,25 +7628,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>컬러테일러</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ariarisom2@naver.com</t>
+          <t>milkycoco95@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>02-749-9134</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
+          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/vivinail</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7780,7 +7660,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7796,7 +7676,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7805,13 +7685,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>322</v>
+        <v>258</v>
       </c>
       <c r="Q78" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="R78" t="n">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7820,12 +7700,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1031854178</t>
+          <t>21834362</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031854178</t>
+          <t>https://m.place.naver.com/place/21834362</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7842,29 +7722,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>봉선화물들이다</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>s8h6y@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>02-749-9134</t>
+          <t>02-6203-5478</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 264 삼익상가</t>
+          <t>서울특별시 용산구 청파로47길 10 1층 2층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/s8h6y</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7874,24 +7754,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w48ses</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>X</t>
@@ -7903,13 +7779,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>258</v>
+        <v>113</v>
       </c>
       <c r="Q79" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="R79" t="n">
-        <v>303</v>
+        <v>128</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7918,12 +7794,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>21834362</t>
+          <t>33618035</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21834362</t>
+          <t>https://m.place.naver.com/place/33618035</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7940,29 +7816,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>리라네일</t>
+          <t>우아엘뷰티</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kkmm_0707@naver.com</t>
+          <t>commathemoon_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>02-703-4125</t>
+          <t>0507-1379-1978</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 23</t>
+          <t>서울특별시 용산구 효창원로 147 2층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/commathemoon_yongsan</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7972,12 +7848,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7993,17 +7869,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="R80" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8012,12 +7888,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1131445662</t>
+          <t>1942029836</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131445662</t>
+          <t>https://m.place.naver.com/place/1942029836</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8034,34 +7910,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>마틸다네일M 한남점</t>
+          <t>오손내미오</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>vin2roo@naver.com</t>
+          <t>playnauts@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1412-3082</t>
+          <t>0507-1492-1340</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한남대로21길 20 7층 마틸다네일 M 한남점</t>
+          <t>서울특별시 용산구 이태원로 217 현대안성타워 305호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://matildanailshop-mo3.imweb.me/</t>
+          <t>https://www.instagram.com/oh_sonemio</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8071,7 +7947,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8091,13 +7967,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="Q81" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8106,12 +7982,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1798849933</t>
+          <t>1311070929</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798849933</t>
+          <t>https://m.place.naver.com/place/1311070929</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8128,29 +8004,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>쿠로키네일</t>
+          <t>팁셋 네일 한남점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>kurokinail@naver.com</t>
+          <t>likelife_lovely@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1481-2893</t>
+          <t>0507-1375-5705</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 신흥로 19-2 1층</t>
+          <t>서울특별시 용산구 이태원로49길 14-3 302호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/tipset.seoul/</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8160,7 +8036,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8170,17 +8046,13 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5z5mm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8189,13 +8061,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="Q82" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R82" t="n">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8204,12 +8076,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1723956505</t>
+          <t>1409853951</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723956505</t>
+          <t>https://m.place.naver.com/place/1409853951</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8226,25 +8098,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>네일더누브</t>
+          <t>빛나러오소문제성발관리 용산점</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>hasom0304@naver.com</t>
+          <t>kknsky73@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1419-6888</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 210 1층</t>
+          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@user-gc4wk2yn2b</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8254,7 +8130,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8279,13 +8155,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>112</v>
+        <v>250</v>
       </c>
       <c r="Q83" t="n">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="R83" t="n">
-        <v>131</v>
+        <v>416</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8294,12 +8170,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1146800442</t>
+          <t>1438224262</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1146800442</t>
+          <t>https://m.place.naver.com/place/1438224262</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8316,35 +8192,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>재니네일한남</t>
+          <t>루아드네일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>evian___@naver.com</t>
+          <t>sumr2002@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1452-9237</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
+          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xoEbJn/friend</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8369,13 +8249,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="Q84" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="R84" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8384,12 +8264,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1593741438</t>
+          <t>2003721483</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593741438</t>
+          <t>https://m.place.naver.com/place/2003721483</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8406,29 +8286,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>네일의날씨</t>
+          <t>네일뮤지엄</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>queen77577@naver.com</t>
+          <t>nail-museum@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1430-0707</t>
+          <t>070-7543-4009</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 288-2 1층</t>
+          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nail-museum</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8438,27 +8318,23 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4yz4o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8467,13 +8343,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>497</v>
+        <v>345</v>
       </c>
       <c r="Q85" t="n">
-        <v>48</v>
+        <v>360</v>
       </c>
       <c r="R85" t="n">
-        <v>545</v>
+        <v>705</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8482,12 +8358,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1050641028</t>
+          <t>1881584782</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050641028</t>
+          <t>https://m.place.naver.com/place/1881584782</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8504,29 +8380,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>켈리하우스 네일샵</t>
+          <t>바림</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>kellylove09@naver.com</t>
+          <t>virus8163@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1393-9967</t>
+          <t>02-318-2055</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로 49</t>
+          <t>서울특별시 용산구 두텁바위로 73</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/Barim_nail</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8536,7 +8412,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8557,17 +8433,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8576,12 +8452,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>32875703</t>
+          <t>1862156671</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32875703</t>
+          <t>https://m.place.naver.com/place/1862156671</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8598,29 +8474,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>코코루네일</t>
+          <t>오드리네일</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>everydayenn@naver.com</t>
+          <t>ardusy@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1390-4270</t>
+          <t>0507-1446-0227</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 녹사평대로46길 23 1층</t>
+          <t>서울특별시 용산구 보광로 29-1 1층 오드리네일</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oudreynail</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8630,7 +8506,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8640,14 +8516,10 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wyj7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>X</t>
@@ -8659,13 +8531,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="Q87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8674,12 +8546,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1768871817</t>
+          <t>1497063684</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768871817</t>
+          <t>https://m.place.naver.com/place/1497063684</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8696,29 +8568,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>진주네 네일 효창공원점</t>
+          <t>손톱의취향 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jiana2002@naver.com</t>
+          <t>tastein_nail_yongsan@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1403-6610</t>
+          <t>0507-1483-0870</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로39길 3 백락빌딩 1층 나나헤어</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B104-2</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/taste_in_nail_</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8728,7 +8600,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8753,13 +8625,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>79</v>
+        <v>482</v>
       </c>
       <c r="Q88" t="n">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c r="R88" t="n">
-        <v>98</v>
+        <v>778</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8768,12 +8640,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2056938739</t>
+          <t>2055593167</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056938739</t>
+          <t>https://m.place.naver.com/place/2055593167</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8790,20 +8662,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>네일바래</t>
+          <t>제이미 네일</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>naillab20@naver.com</t>
+          <t>see7833@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>02-701-5602</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 214-6 2층</t>
+          <t>서울특별시 용산구 청파로45길 28 1층 제이미네일</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8839,17 +8715,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="Q89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8858,12 +8734,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>835341707</t>
+          <t>255540367</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/835341707</t>
+          <t>https://m.place.naver.com/place/255540367</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8880,24 +8756,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>티아라네일어반스파</t>
+          <t>쵸민네일</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>orora_1976@naver.com</t>
+          <t>sunday020@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>02-790-7882</t>
+          <t>0507-1403-3417</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 248 한강맨션31동 202호</t>
+          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8937,10 +8813,10 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
         <v>2</v>
@@ -8952,12 +8828,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>33213520</t>
+          <t>1664663384</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33213520</t>
+          <t>https://m.place.naver.com/place/1664663384</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8974,25 +8850,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>데코네일</t>
+          <t>제이제이 네일</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jessygod@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1411-8138</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로45길 8 2층 데코네일</t>
+          <t>서울특별시 용산구 회나무로 32-3 2층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://instagram.com/deco._.nail?igshid=Zjc2ZTc4Nzk=</t>
+          <t>https://www.instagram.com/jjjjnail</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9027,13 +8907,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="R91" t="n">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -9042,12 +8922,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>36812317</t>
+          <t>79017915</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36812317</t>
+          <t>https://m.place.naver.com/place/79017915</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9064,24 +8944,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>클리피</t>
+          <t>리라네일</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>seoul2gun@naver.com</t>
+          <t>kkmm_0707@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1855-4010</t>
+          <t>02-703-4125</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로44길 29 1층 101호</t>
+          <t>서울특별시 용산구 원효로41길 23</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9112,22 +8992,22 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9136,12 +9016,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1546271749</t>
+          <t>1131445662</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546271749</t>
+          <t>https://m.place.naver.com/place/1131445662</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9158,29 +9038,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>팝네일 신용산</t>
+          <t>아로하네일</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>mhhj951026@naver.com</t>
+          <t>bbotive@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0507-1345-7477</t>
+          <t>0507-1391-4369</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 100 아모레퍼시픽 신사옥 지하1층</t>
+          <t>서울특별시 용산구 이태원로14길 10 2층</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/popnail_7477</t>
+          <t>http://www.instagram.com/alohanail_chae</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9206,7 +9086,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9215,13 +9095,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>316</v>
+        <v>75</v>
       </c>
       <c r="Q93" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="R93" t="n">
-        <v>363</v>
+        <v>78</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9230,12 +9110,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1306229960</t>
+          <t>1264306160</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306229960</t>
+          <t>https://m.place.naver.com/place/1264306160</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9252,24 +9132,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>루아드네일</t>
+          <t>네일휴</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sumr2002@naver.com</t>
+          <t>white5198@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1452-9237</t>
+          <t>02-711-3646</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로20길 9-13 3층</t>
+          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9294,32 +9174,28 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa539rh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9328,12 +9204,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>2003721483</t>
+          <t>1611951357</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003721483</t>
+          <t>https://m.place.naver.com/place/1611951357</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9350,29 +9226,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>네일휴</t>
+          <t>후암네일</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>white5198@naver.com</t>
+          <t>dndud7532@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>02-711-3646</t>
+          <t>0507-1301-4091</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6 1층 네일휴</t>
+          <t>서울특별시 용산구 두텁바위로37길 6 1층 101호</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/huam_nail</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9382,7 +9258,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9403,17 +9279,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9422,12 +9298,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1611951357</t>
+          <t>2033884779</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611951357</t>
+          <t>https://m.place.naver.com/place/2033884779</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9444,29 +9320,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>제이제이 네일</t>
+          <t>또또네일</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>clsald30@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1411-8138</t>
+          <t>0507-1354-9049</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 회나무로 32-3 2층</t>
+          <t>서울특별시 용산구 원효로 200 1층</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ttotto__nail</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9476,7 +9352,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9501,13 +9377,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R96" t="n">
-        <v>3</v>
+        <v>157</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9516,12 +9392,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>79017915</t>
+          <t>2020672159</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/79017915</t>
+          <t>https://m.place.naver.com/place/2020672159</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9538,29 +9414,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>레푸스 용산역점</t>
+          <t>버들네일</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>refussyss@naver.com</t>
+          <t>test_golry@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1417-1074</t>
+          <t>0507-1400-7111</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 69 상가동 지하1층 B103-1호</t>
+          <t>서울특별시 용산구 신흥로 147 1층</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/b_d_nail</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9570,7 +9446,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9580,14 +9456,10 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5iw5q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>X</t>
@@ -9599,13 +9471,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>293</v>
+        <v>24</v>
       </c>
       <c r="Q97" t="n">
-        <v>192</v>
+        <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>485</v>
+        <v>28</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9614,12 +9486,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1153661148</t>
+          <t>1127614127</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153661148</t>
+          <t>https://m.place.naver.com/place/1127614127</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9636,39 +9508,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>설화미</t>
+          <t>쿠로키네일</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>who1who2@naver.com</t>
+          <t>vin2roo@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1381-4227</t>
+          <t>0507-1481-2893</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 143-1 2층 설화미</t>
+          <t>서울특별시 용산구 신흥로 19-2 1층</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xaxcxeBG</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9678,17 +9550,13 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4krlm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9697,13 +9565,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="Q98" t="n">
-        <v>288</v>
+        <v>8</v>
       </c>
       <c r="R98" t="n">
-        <v>342</v>
+        <v>166</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9712,12 +9580,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>33647337</t>
+          <t>1723956505</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33647337</t>
+          <t>https://m.place.naver.com/place/1723956505</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9734,29 +9602,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>메종드로르</t>
+          <t>유스뷰티</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>stylechosun@naver.com</t>
+          <t>jyrif91@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1386-1014</t>
+          <t>0507-1422-3533</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
+          <t>서울특별시 용산구 이태원로20길 21 1층</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/youthnail/</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9766,7 +9634,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -9791,13 +9659,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="R99" t="n">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9806,12 +9674,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>2029580174</t>
+          <t>38467380</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029580174</t>
+          <t>https://m.place.naver.com/place/38467380</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -9828,39 +9696,35 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>루미가넷네일존 이마트 용산점</t>
+          <t>컬러테일러</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>hyer2986@naver.com</t>
+          <t>ariarisom2@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0507-1401-9470</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
+          <t>서울특별시 용산구 백범로99길 40 101동 112호</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_vpyXn</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9876,22 +9740,22 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>86</v>
+        <v>322</v>
       </c>
       <c r="Q100" t="n">
         <v>2</v>
       </c>
       <c r="R100" t="n">
-        <v>88</v>
+        <v>324</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9900,12 +9764,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1619342094</t>
+          <t>1031854178</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619342094</t>
+          <t>https://m.place.naver.com/place/1031854178</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -9922,24 +9786,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>몽드메리</t>
+          <t>제이비풋 굳은살&amp;발톱 케어</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>soul-bi@naver.com</t>
+          <t>sunny_0225@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1382-2264</t>
+          <t>02-794-8551</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 D몰 1층 1052호</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 1층 114-1호</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9964,14 +9828,10 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqmw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>X</t>
@@ -9979,17 +9839,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>764</v>
+        <v>350</v>
       </c>
       <c r="Q101" t="n">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="R101" t="n">
-        <v>778</v>
+        <v>529</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9998,12 +9858,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1681006741</t>
+          <t>12791408</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681006741</t>
+          <t>https://m.place.naver.com/place/12791408</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -10020,29 +9880,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>벨르네이쳐</t>
+          <t>어서오손네일</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>dewsang@naver.com</t>
+          <t>funhanbro@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>0507-1463-0395</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 39 101동 1층 108-4호 Bellenature</t>
+          <t>서울특별시 용산구 한강대로 115 대우디오빌 2층 201호</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/funhanbro</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10052,12 +9908,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10068,7 +9924,7 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -10077,13 +9933,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="Q102" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R102" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -10092,12 +9948,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>2043754067</t>
+          <t>1030962704</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043754067</t>
+          <t>https://m.place.naver.com/place/1030962704</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -10114,25 +9970,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>토마네일</t>
+          <t>네일프롬다니</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>yeoooey@naver.com</t>
+          <t>arielisflowery@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1349-9460</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로49길 14 은주빌 1층</t>
+          <t>서울특별시 용산구 백범로45길 4-10 . 지하1층 B105호</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailfrm_dani?utm_source=qr&amp;igsh=ZTM4ZDRiNzUwMw==</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10142,7 +10002,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10167,13 +10027,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="Q103" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10182,12 +10042,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1701565426</t>
+          <t>1774853191</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701565426</t>
+          <t>https://m.place.naver.com/place/1774853191</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -10199,61 +10059,53 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>네일아트재료</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>에일린</t>
+          <t>메이크케이</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>skl_0527@naver.com</t>
+          <t>kbanknow@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>0507-1445-2816</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로65가길 66 대영아파트상가지하1층</t>
+          <t>서울특별시 용산구 청파로47길 56 1층</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/reel/DXD2x-ciXs5/?utm_source=ig_web_copy_link</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4rgmy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>X</t>
@@ -10261,17 +10113,17 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10280,12 +10132,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1447531035</t>
+          <t>2081839313</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447531035</t>
+          <t>https://m.place.naver.com/place/2081839313</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -10302,24 +10154,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>이앤앤</t>
+          <t>러블리핑크</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>eyennail@naver.com</t>
+          <t>kisever1@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1316-3771</t>
+          <t>02-704-8470</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
+          <t>서울특별시 용산구 청파로45길 27 2층</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10344,14 +10196,10 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc6bbh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>X</t>
@@ -10359,17 +10207,17 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>599</v>
+        <v>11</v>
       </c>
       <c r="Q105" t="n">
-        <v>1333</v>
+        <v>2</v>
       </c>
       <c r="R105" t="n">
-        <v>1932</v>
+        <v>13</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10378,12 +10226,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>375707328</t>
+          <t>36901322</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/375707328</t>
+          <t>https://m.place.naver.com/place/36901322</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -10400,24 +10248,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>또또네일</t>
+          <t>루미가넷네일존 이마트 용산점</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>clsald30@naver.com</t>
+          <t>hyer2986@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0507-1354-9049</t>
+          <t>0507-1401-9470</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로 200 1층</t>
+          <t>서울특별시 용산구 한강대로23길 55 이마트 용산점 지하2층</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10442,14 +10290,10 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wal8cit</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>X</t>
@@ -10457,17 +10301,17 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="Q106" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R106" t="n">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10476,12 +10320,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>2020672159</t>
+          <t>1619342094</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020672159</t>
+          <t>https://m.place.naver.com/place/1619342094</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -10493,17 +10337,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>네일아트재료</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>메이크케이</t>
+          <t>재니네일한남</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>kbanknow@naver.com</t>
+          <t>evian___@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -10511,22 +10355,22 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로47길 56 1층</t>
+          <t>서울특별시 용산구 독서당로 46 1층 104호 재니네일한남</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_eKxmLxl</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -10542,22 +10386,22 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10566,12 +10410,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>2081839313</t>
+          <t>1593741438</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2081839313</t>
+          <t>https://m.place.naver.com/place/1593741438</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -10588,24 +10432,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>나비네일</t>
+          <t>호박손톱</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>shinding7610@naver.com</t>
+          <t>bomi3692@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0507-1416-0638</t>
+          <t>02-794-7958</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 새창로 70 상가-210</t>
+          <t>서울특별시 용산구 보광로 11 2층 호박손톱</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10645,13 +10489,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Q108" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R108" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10660,12 +10504,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>36629016</t>
+          <t>35927853</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36629016</t>
+          <t>https://m.place.naver.com/place/35927853</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -10682,39 +10526,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>빛나러오소문제성발관리 용산점</t>
+          <t>다교네일 한남</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>kknsky73@naver.com</t>
+          <t>swih@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0507-1419-6888</t>
+          <t>0507-1339-1024</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 95 지하2층 비204호</t>
+          <t>서울특별시 용산구 독서당로 46 한남아이파크 204호</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_VZqxfG/chat</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -10724,14 +10568,10 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e3s1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
           <t>O</t>
@@ -10743,13 +10583,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>250</v>
+        <v>338</v>
       </c>
       <c r="Q109" t="n">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="R109" t="n">
-        <v>416</v>
+        <v>374</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10758,12 +10598,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1438224262</t>
+          <t>37620988</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438224262</t>
+          <t>https://m.place.naver.com/place/37620988</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -10780,29 +10620,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>네일뮤지엄</t>
+          <t>네일바이르레</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>nail-museum@naver.com</t>
+          <t>l5v2osh@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>070-7543-4009</t>
+          <t>0507-1312-9470</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 275 제상가동 101호 네일뮤지엄</t>
+          <t>서울특별시 용산구 이촌로 224 1층 136호</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_by_lerre</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -10812,7 +10652,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -10822,14 +10662,10 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wch6zi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>X</t>
@@ -10841,13 +10677,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>345</v>
+        <v>87</v>
       </c>
       <c r="Q110" t="n">
-        <v>360</v>
+        <v>6</v>
       </c>
       <c r="R110" t="n">
-        <v>705</v>
+        <v>93</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10856,12 +10692,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1881584782</t>
+          <t>37818863</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881584782</t>
+          <t>https://m.place.naver.com/place/37818863</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10878,29 +10714,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>네일월드</t>
+          <t>프로네일</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>bongbong0401@naver.com</t>
+          <t>sonvely89@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>02-715-9585</t>
+          <t>0507-1421-1525</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 효창원로8길 6</t>
+          <t>서울특별시 용산구 이태원로27가길 9 3층 프로네일</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/itaewonpronail/</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10910,7 +10746,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -10931,17 +10767,17 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10950,12 +10786,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1228817187</t>
+          <t>13028002</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228817187</t>
+          <t>https://m.place.naver.com/place/13028002</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10972,29 +10808,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>뷰리뉼레</t>
+          <t>네일셀레나</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>kimnr123@naver.com</t>
+          <t>na_young03@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0507-1389-5562</t>
+          <t>02-795-6529</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 후암로 28 1층</t>
+          <t>서울특별시 용산구 한강대로 205 용산파크자이</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYhSdSVIw</t>
+          <t>http://pf.kakao.com/_zJpfG</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -11004,7 +10840,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -11020,7 +10856,7 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -11029,13 +10865,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>136</v>
+        <v>396</v>
       </c>
       <c r="Q112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R112" t="n">
-        <v>142</v>
+        <v>401</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -11044,12 +10880,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>33277553</t>
+          <t>35489351</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33277553</t>
+          <t>https://m.place.naver.com/place/35489351</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -11066,29 +10902,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>플리네일 용산해링턴점</t>
+          <t>네일드모네</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>lamidays@naver.com</t>
+          <t>themy1226@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>0507-1406-7552</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 17 E몰동 2층 2023호</t>
+          <t>서울특별시 용산구 독서당로 67 206호</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/naildemonet</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -11098,7 +10930,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -11108,14 +10940,10 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wl1i419</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>X</t>
@@ -11127,13 +10955,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>442</v>
+        <v>100</v>
       </c>
       <c r="Q113" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="R113" t="n">
-        <v>457</v>
+        <v>103</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -11142,12 +10970,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>2075608465</t>
+          <t>2062875678</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075608465</t>
+          <t>https://m.place.naver.com/place/2062875678</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -11164,29 +10992,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>덴드네일한남</t>
+          <t>네일노마드 용산푸르지오써밋점</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>eunii222@naver.com</t>
+          <t>kjr1212a@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1378-0596</t>
+          <t>0507-1310-3658</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로 56 4층 401호</t>
+          <t>서울특별시 용산구 한강대로 69 용산푸르지오써밋 지하1층 B110-1호</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailnomad_</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11196,7 +11024,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -11221,13 +11049,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>124</v>
+        <v>471</v>
       </c>
       <c r="Q114" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="R114" t="n">
-        <v>146</v>
+        <v>479</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11236,12 +11064,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1108900148</t>
+          <t>1841821386</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108900148</t>
+          <t>https://m.place.naver.com/place/1841821386</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -11258,24 +11086,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>쵸민네일</t>
+          <t>제이매직네일스</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>sunday020@naver.com</t>
+          <t>tlstnals1010@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>0507-1403-3417</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 69 파크타워 106동 지하1층 쵸민네일</t>
+          <t>서울특별시 용산구 문배동 40-29 용산리첸시아 상가 a동 310호</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -11300,14 +11124,10 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ua47</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
           <t>X</t>
@@ -11319,13 +11139,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
         <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11334,12 +11154,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1664663384</t>
+          <t>1222846707</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664663384</t>
+          <t>https://m.place.naver.com/place/1222846707</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -11356,25 +11176,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>센스</t>
+          <t>이앤앤</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>showmblog@naver.com</t>
+          <t>eyennail@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0507-1316-3771</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 140-1</t>
+          <t>서울특별시 용산구 한강대로44길 17-3 2층 201호</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/_eyennail_</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11384,7 +11208,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -11405,17 +11229,17 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>4</v>
+        <v>599</v>
       </c>
       <c r="Q116" t="n">
-        <v>2</v>
+        <v>1333</v>
       </c>
       <c r="R116" t="n">
-        <v>6</v>
+        <v>1932</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11424,12 +11248,12 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>1189922870</t>
+          <t>375707328</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189922870</t>
+          <t>https://m.place.naver.com/place/375707328</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -11446,29 +11270,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>카밍네일</t>
+          <t>메종드로르</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ynh3377@naver.com</t>
+          <t>stylechosun@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0507-1357-1496</t>
+          <t>0507-1386-1014</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 소월로20길 42 1층</t>
+          <t>서울특별시 용산구 한강대로50길 14 5층 501호</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/maisondelor.official?igsh=OWh3MXlqb2dxd2Yx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11478,7 +11302,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -11488,14 +11312,10 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qpdf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>X</t>
@@ -11507,13 +11327,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>167</v>
+        <v>30</v>
       </c>
       <c r="Q117" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11522,12 +11342,12 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>1383549813</t>
+          <t>2029580174</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383549813</t>
+          <t>https://m.place.naver.com/place/2029580174</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
